--- a/Assets/StreamingAssets/Configurations/dev/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/dev/Cards.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{402544E3-79F5-492A-BE22-4EEB323B6A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFAA2696-E98F-42D5-8367-B5DB15D52C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="540" windowWidth="38730" windowHeight="20850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Conditions" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$A$1:$AG$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$A$1:$AH$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="317">
   <si>
     <t>ID</t>
   </si>
@@ -261,9 +261,6 @@
     <t>欢迎上舰</t>
   </si>
   <si>
-    <t>舰长+1，神采+4，体力消耗减少+2回合</t>
-  </si>
-  <si>
     <t>攻击弹幕</t>
   </si>
   <si>
@@ -940,6 +937,57 @@
   </si>
   <si>
     <t>VCardTypeUsedCountCondition</t>
+  </si>
+  <si>
+    <t>参数+X1</t>
+  </si>
+  <si>
+    <t>DescriptionInGame</t>
+  </si>
+  <si>
+    <t>神采+X1</t>
+  </si>
+  <si>
+    <t>参数+X1，红温大于10层时，参数+X2</t>
+  </si>
+  <si>
+    <t>参数+X1，神采+X2</t>
+  </si>
+  <si>
+    <t>重抽其他手牌，卡牌使用次数+X3，体力消耗减少50%+X2回合</t>
+  </si>
+  <si>
+    <t>获得一个额外回合，神采+X1，出牌次数+X2</t>
+  </si>
+  <si>
+    <t>亲和力+X1，神采+X2</t>
+  </si>
+  <si>
+    <t>专注+X1，神采+X2</t>
+  </si>
+  <si>
+    <t>红温+X1，神采+X2</t>
+  </si>
+  <si>
+    <t>参数+X1/2次</t>
+  </si>
+  <si>
+    <t>获得亲和力X1的参数</t>
+  </si>
+  <si>
+    <t>亲和力+X1，获得亲和力层数X2的参数</t>
+  </si>
+  <si>
+    <t>舰长+X1，神采+X2，体力消耗减少+X3回合</t>
+  </si>
+  <si>
+    <t>舰长+1，神采+4，体力消耗减少+2回合+UC17:V17</t>
+  </si>
+  <si>
+    <t>下一张使用的牌会使用两次，抽X3张卡,神采+X2</t>
+  </si>
+  <si>
+    <t>亲和力+X1</t>
   </si>
 </sst>
 </file>
@@ -1302,42 +1350,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG61"/>
+  <dimension ref="A1:AH61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="4.85546875" customWidth="1"/>
-    <col min="6" max="6" width="7.85546875" customWidth="1"/>
-    <col min="7" max="7" width="5" customWidth="1"/>
-    <col min="8" max="8" width="5.5703125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" style="3" customWidth="1"/>
-    <col min="11" max="11" width="7.140625" customWidth="1"/>
-    <col min="12" max="12" width="14" style="3" customWidth="1"/>
-    <col min="13" max="13" width="10.28515625" customWidth="1"/>
-    <col min="14" max="14" width="13.7109375" customWidth="1"/>
-    <col min="15" max="15" width="9.7109375" style="3" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="17" width="12.140625" customWidth="1"/>
-    <col min="18" max="18" width="17.7109375" style="3" customWidth="1"/>
-    <col min="19" max="19" width="11" customWidth="1"/>
-    <col min="20" max="20" width="12.28515625" customWidth="1"/>
-    <col min="21" max="21" width="17.140625" style="3" customWidth="1"/>
-    <col min="24" max="24" width="17.7109375" style="3" customWidth="1"/>
-    <col min="25" max="25" width="10.7109375" customWidth="1"/>
-    <col min="26" max="26" width="11" customWidth="1"/>
-    <col min="27" max="27" width="17.7109375" style="3" customWidth="1"/>
-    <col min="28" max="28" width="12.42578125" customWidth="1"/>
-    <col min="29" max="29" width="12.42578125" style="3" customWidth="1"/>
-    <col min="30" max="30" width="12.28515625" customWidth="1"/>
-    <col min="31" max="31" width="9" style="3"/>
-    <col min="32" max="32" width="4.28515625" customWidth="1"/>
+    <col min="4" max="4" width="57.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="4.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.85546875" customWidth="1"/>
+    <col min="8" max="8" width="5" customWidth="1"/>
+    <col min="9" max="9" width="5.5703125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="7.140625" customWidth="1"/>
+    <col min="13" max="13" width="14" style="3" customWidth="1"/>
+    <col min="14" max="14" width="10.28515625" customWidth="1"/>
+    <col min="15" max="15" width="13.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" style="3" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="18" width="12.140625" customWidth="1"/>
+    <col min="19" max="19" width="17.7109375" style="3" customWidth="1"/>
+    <col min="20" max="20" width="11" customWidth="1"/>
+    <col min="21" max="21" width="12.28515625" customWidth="1"/>
+    <col min="22" max="22" width="17.140625" style="3" customWidth="1"/>
+    <col min="25" max="25" width="17.7109375" style="3" customWidth="1"/>
+    <col min="26" max="26" width="10.7109375" customWidth="1"/>
+    <col min="27" max="27" width="11" customWidth="1"/>
+    <col min="28" max="28" width="17.7109375" style="3" customWidth="1"/>
+    <col min="29" max="29" width="12.42578125" customWidth="1"/>
+    <col min="30" max="30" width="12.42578125" style="3" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" customWidth="1"/>
+    <col min="32" max="32" width="9" style="3"/>
+    <col min="33" max="33" width="4.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" spans="1:34">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1347,95 +1396,98 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="D1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:33">
+    <row r="2" spans="1:34">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1445,49 +1497,52 @@
       <c r="C2" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>35</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>36</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>37</v>
       </c>
-      <c r="J2"/>
-      <c r="K2" s="2">
+      <c r="K2"/>
+      <c r="L2" s="2">
         <v>4</v>
       </c>
-      <c r="L2" s="3">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
+      <c r="M2" s="3">
+        <v>3</v>
       </c>
       <c r="N2">
         <v>0</v>
       </c>
-      <c r="O2"/>
-      <c r="P2" s="2">
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2"/>
+      <c r="Q2" s="2">
         <v>11</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>7</v>
       </c>
-      <c r="R2" s="3">
+      <c r="S2" s="3">
         <v>7</v>
       </c>
-      <c r="U2"/>
-      <c r="X2"/>
-      <c r="AA2"/>
-      <c r="AC2"/>
-      <c r="AE2"/>
-      <c r="AF2" s="5"/>
-    </row>
-    <row r="3" spans="1:33">
+      <c r="V2"/>
+      <c r="Y2"/>
+      <c r="AB2"/>
+      <c r="AD2"/>
+      <c r="AF2"/>
+      <c r="AG2" s="5"/>
+    </row>
+    <row r="3" spans="1:34">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1497,49 +1552,52 @@
       <c r="C3" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>40</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>36</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>37</v>
       </c>
-      <c r="J3"/>
-      <c r="K3" s="2">
-        <v>0</v>
-      </c>
-      <c r="L3" s="3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
+      <c r="K3"/>
+      <c r="L3" s="2">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3">
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3"/>
-      <c r="P3" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3"/>
+      <c r="Q3" s="2">
+        <v>2</v>
+      </c>
+      <c r="R3">
         <v>4</v>
       </c>
-      <c r="R3" s="3">
+      <c r="S3" s="3">
         <v>4</v>
       </c>
-      <c r="U3"/>
-      <c r="X3"/>
-      <c r="AA3"/>
-      <c r="AC3"/>
-      <c r="AE3"/>
-      <c r="AF3" s="5"/>
-    </row>
-    <row r="4" spans="1:33">
+      <c r="V3"/>
+      <c r="Y3"/>
+      <c r="AB3"/>
+      <c r="AD3"/>
+      <c r="AF3"/>
+      <c r="AG3" s="5"/>
+    </row>
+    <row r="4" spans="1:34">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1549,51 +1607,54 @@
       <c r="C4" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" t="s">
+        <v>303</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>35</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>43</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>37</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>5</v>
       </c>
-      <c r="L4" s="3">
+      <c r="M4" s="3">
         <v>4</v>
       </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
       <c r="N4">
         <v>0</v>
       </c>
-      <c r="P4" s="2">
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2">
         <v>11</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>15</v>
       </c>
-      <c r="R4" s="3">
+      <c r="S4" s="3">
         <v>18</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <v>56</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <v>9</v>
       </c>
-      <c r="U4" s="3">
+      <c r="V4" s="3">
         <v>12</v>
       </c>
-      <c r="AF4" s="5"/>
-    </row>
-    <row r="5" spans="1:33">
+      <c r="AG4" s="5"/>
+    </row>
+    <row r="5" spans="1:34">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1603,57 +1664,60 @@
       <c r="C5" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" t="s">
+        <v>304</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>35</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>36</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>37</v>
       </c>
-      <c r="J5"/>
-      <c r="K5" s="2">
-        <v>3</v>
-      </c>
-      <c r="L5" s="3">
-        <v>3</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
+      <c r="K5"/>
+      <c r="L5" s="2">
+        <v>3</v>
+      </c>
+      <c r="M5" s="3">
+        <v>3</v>
       </c>
       <c r="N5">
         <v>0</v>
       </c>
-      <c r="O5"/>
-      <c r="P5" s="2">
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5"/>
+      <c r="Q5" s="2">
         <v>11</v>
       </c>
-      <c r="Q5">
+      <c r="R5">
         <v>5</v>
       </c>
-      <c r="R5" s="3">
+      <c r="S5" s="3">
         <v>5</v>
       </c>
-      <c r="S5" s="2">
-        <v>2</v>
-      </c>
-      <c r="T5">
-        <v>2</v>
-      </c>
-      <c r="U5" s="3">
-        <v>2</v>
-      </c>
-      <c r="X5"/>
-      <c r="AA5"/>
-      <c r="AC5"/>
-      <c r="AE5"/>
-      <c r="AF5" s="5"/>
-    </row>
-    <row r="6" spans="1:33">
+      <c r="T5" s="2">
+        <v>2</v>
+      </c>
+      <c r="U5">
+        <v>2</v>
+      </c>
+      <c r="V5" s="3">
+        <v>2</v>
+      </c>
+      <c r="Y5"/>
+      <c r="AB5"/>
+      <c r="AD5"/>
+      <c r="AF5"/>
+      <c r="AG5" s="5"/>
+    </row>
+    <row r="6" spans="1:34">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1663,57 +1727,60 @@
       <c r="C6" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" t="s">
+        <v>315</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>40</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>43</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>49</v>
       </c>
-      <c r="J6" s="3">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6" s="3">
-        <v>1</v>
-      </c>
-      <c r="M6">
+      <c r="K6" s="3">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6" s="3">
         <v>1</v>
       </c>
       <c r="N6">
         <v>1</v>
       </c>
-      <c r="P6" s="2">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>2</v>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>0</v>
       </c>
       <c r="T6">
         <v>2</v>
       </c>
-      <c r="U6" s="3">
+      <c r="U6">
+        <v>2</v>
+      </c>
+      <c r="V6" s="3">
         <v>7</v>
       </c>
-      <c r="V6">
+      <c r="W6">
         <v>9</v>
       </c>
-      <c r="W6">
-        <v>1</v>
-      </c>
-      <c r="X6" s="3">
-        <v>1</v>
-      </c>
-      <c r="AF6" s="5"/>
-    </row>
-    <row r="7" spans="1:33">
+      <c r="X6">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG6" s="5"/>
+    </row>
+    <row r="7" spans="1:34">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1723,60 +1790,63 @@
       <c r="C7" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" t="s">
+        <v>305</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>40</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>36</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>37</v>
       </c>
-      <c r="J7"/>
-      <c r="K7" s="2">
+      <c r="K7"/>
+      <c r="L7" s="2">
         <v>5</v>
       </c>
-      <c r="L7" s="3">
+      <c r="M7" s="3">
         <v>4</v>
       </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
       <c r="N7">
         <v>1</v>
       </c>
-      <c r="O7"/>
-      <c r="P7" s="2">
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7"/>
+      <c r="Q7" s="2">
         <v>4</v>
       </c>
-      <c r="R7"/>
-      <c r="S7" s="2">
+      <c r="S7"/>
+      <c r="T7" s="2">
         <v>21</v>
       </c>
-      <c r="T7">
-        <v>2</v>
-      </c>
-      <c r="U7" s="3">
-        <v>2</v>
-      </c>
-      <c r="V7" s="2">
+      <c r="U7">
+        <v>2</v>
+      </c>
+      <c r="V7" s="3">
+        <v>2</v>
+      </c>
+      <c r="W7" s="2">
         <v>14</v>
       </c>
-      <c r="W7">
-        <v>1</v>
-      </c>
-      <c r="X7" s="3">
-        <v>1</v>
-      </c>
-      <c r="AA7"/>
-      <c r="AC7"/>
-      <c r="AE7"/>
-      <c r="AF7" s="5"/>
-    </row>
-    <row r="8" spans="1:33">
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB7"/>
+      <c r="AD7"/>
+      <c r="AF7"/>
+      <c r="AG7" s="5"/>
+    </row>
+    <row r="8" spans="1:34">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1786,67 +1856,70 @@
       <c r="C8" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" t="s">
+        <v>306</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>40</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>54</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>49</v>
       </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8" s="2">
-        <v>1</v>
-      </c>
-      <c r="L8" s="3">
-        <v>1</v>
-      </c>
-      <c r="M8">
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1</v>
+      </c>
+      <c r="M8" s="3">
         <v>1</v>
       </c>
       <c r="N8">
         <v>1</v>
       </c>
-      <c r="O8"/>
-      <c r="P8" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q8">
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8"/>
+      <c r="Q8" s="2">
+        <v>2</v>
+      </c>
+      <c r="R8">
         <v>7</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7</v>
       </c>
-      <c r="S8" s="2">
-        <v>3</v>
-      </c>
-      <c r="T8">
-        <v>1</v>
-      </c>
-      <c r="U8" s="3">
-        <v>1</v>
-      </c>
-      <c r="V8" s="2">
+      <c r="T8" s="2">
+        <v>3</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8" s="3">
+        <v>1</v>
+      </c>
+      <c r="W8" s="2">
         <v>14</v>
       </c>
-      <c r="W8">
-        <v>1</v>
-      </c>
-      <c r="X8" s="3">
-        <v>1</v>
-      </c>
-      <c r="AA8"/>
-      <c r="AC8"/>
-      <c r="AE8"/>
-      <c r="AF8" s="5"/>
-    </row>
-    <row r="9" spans="1:33">
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB8"/>
+      <c r="AD8"/>
+      <c r="AF8"/>
+      <c r="AG8" s="5"/>
+    </row>
+    <row r="9" spans="1:34">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1856,57 +1929,60 @@
       <c r="C9" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" t="s">
+        <v>307</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>40</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>35</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>37</v>
       </c>
-      <c r="J9"/>
-      <c r="K9" s="2">
-        <v>2</v>
-      </c>
-      <c r="L9" s="3">
-        <v>2</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
+      <c r="K9"/>
+      <c r="L9" s="2">
+        <v>2</v>
+      </c>
+      <c r="M9" s="3">
+        <v>2</v>
       </c>
       <c r="N9">
         <v>0</v>
       </c>
-      <c r="O9"/>
-      <c r="P9" s="2">
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9"/>
+      <c r="Q9" s="2">
         <v>6</v>
       </c>
-      <c r="Q9">
-        <v>3</v>
-      </c>
-      <c r="R9" s="3">
+      <c r="R9">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3">
         <v>4</v>
       </c>
-      <c r="S9" s="2">
-        <v>2</v>
-      </c>
-      <c r="T9">
-        <v>3</v>
-      </c>
-      <c r="U9" s="3">
+      <c r="T9" s="2">
+        <v>2</v>
+      </c>
+      <c r="U9">
+        <v>3</v>
+      </c>
+      <c r="V9" s="3">
         <v>4</v>
       </c>
-      <c r="X9"/>
-      <c r="AA9"/>
-      <c r="AC9"/>
-      <c r="AE9"/>
-      <c r="AF9" s="5"/>
-    </row>
-    <row r="10" spans="1:33">
+      <c r="Y9"/>
+      <c r="AB9"/>
+      <c r="AD9"/>
+      <c r="AF9"/>
+      <c r="AG9" s="5"/>
+    </row>
+    <row r="10" spans="1:34">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1916,57 +1992,60 @@
       <c r="C10" t="s">
         <v>58</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" t="s">
+        <v>308</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>40</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>54</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>37</v>
       </c>
-      <c r="J10"/>
-      <c r="K10" s="2">
-        <v>2</v>
-      </c>
-      <c r="L10" s="3">
-        <v>2</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
+      <c r="K10"/>
+      <c r="L10" s="2">
+        <v>2</v>
+      </c>
+      <c r="M10" s="3">
+        <v>2</v>
       </c>
       <c r="N10">
         <v>0</v>
       </c>
-      <c r="O10"/>
-      <c r="P10" s="2">
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10"/>
+      <c r="Q10" s="2">
         <v>7</v>
       </c>
-      <c r="Q10">
-        <v>2</v>
-      </c>
-      <c r="R10" s="3">
-        <v>3</v>
-      </c>
-      <c r="S10" s="2">
-        <v>2</v>
-      </c>
-      <c r="T10">
-        <v>2</v>
-      </c>
-      <c r="U10" s="3">
-        <v>3</v>
-      </c>
-      <c r="X10"/>
-      <c r="AA10"/>
-      <c r="AC10"/>
-      <c r="AE10"/>
-      <c r="AF10" s="5"/>
-    </row>
-    <row r="11" spans="1:33">
+      <c r="R10">
+        <v>2</v>
+      </c>
+      <c r="S10" s="3">
+        <v>3</v>
+      </c>
+      <c r="T10" s="2">
+        <v>2</v>
+      </c>
+      <c r="U10">
+        <v>2</v>
+      </c>
+      <c r="V10" s="3">
+        <v>3</v>
+      </c>
+      <c r="Y10"/>
+      <c r="AB10"/>
+      <c r="AD10"/>
+      <c r="AF10"/>
+      <c r="AG10" s="5"/>
+    </row>
+    <row r="11" spans="1:34">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1976,51 +2055,54 @@
       <c r="C11" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" t="s">
+        <v>309</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>40</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>43</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>37</v>
       </c>
-      <c r="K11">
-        <v>2</v>
-      </c>
-      <c r="L11" s="3">
-        <v>2</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
+      <c r="L11">
+        <v>2</v>
+      </c>
+      <c r="M11" s="3">
+        <v>2</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
-      <c r="P11" s="2">
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="2">
         <v>15</v>
       </c>
-      <c r="Q11">
-        <v>2</v>
-      </c>
-      <c r="R11" s="3">
-        <v>3</v>
-      </c>
-      <c r="S11" s="2">
-        <v>2</v>
-      </c>
-      <c r="T11">
-        <v>2</v>
-      </c>
-      <c r="U11" s="3">
-        <v>3</v>
-      </c>
-      <c r="AF11" s="5"/>
-    </row>
-    <row r="12" spans="1:33">
+      <c r="R11">
+        <v>2</v>
+      </c>
+      <c r="S11" s="3">
+        <v>3</v>
+      </c>
+      <c r="T11" s="2">
+        <v>2</v>
+      </c>
+      <c r="U11">
+        <v>2</v>
+      </c>
+      <c r="V11" s="3">
+        <v>3</v>
+      </c>
+      <c r="AG11" s="5"/>
+    </row>
+    <row r="12" spans="1:34">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2030,60 +2112,63 @@
       <c r="C12" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" t="s">
+        <v>310</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>35</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>54</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>37</v>
       </c>
-      <c r="J12"/>
-      <c r="K12" s="2">
+      <c r="K12"/>
+      <c r="L12" s="2">
         <v>6</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>6</v>
       </c>
-      <c r="M12">
-        <v>1</v>
-      </c>
       <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12"/>
-      <c r="P12" s="2">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12"/>
+      <c r="Q12" s="2">
         <v>11</v>
       </c>
-      <c r="Q12">
+      <c r="R12">
         <v>9</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>13</v>
       </c>
-      <c r="S12" s="2">
+      <c r="T12" s="2">
         <v>11</v>
       </c>
-      <c r="T12">
+      <c r="U12">
         <v>9</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>13</v>
       </c>
-      <c r="X12"/>
-      <c r="AA12"/>
-      <c r="AC12"/>
-      <c r="AE12"/>
-      <c r="AF12" s="5"/>
-      <c r="AG12" t="s">
+      <c r="Y12"/>
+      <c r="AB12"/>
+      <c r="AD12"/>
+      <c r="AF12"/>
+      <c r="AG12" s="5"/>
+      <c r="AH12" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:33">
+    <row r="13" spans="1:34">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2093,57 +2178,60 @@
       <c r="C13" t="s">
         <v>65</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" t="s">
+        <v>304</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>35</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>36</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>37</v>
       </c>
-      <c r="J13"/>
-      <c r="K13" s="2">
+      <c r="K13"/>
+      <c r="L13" s="2">
         <v>5</v>
       </c>
-      <c r="L13" s="3">
+      <c r="M13" s="3">
         <v>5</v>
       </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
       <c r="N13">
         <v>0</v>
       </c>
-      <c r="O13"/>
-      <c r="P13" s="2">
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13"/>
+      <c r="Q13" s="2">
         <v>11</v>
       </c>
-      <c r="Q13">
+      <c r="R13">
         <v>11</v>
       </c>
-      <c r="R13" s="3">
+      <c r="S13" s="3">
         <v>15</v>
       </c>
-      <c r="S13" s="2">
-        <v>2</v>
-      </c>
-      <c r="T13">
+      <c r="T13" s="2">
+        <v>2</v>
+      </c>
+      <c r="U13">
         <v>7</v>
       </c>
-      <c r="U13" s="3">
+      <c r="V13" s="3">
         <v>9</v>
       </c>
-      <c r="X13"/>
-      <c r="AA13"/>
-      <c r="AC13"/>
-      <c r="AE13"/>
-      <c r="AF13" s="5"/>
-    </row>
-    <row r="14" spans="1:33">
+      <c r="Y13"/>
+      <c r="AB13"/>
+      <c r="AD13"/>
+      <c r="AF13"/>
+      <c r="AG13" s="5"/>
+    </row>
+    <row r="14" spans="1:34">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2153,49 +2241,52 @@
       <c r="C14" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" t="s">
+        <v>316</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>40</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>35</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>37</v>
       </c>
-      <c r="J14"/>
-      <c r="K14" s="2">
+      <c r="K14"/>
+      <c r="L14" s="2">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4</v>
       </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
       <c r="N14">
         <v>0</v>
       </c>
-      <c r="O14"/>
-      <c r="P14" s="2">
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14"/>
+      <c r="Q14" s="2">
         <v>6</v>
       </c>
-      <c r="Q14">
+      <c r="R14">
         <v>6</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>8</v>
       </c>
-      <c r="U14"/>
-      <c r="X14"/>
-      <c r="AA14"/>
-      <c r="AC14"/>
-      <c r="AE14"/>
-      <c r="AF14" s="5"/>
-    </row>
-    <row r="15" spans="1:33">
+      <c r="V14"/>
+      <c r="Y14"/>
+      <c r="AB14"/>
+      <c r="AD14"/>
+      <c r="AF14"/>
+      <c r="AG14" s="5"/>
+    </row>
+    <row r="15" spans="1:34">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2205,49 +2296,52 @@
       <c r="C15" t="s">
         <v>70</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" t="s">
+        <v>311</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="E15" t="s">
-        <v>35</v>
       </c>
       <c r="F15" t="s">
         <v>35</v>
       </c>
-      <c r="I15" t="s">
+      <c r="G15" t="s">
+        <v>35</v>
+      </c>
+      <c r="J15" t="s">
         <v>37</v>
       </c>
-      <c r="J15"/>
-      <c r="K15" s="2">
+      <c r="K15"/>
+      <c r="L15" s="2">
         <v>4</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4</v>
       </c>
-      <c r="M15">
-        <v>1</v>
-      </c>
       <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15"/>
-      <c r="P15" s="2">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15"/>
+      <c r="Q15" s="2">
         <v>18</v>
       </c>
-      <c r="Q15">
+      <c r="R15">
         <v>1.4</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1.8</v>
       </c>
-      <c r="U15"/>
-      <c r="X15"/>
-      <c r="AA15"/>
-      <c r="AC15"/>
-      <c r="AE15"/>
-      <c r="AF15" s="5"/>
-    </row>
-    <row r="16" spans="1:33">
+      <c r="V15"/>
+      <c r="Y15"/>
+      <c r="AB15"/>
+      <c r="AD15"/>
+      <c r="AF15"/>
+      <c r="AG15" s="5"/>
+    </row>
+    <row r="16" spans="1:34">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2257,57 +2351,60 @@
       <c r="C16" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" t="s">
+        <v>312</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="E16" t="s">
-        <v>35</v>
       </c>
       <c r="F16" t="s">
         <v>35</v>
       </c>
-      <c r="I16" t="s">
+      <c r="G16" t="s">
+        <v>35</v>
+      </c>
+      <c r="J16" t="s">
         <v>37</v>
       </c>
-      <c r="J16"/>
-      <c r="K16" s="2">
+      <c r="K16"/>
+      <c r="L16" s="2">
         <v>6</v>
       </c>
-      <c r="L16" s="3">
+      <c r="M16" s="3">
         <v>5</v>
       </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
       <c r="N16">
         <v>0</v>
       </c>
-      <c r="O16"/>
-      <c r="P16" s="2">
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16"/>
+      <c r="Q16" s="2">
         <v>6</v>
       </c>
-      <c r="Q16">
+      <c r="R16">
         <v>4</v>
       </c>
-      <c r="R16" s="3">
+      <c r="S16" s="3">
         <v>5</v>
       </c>
-      <c r="S16" s="2">
+      <c r="T16" s="2">
         <v>18</v>
       </c>
-      <c r="T16">
+      <c r="U16">
         <v>0.8</v>
       </c>
-      <c r="U16" s="3">
+      <c r="V16" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="X16"/>
-      <c r="AA16"/>
-      <c r="AC16"/>
-      <c r="AE16"/>
-      <c r="AF16" s="5"/>
-    </row>
-    <row r="17" spans="1:32">
+      <c r="Y16"/>
+      <c r="AB16"/>
+      <c r="AD16"/>
+      <c r="AF16"/>
+      <c r="AG16" s="5"/>
+    </row>
+    <row r="17" spans="1:33">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2315,1076 +2412,1133 @@
         <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>74</v>
-      </c>
-      <c r="D17" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D17" t="s">
+        <v>313</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>40</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>36</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>37</v>
       </c>
-      <c r="J17"/>
-      <c r="K17" s="2">
-        <v>3</v>
-      </c>
-      <c r="L17" s="3">
-        <v>3</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
+      <c r="K17"/>
+      <c r="L17" s="2">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3">
+        <v>3</v>
       </c>
       <c r="N17">
-        <v>1</v>
-      </c>
-      <c r="O17"/>
-      <c r="P17" s="2">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="P17"/>
+      <c r="Q17" s="2">
         <v>19</v>
       </c>
-      <c r="Q17">
-        <v>1</v>
-      </c>
-      <c r="R17" s="3">
-        <v>1</v>
-      </c>
-      <c r="S17" s="2">
-        <v>2</v>
-      </c>
-      <c r="T17">
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="S17" s="3">
+        <v>1</v>
+      </c>
+      <c r="T17" s="2">
+        <v>2</v>
+      </c>
+      <c r="U17">
         <v>4</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6</v>
       </c>
-      <c r="V17" s="2">
+      <c r="W17" s="2">
         <v>21</v>
       </c>
-      <c r="W17">
-        <v>2</v>
-      </c>
-      <c r="X17" s="3">
-        <v>3</v>
-      </c>
-      <c r="AA17"/>
-      <c r="AC17"/>
-      <c r="AE17"/>
-      <c r="AF17" s="6"/>
-    </row>
-    <row r="18" spans="1:32">
+      <c r="X17">
+        <v>2</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB17"/>
+      <c r="AD17"/>
+      <c r="AF17"/>
+      <c r="AG17" s="6"/>
+    </row>
+    <row r="18" spans="1:33">
       <c r="A18">
         <v>18</v>
       </c>
       <c r="B18" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" t="s">
         <v>75</v>
       </c>
-      <c r="C18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>40</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>43</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>37</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>4</v>
       </c>
-      <c r="L18" s="3">
-        <v>3</v>
-      </c>
-      <c r="M18">
-        <v>1</v>
+      <c r="M18" s="3">
+        <v>3</v>
       </c>
       <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="P18" s="2">
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="2">
         <v>15</v>
       </c>
-      <c r="Q18">
+      <c r="R18">
         <v>5</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>7</v>
       </c>
-      <c r="AB18">
+      <c r="AC18">
         <v>61</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1.5</v>
       </c>
-      <c r="AF18" s="5"/>
-    </row>
-    <row r="19" spans="1:32">
+      <c r="AG18" s="5"/>
+    </row>
+    <row r="19" spans="1:33">
       <c r="A19">
         <v>19</v>
       </c>
       <c r="B19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" t="s">
         <v>77</v>
       </c>
-      <c r="C19" t="s">
-        <v>78</v>
-      </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" t="s">
+        <v>77</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>40</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>54</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>37</v>
       </c>
-      <c r="J19"/>
-      <c r="K19" s="2">
+      <c r="K19"/>
+      <c r="L19" s="2">
         <v>5</v>
       </c>
-      <c r="L19" s="3">
+      <c r="M19" s="3">
         <v>4</v>
       </c>
-      <c r="M19">
-        <v>1</v>
-      </c>
       <c r="N19">
         <v>1</v>
       </c>
-      <c r="O19"/>
-      <c r="P19" s="2">
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19"/>
+      <c r="Q19" s="2">
         <v>23</v>
       </c>
-      <c r="Q19">
-        <v>1</v>
-      </c>
-      <c r="R19" s="3">
-        <v>1</v>
-      </c>
-      <c r="S19" s="2">
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="S19" s="3">
+        <v>1</v>
+      </c>
+      <c r="T19" s="2">
         <v>7</v>
       </c>
-      <c r="T19">
-        <v>1</v>
-      </c>
-      <c r="U19" s="3">
-        <v>2</v>
-      </c>
-      <c r="X19"/>
-      <c r="AA19"/>
-      <c r="AC19"/>
-      <c r="AE19"/>
-      <c r="AF19" s="5"/>
-    </row>
-    <row r="20" spans="1:32">
+      <c r="U19">
+        <v>1</v>
+      </c>
+      <c r="V19" s="3">
+        <v>2</v>
+      </c>
+      <c r="Y19"/>
+      <c r="AB19"/>
+      <c r="AD19"/>
+      <c r="AF19"/>
+      <c r="AG19" s="5"/>
+    </row>
+    <row r="20" spans="1:33">
       <c r="A20">
         <v>20</v>
       </c>
       <c r="B20" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" t="s">
         <v>79</v>
       </c>
-      <c r="C20" t="s">
-        <v>80</v>
-      </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>35</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>43</v>
       </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
         <v>37</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>6</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>6</v>
       </c>
-      <c r="M20">
-        <v>1</v>
-      </c>
       <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="2">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="2">
         <v>11</v>
       </c>
-      <c r="Q20">
+      <c r="R20">
         <v>24</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>30</v>
       </c>
-      <c r="AB20">
+      <c r="AC20">
         <v>62</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>7</v>
       </c>
-      <c r="AF20" s="6"/>
-    </row>
-    <row r="21" spans="1:32">
+      <c r="AG20" s="6"/>
+    </row>
+    <row r="21" spans="1:33">
       <c r="A21">
         <v>21</v>
       </c>
       <c r="B21" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" t="s">
         <v>81</v>
       </c>
-      <c r="C21" t="s">
-        <v>82</v>
-      </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>35</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>43</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>37</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>5</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4</v>
       </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
       <c r="N21">
-        <v>1</v>
-      </c>
-      <c r="P21" s="2">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="2">
         <v>26</v>
       </c>
-      <c r="Q21">
-        <v>2</v>
-      </c>
-      <c r="R21" s="3">
-        <v>2</v>
-      </c>
-      <c r="S21" s="2">
+      <c r="R21">
+        <v>2</v>
+      </c>
+      <c r="S21" s="3">
+        <v>2</v>
+      </c>
+      <c r="T21" s="2">
         <v>11</v>
       </c>
-      <c r="T21">
+      <c r="U21">
         <v>30</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>42</v>
       </c>
-      <c r="V21">
-        <v>2</v>
-      </c>
       <c r="W21">
+        <v>2</v>
+      </c>
+      <c r="X21">
         <v>5</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>7</v>
       </c>
-      <c r="AF21" s="5"/>
-    </row>
-    <row r="22" spans="1:32">
+      <c r="AG21" s="5"/>
+    </row>
+    <row r="22" spans="1:33">
       <c r="A22">
         <v>22</v>
       </c>
       <c r="B22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" t="s">
         <v>83</v>
       </c>
-      <c r="C22" t="s">
-        <v>84</v>
-      </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>40</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>35</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>37</v>
       </c>
-      <c r="J22"/>
-      <c r="K22" s="2">
+      <c r="K22"/>
+      <c r="L22" s="2">
         <v>4</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>4</v>
       </c>
-      <c r="M22">
-        <v>1</v>
-      </c>
       <c r="N22">
         <v>1</v>
       </c>
-      <c r="O22"/>
-      <c r="P22" s="2">
+      <c r="O22">
+        <v>1</v>
+      </c>
+      <c r="P22"/>
+      <c r="Q22" s="2">
         <v>6</v>
       </c>
-      <c r="Q22">
-        <v>2</v>
-      </c>
-      <c r="R22" s="3">
+      <c r="R22">
+        <v>2</v>
+      </c>
+      <c r="S22" s="3">
         <v>4</v>
       </c>
-      <c r="S22" s="2">
+      <c r="T22" s="2">
         <v>28</v>
       </c>
-      <c r="T22">
-        <v>1</v>
-      </c>
-      <c r="U22" s="3">
-        <v>1</v>
-      </c>
-      <c r="X22"/>
-      <c r="AA22"/>
-      <c r="AC22"/>
-      <c r="AE22"/>
-      <c r="AF22" s="5"/>
-    </row>
-    <row r="23" spans="1:32">
+      <c r="U22">
+        <v>1</v>
+      </c>
+      <c r="V22" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y22"/>
+      <c r="AB22"/>
+      <c r="AD22"/>
+      <c r="AF22"/>
+      <c r="AG22" s="5"/>
+    </row>
+    <row r="23" spans="1:33">
       <c r="A23">
         <v>23</v>
       </c>
       <c r="B23" t="s">
+        <v>84</v>
+      </c>
+      <c r="C23" t="s">
         <v>85</v>
       </c>
-      <c r="C23" t="s">
-        <v>86</v>
-      </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" t="s">
+        <v>85</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>40</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>35</v>
       </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>37</v>
       </c>
-      <c r="J23"/>
-      <c r="K23" s="2">
-        <v>1</v>
-      </c>
-      <c r="L23" s="3">
-        <v>1</v>
-      </c>
-      <c r="M23">
+      <c r="K23"/>
+      <c r="L23" s="2">
+        <v>1</v>
+      </c>
+      <c r="M23" s="3">
         <v>1</v>
       </c>
       <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23"/>
-      <c r="P23" s="2">
+        <v>1</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23"/>
+      <c r="Q23" s="2">
         <v>6</v>
       </c>
-      <c r="Q23">
+      <c r="R23">
         <v>5</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7</v>
       </c>
-      <c r="S23" s="2">
-        <v>2</v>
-      </c>
-      <c r="T23">
-        <v>1</v>
-      </c>
-      <c r="U23" s="3">
-        <v>1</v>
-      </c>
-      <c r="X23"/>
-      <c r="AA23"/>
-      <c r="AC23"/>
-      <c r="AE23"/>
-      <c r="AF23" s="5"/>
-    </row>
-    <row r="24" spans="1:32">
+      <c r="T23" s="2">
+        <v>2</v>
+      </c>
+      <c r="U23">
+        <v>1</v>
+      </c>
+      <c r="V23" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y23"/>
+      <c r="AB23"/>
+      <c r="AD23"/>
+      <c r="AF23"/>
+      <c r="AG23" s="5"/>
+    </row>
+    <row r="24" spans="1:33">
       <c r="A24">
         <v>24</v>
       </c>
       <c r="B24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" t="s">
         <v>87</v>
       </c>
-      <c r="C24" t="s">
-        <v>88</v>
-      </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" t="s">
+        <v>87</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>35</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>43</v>
       </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>37</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>4</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4</v>
       </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
       <c r="N24">
         <v>0</v>
       </c>
-      <c r="P24" s="2">
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="2">
         <v>15</v>
       </c>
-      <c r="Q24">
-        <v>3</v>
-      </c>
-      <c r="R24" s="3">
+      <c r="R24">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3">
         <v>4</v>
       </c>
-      <c r="S24" s="2">
+      <c r="T24" s="2">
         <v>11</v>
       </c>
-      <c r="T24">
+      <c r="U24">
         <v>8</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>11</v>
       </c>
-      <c r="AB24">
+      <c r="AC24">
         <v>63</v>
       </c>
-      <c r="AC24" s="3">
-        <v>3</v>
-      </c>
-      <c r="AF24" s="5"/>
-    </row>
-    <row r="25" spans="1:32">
+      <c r="AD24" s="3">
+        <v>3</v>
+      </c>
+      <c r="AG24" s="5"/>
+    </row>
+    <row r="25" spans="1:33">
       <c r="A25">
         <v>25</v>
       </c>
       <c r="B25" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" t="s">
         <v>89</v>
       </c>
-      <c r="C25" t="s">
-        <v>90</v>
-      </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>40</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>54</v>
       </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>37</v>
       </c>
-      <c r="J25"/>
-      <c r="K25" s="2">
-        <v>3</v>
-      </c>
-      <c r="L25" s="3">
-        <v>2</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
+      <c r="K25"/>
+      <c r="L25" s="2">
+        <v>3</v>
+      </c>
+      <c r="M25" s="3">
+        <v>2</v>
       </c>
       <c r="N25">
         <v>0</v>
       </c>
-      <c r="O25"/>
-      <c r="P25" s="2">
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25"/>
+      <c r="Q25" s="2">
         <v>7</v>
       </c>
-      <c r="Q25">
-        <v>3</v>
-      </c>
-      <c r="R25" s="3">
+      <c r="R25">
+        <v>3</v>
+      </c>
+      <c r="S25" s="3">
         <v>5</v>
       </c>
-      <c r="U25"/>
-      <c r="X25"/>
-      <c r="AA25"/>
-      <c r="AC25"/>
-      <c r="AE25"/>
-      <c r="AF25" s="5"/>
-    </row>
-    <row r="26" spans="1:32">
+      <c r="V25"/>
+      <c r="Y25"/>
+      <c r="AB25"/>
+      <c r="AD25"/>
+      <c r="AF25"/>
+      <c r="AG25" s="5"/>
+    </row>
+    <row r="26" spans="1:33">
       <c r="A26">
         <v>26</v>
       </c>
       <c r="B26" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" t="s">
         <v>91</v>
       </c>
-      <c r="C26" t="s">
-        <v>92</v>
-      </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>40</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>54</v>
       </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>37</v>
       </c>
-      <c r="J26"/>
-      <c r="K26" s="2">
-        <v>3</v>
-      </c>
-      <c r="L26" s="3">
-        <v>2</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
+      <c r="K26"/>
+      <c r="L26" s="2">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3">
+        <v>2</v>
       </c>
       <c r="N26">
         <v>0</v>
       </c>
-      <c r="O26"/>
-      <c r="P26" s="2">
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26"/>
+      <c r="Q26" s="2">
         <v>7</v>
       </c>
-      <c r="Q26">
-        <v>3</v>
-      </c>
-      <c r="R26" s="3">
+      <c r="R26">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3">
         <v>4</v>
       </c>
-      <c r="S26" s="2">
-        <v>2</v>
-      </c>
-      <c r="T26">
+      <c r="T26" s="2">
+        <v>2</v>
+      </c>
+      <c r="U26">
         <v>4</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>6</v>
       </c>
-      <c r="X26"/>
-      <c r="AA26"/>
-      <c r="AC26"/>
-      <c r="AE26"/>
-      <c r="AF26" s="5"/>
-    </row>
-    <row r="27" spans="1:32">
+      <c r="Y26"/>
+      <c r="AB26"/>
+      <c r="AD26"/>
+      <c r="AF26"/>
+      <c r="AG26" s="5"/>
+    </row>
+    <row r="27" spans="1:33">
       <c r="A27">
         <v>27</v>
       </c>
       <c r="B27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" t="s">
         <v>93</v>
       </c>
-      <c r="C27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" t="s">
+        <v>93</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>35</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>43</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
         <v>37</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <v>8</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6</v>
       </c>
-      <c r="M27">
-        <v>1</v>
-      </c>
       <c r="N27">
         <v>1</v>
       </c>
-      <c r="O27" s="3">
-        <v>0</v>
-      </c>
-      <c r="P27" s="2">
+      <c r="O27">
+        <v>1</v>
+      </c>
+      <c r="P27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2">
         <v>11</v>
       </c>
-      <c r="Q27">
+      <c r="R27">
         <v>12</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>18</v>
       </c>
-      <c r="S27" s="2">
+      <c r="T27" s="2">
         <v>56</v>
       </c>
-      <c r="T27">
+      <c r="U27">
         <v>24</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>30</v>
       </c>
-      <c r="V27">
+      <c r="W27">
         <v>57</v>
       </c>
-      <c r="W27">
+      <c r="X27">
         <v>36</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>44</v>
       </c>
-      <c r="AF27" s="6"/>
-    </row>
-    <row r="28" spans="1:32">
+      <c r="AG27" s="6"/>
+    </row>
+    <row r="28" spans="1:33">
       <c r="A28">
         <v>28</v>
       </c>
       <c r="B28" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" t="s">
         <v>95</v>
       </c>
-      <c r="C28" t="s">
-        <v>96</v>
-      </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" t="s">
+        <v>95</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>40</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>43</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
         <v>37</v>
       </c>
-      <c r="K28">
-        <v>1</v>
-      </c>
-      <c r="L28" s="3">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>1</v>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
       </c>
       <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="P28" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q28">
+        <v>1</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="2">
+        <v>2</v>
+      </c>
+      <c r="R28">
         <v>6</v>
       </c>
-      <c r="R28" s="3">
+      <c r="S28" s="3">
         <v>8</v>
       </c>
-      <c r="AB28">
+      <c r="AC28">
         <v>21</v>
       </c>
-      <c r="AC28" s="3">
+      <c r="AD28" s="3">
         <v>12</v>
       </c>
-      <c r="AF28" s="5"/>
-    </row>
-    <row r="29" spans="1:32">
+      <c r="AG28" s="5"/>
+    </row>
+    <row r="29" spans="1:33">
       <c r="A29">
         <v>30</v>
       </c>
       <c r="B29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29" t="s">
         <v>97</v>
       </c>
-      <c r="C29" t="s">
-        <v>98</v>
-      </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" t="s">
+        <v>97</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>40</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>36</v>
       </c>
-      <c r="I29" t="s">
+      <c r="J29" t="s">
         <v>37</v>
       </c>
-      <c r="J29"/>
-      <c r="K29" s="2">
+      <c r="K29"/>
+      <c r="L29" s="2">
         <v>5</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>5</v>
       </c>
-      <c r="M29">
-        <v>1</v>
-      </c>
       <c r="N29">
         <v>1</v>
       </c>
-      <c r="O29"/>
-      <c r="P29" s="2">
+      <c r="O29">
+        <v>1</v>
+      </c>
+      <c r="P29"/>
+      <c r="Q29" s="2">
         <v>32</v>
       </c>
-      <c r="Q29">
+      <c r="R29">
         <v>30</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>30</v>
       </c>
-      <c r="S29" s="2">
-        <v>2</v>
-      </c>
-      <c r="T29">
-        <v>3</v>
-      </c>
-      <c r="U29" s="3">
+      <c r="T29" s="2">
+        <v>2</v>
+      </c>
+      <c r="U29">
+        <v>3</v>
+      </c>
+      <c r="V29" s="3">
         <v>5</v>
       </c>
-      <c r="V29" s="2">
+      <c r="W29" s="2">
         <v>21</v>
       </c>
-      <c r="W29">
-        <v>2</v>
-      </c>
-      <c r="X29" s="3">
-        <v>3</v>
-      </c>
-      <c r="AA29"/>
-      <c r="AC29"/>
-      <c r="AE29"/>
-      <c r="AF29" s="5"/>
-    </row>
-    <row r="30" spans="1:32">
+      <c r="X29">
+        <v>2</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB29"/>
+      <c r="AD29"/>
+      <c r="AF29"/>
+      <c r="AG29" s="5"/>
+    </row>
+    <row r="30" spans="1:33">
       <c r="A30">
         <v>31</v>
       </c>
       <c r="B30" t="s">
+        <v>98</v>
+      </c>
+      <c r="C30" t="s">
         <v>99</v>
       </c>
-      <c r="C30" t="s">
-        <v>100</v>
-      </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" t="s">
+        <v>99</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>40</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>36</v>
       </c>
-      <c r="I30" t="s">
+      <c r="J30" t="s">
         <v>37</v>
       </c>
-      <c r="J30"/>
-      <c r="K30" s="2">
+      <c r="K30"/>
+      <c r="L30" s="2">
         <v>4</v>
       </c>
-      <c r="L30" s="3">
+      <c r="M30" s="3">
         <v>4</v>
       </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
       <c r="N30">
-        <v>1</v>
-      </c>
-      <c r="O30"/>
-      <c r="P30" s="2">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>1</v>
+      </c>
+      <c r="P30"/>
+      <c r="Q30" s="2">
         <v>33</v>
       </c>
-      <c r="Q30">
+      <c r="R30">
         <v>50</v>
       </c>
-      <c r="R30" s="3">
+      <c r="S30" s="3">
         <v>70</v>
       </c>
-      <c r="S30" s="2">
-        <v>2</v>
-      </c>
-      <c r="T30">
-        <v>2</v>
-      </c>
-      <c r="U30" s="3">
+      <c r="T30" s="2">
+        <v>2</v>
+      </c>
+      <c r="U30">
+        <v>2</v>
+      </c>
+      <c r="V30" s="3">
         <v>4</v>
       </c>
-      <c r="X30"/>
-      <c r="AA30"/>
-      <c r="AC30"/>
-      <c r="AE30"/>
-      <c r="AF30" s="6"/>
-    </row>
-    <row r="31" spans="1:32">
+      <c r="Y30"/>
+      <c r="AB30"/>
+      <c r="AD30"/>
+      <c r="AF30"/>
+      <c r="AG30" s="6"/>
+    </row>
+    <row r="31" spans="1:33">
       <c r="A31">
         <v>32</v>
       </c>
       <c r="B31" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" t="s">
         <v>101</v>
       </c>
-      <c r="C31" t="s">
-        <v>102</v>
-      </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" t="s">
+        <v>101</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>40</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>36</v>
       </c>
-      <c r="I31" t="s">
+      <c r="J31" t="s">
         <v>37</v>
       </c>
-      <c r="J31"/>
-      <c r="K31" s="2">
+      <c r="K31"/>
+      <c r="L31" s="2">
         <v>4</v>
       </c>
-      <c r="L31" s="3">
-        <v>3</v>
-      </c>
-      <c r="M31">
-        <v>1</v>
+      <c r="M31" s="3">
+        <v>3</v>
       </c>
       <c r="N31">
         <v>1</v>
       </c>
-      <c r="O31"/>
-      <c r="P31" s="2">
+      <c r="O31">
+        <v>1</v>
+      </c>
+      <c r="P31"/>
+      <c r="Q31" s="2">
         <v>33</v>
       </c>
-      <c r="Q31">
+      <c r="R31">
         <v>20</v>
       </c>
-      <c r="R31" s="3">
+      <c r="S31" s="3">
         <v>30</v>
       </c>
-      <c r="S31" s="2">
+      <c r="T31" s="2">
         <v>35</v>
       </c>
-      <c r="T31">
-        <v>1</v>
-      </c>
-      <c r="U31" s="3">
-        <v>1</v>
-      </c>
-      <c r="X31"/>
-      <c r="AA31"/>
-      <c r="AC31"/>
-      <c r="AE31"/>
-      <c r="AF31" s="6"/>
-    </row>
-    <row r="32" spans="1:32">
+      <c r="U31">
+        <v>1</v>
+      </c>
+      <c r="V31" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y31"/>
+      <c r="AB31"/>
+      <c r="AD31"/>
+      <c r="AF31"/>
+      <c r="AG31" s="6"/>
+    </row>
+    <row r="32" spans="1:33">
       <c r="A32">
         <v>33</v>
       </c>
       <c r="B32" t="s">
+        <v>102</v>
+      </c>
+      <c r="C32" t="s">
         <v>103</v>
       </c>
-      <c r="C32" t="s">
-        <v>104</v>
-      </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" t="s">
+        <v>103</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>40</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>36</v>
       </c>
-      <c r="I32" t="s">
+      <c r="J32" t="s">
         <v>37</v>
       </c>
-      <c r="J32"/>
-      <c r="K32" s="2">
+      <c r="K32"/>
+      <c r="L32" s="2">
         <v>7</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>6</v>
       </c>
-      <c r="M32">
-        <v>1</v>
-      </c>
       <c r="N32">
         <v>1</v>
       </c>
-      <c r="O32"/>
-      <c r="R32"/>
-      <c r="U32"/>
-      <c r="X32"/>
-      <c r="AA32"/>
-      <c r="AC32"/>
-      <c r="AE32"/>
-    </row>
-    <row r="33" spans="1:31">
+      <c r="O32">
+        <v>1</v>
+      </c>
+      <c r="P32"/>
+      <c r="S32"/>
+      <c r="V32"/>
+      <c r="Y32"/>
+      <c r="AB32"/>
+      <c r="AD32"/>
+      <c r="AF32"/>
+    </row>
+    <row r="33" spans="1:32">
       <c r="A33">
         <v>34</v>
       </c>
       <c r="B33" t="s">
+        <v>104</v>
+      </c>
+      <c r="C33" t="s">
         <v>105</v>
       </c>
-      <c r="C33" t="s">
-        <v>106</v>
-      </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" t="s">
+        <v>105</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>35</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>43</v>
       </c>
-      <c r="I33" t="s">
+      <c r="J33" t="s">
         <v>37</v>
       </c>
-      <c r="K33">
+      <c r="L33">
         <v>8</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7</v>
       </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
       <c r="N33">
-        <v>1</v>
-      </c>
-      <c r="P33" s="2">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="2">
         <v>11</v>
       </c>
-      <c r="Q33">
+      <c r="R33">
         <v>38</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>52</v>
       </c>
-      <c r="AB33">
+      <c r="AC33">
         <v>64</v>
       </c>
-      <c r="AC33" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:31">
+      <c r="AD33" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:32">
       <c r="A34">
         <v>35</v>
       </c>
       <c r="B34" t="s">
+        <v>106</v>
+      </c>
+      <c r="C34" t="s">
         <v>107</v>
       </c>
-      <c r="C34" t="s">
-        <v>108</v>
-      </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" t="s">
+        <v>107</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>40</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>43</v>
       </c>
-      <c r="I34" t="s">
+      <c r="J34" t="s">
         <v>37</v>
       </c>
-      <c r="K34">
-        <v>3</v>
-      </c>
-      <c r="L34" s="3">
-        <v>3</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
+      <c r="L34">
+        <v>3</v>
+      </c>
+      <c r="M34" s="3">
+        <v>3</v>
       </c>
       <c r="N34">
         <v>0</v>
       </c>
-      <c r="O34" s="3">
-        <v>0</v>
-      </c>
-      <c r="P34" s="2">
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="2">
         <v>15</v>
       </c>
-      <c r="Q34">
-        <v>3</v>
-      </c>
-      <c r="R34" s="3">
+      <c r="R34">
+        <v>3</v>
+      </c>
+      <c r="S34" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:31">
+    <row r="35" spans="1:32">
       <c r="A35">
         <v>36</v>
       </c>
       <c r="B35" t="s">
+        <v>108</v>
+      </c>
+      <c r="C35" t="s">
         <v>109</v>
       </c>
-      <c r="C35" t="s">
-        <v>110</v>
-      </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" t="s">
+        <v>109</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>35</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>43</v>
       </c>
-      <c r="I35" t="s">
+      <c r="J35" t="s">
         <v>37</v>
       </c>
-      <c r="K35">
-        <v>3</v>
-      </c>
-      <c r="L35" s="3">
-        <v>3</v>
-      </c>
-      <c r="M35">
-        <v>1</v>
+      <c r="L35">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3">
+        <v>3</v>
       </c>
       <c r="N35">
-        <v>0</v>
-      </c>
-      <c r="P35" s="2">
+        <v>1</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="2">
         <v>11</v>
       </c>
-      <c r="Q35">
+      <c r="R35">
         <v>18</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:31">
+    <row r="36" spans="1:32">
       <c r="A36">
         <v>37</v>
       </c>
@@ -3392,711 +3546,747 @@
         <v>144</v>
       </c>
       <c r="C36" t="s">
-        <v>111</v>
-      </c>
-      <c r="D36" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D36" t="s">
+        <v>110</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>40</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>43</v>
       </c>
-      <c r="I36" t="s">
+      <c r="J36" t="s">
         <v>37</v>
       </c>
-      <c r="K36">
-        <v>3</v>
-      </c>
-      <c r="L36" s="3">
-        <v>3</v>
-      </c>
-      <c r="M36">
-        <v>1</v>
+      <c r="L36">
+        <v>3</v>
+      </c>
+      <c r="M36" s="3">
+        <v>3</v>
       </c>
       <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="P36" s="2">
+        <v>1</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="2">
         <v>15</v>
       </c>
-      <c r="Q36">
-        <v>3</v>
-      </c>
-      <c r="R36" s="3">
+      <c r="R36">
+        <v>3</v>
+      </c>
+      <c r="S36" s="3">
         <v>4</v>
       </c>
-      <c r="S36" s="2">
-        <v>2</v>
-      </c>
-      <c r="T36">
+      <c r="T36" s="2">
+        <v>2</v>
+      </c>
+      <c r="U36">
         <v>6</v>
       </c>
-      <c r="U36" s="3">
+      <c r="V36" s="3">
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:31">
+    <row r="37" spans="1:32">
       <c r="A37">
         <v>38</v>
       </c>
       <c r="B37" t="s">
+        <v>111</v>
+      </c>
+      <c r="C37" t="s">
         <v>112</v>
       </c>
-      <c r="C37" t="s">
-        <v>113</v>
-      </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" t="s">
+        <v>112</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>40</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>54</v>
       </c>
-      <c r="I37" t="s">
+      <c r="J37" t="s">
         <v>37</v>
       </c>
-      <c r="J37"/>
-      <c r="K37" s="2">
-        <v>3</v>
-      </c>
-      <c r="L37" s="3">
-        <v>3</v>
-      </c>
-      <c r="M37">
-        <v>1</v>
+      <c r="K37"/>
+      <c r="L37" s="2">
+        <v>3</v>
+      </c>
+      <c r="M37" s="3">
+        <v>3</v>
       </c>
       <c r="N37">
-        <v>0</v>
-      </c>
-      <c r="O37"/>
-      <c r="P37" s="2">
+        <v>1</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37"/>
+      <c r="Q37" s="2">
         <v>7</v>
       </c>
-      <c r="Q37">
-        <v>3</v>
-      </c>
-      <c r="R37" s="3">
+      <c r="R37">
+        <v>3</v>
+      </c>
+      <c r="S37" s="3">
         <v>4</v>
       </c>
-      <c r="S37" s="2">
-        <v>2</v>
-      </c>
-      <c r="T37">
+      <c r="T37" s="2">
+        <v>2</v>
+      </c>
+      <c r="U37">
         <v>6</v>
       </c>
-      <c r="U37" s="3">
+      <c r="V37" s="3">
         <v>8</v>
       </c>
-      <c r="X37"/>
-      <c r="AA37"/>
-      <c r="AC37"/>
-      <c r="AE37"/>
-    </row>
-    <row r="38" spans="1:31">
+      <c r="Y37"/>
+      <c r="AB37"/>
+      <c r="AD37"/>
+      <c r="AF37"/>
+    </row>
+    <row r="38" spans="1:32">
       <c r="A38">
         <v>39</v>
       </c>
       <c r="B38" t="s">
+        <v>113</v>
+      </c>
+      <c r="C38" t="s">
         <v>114</v>
       </c>
-      <c r="C38" t="s">
-        <v>115</v>
-      </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" t="s">
+        <v>114</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>40</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>36</v>
       </c>
-      <c r="I38" t="s">
+      <c r="J38" t="s">
         <v>37</v>
       </c>
-      <c r="J38"/>
-      <c r="K38" s="2">
-        <v>1</v>
-      </c>
-      <c r="L38" s="3">
-        <v>1</v>
-      </c>
-      <c r="M38">
+      <c r="K38"/>
+      <c r="L38" s="2">
+        <v>1</v>
+      </c>
+      <c r="M38" s="3">
         <v>1</v>
       </c>
       <c r="N38">
         <v>1</v>
       </c>
-      <c r="O38"/>
-      <c r="P38" s="2">
+      <c r="O38">
+        <v>1</v>
+      </c>
+      <c r="P38"/>
+      <c r="Q38" s="2">
         <v>21</v>
       </c>
-      <c r="Q38">
+      <c r="R38">
         <v>4</v>
       </c>
-      <c r="R38" s="3">
+      <c r="S38" s="3">
         <v>5</v>
       </c>
-      <c r="S38" s="2">
-        <v>2</v>
-      </c>
-      <c r="T38">
-        <v>3</v>
-      </c>
-      <c r="U38" s="3">
+      <c r="T38" s="2">
+        <v>2</v>
+      </c>
+      <c r="U38">
+        <v>3</v>
+      </c>
+      <c r="V38" s="3">
         <v>5</v>
       </c>
-      <c r="X38"/>
-      <c r="AA38"/>
-      <c r="AC38"/>
-      <c r="AE38"/>
-    </row>
-    <row r="39" spans="1:31">
+      <c r="Y38"/>
+      <c r="AB38"/>
+      <c r="AD38"/>
+      <c r="AF38"/>
+    </row>
+    <row r="39" spans="1:32">
       <c r="A39">
         <v>40</v>
       </c>
       <c r="B39" t="s">
+        <v>115</v>
+      </c>
+      <c r="C39" t="s">
         <v>116</v>
       </c>
-      <c r="C39" t="s">
-        <v>117</v>
-      </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" t="s">
+        <v>116</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>40</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>36</v>
       </c>
-      <c r="I39" t="s">
+      <c r="J39" t="s">
         <v>37</v>
       </c>
-      <c r="J39"/>
-      <c r="K39" s="2">
-        <v>1</v>
-      </c>
-      <c r="L39" s="3">
-        <v>1</v>
-      </c>
-      <c r="M39">
+      <c r="K39"/>
+      <c r="L39" s="2">
+        <v>1</v>
+      </c>
+      <c r="M39" s="3">
         <v>1</v>
       </c>
       <c r="N39">
         <v>1</v>
       </c>
-      <c r="O39"/>
-      <c r="P39" s="2">
+      <c r="O39">
+        <v>1</v>
+      </c>
+      <c r="P39"/>
+      <c r="Q39" s="2">
         <v>5</v>
       </c>
-      <c r="Q39">
-        <v>1</v>
-      </c>
-      <c r="R39" s="3">
-        <v>2</v>
-      </c>
-      <c r="S39" s="2">
-        <v>2</v>
-      </c>
-      <c r="T39">
+      <c r="R39">
+        <v>1</v>
+      </c>
+      <c r="S39" s="3">
+        <v>2</v>
+      </c>
+      <c r="T39" s="2">
+        <v>2</v>
+      </c>
+      <c r="U39">
         <v>6</v>
       </c>
-      <c r="U39" s="3">
+      <c r="V39" s="3">
         <v>7</v>
       </c>
-      <c r="X39"/>
-      <c r="AA39"/>
-      <c r="AC39"/>
-      <c r="AE39"/>
-    </row>
-    <row r="40" spans="1:31">
+      <c r="Y39"/>
+      <c r="AB39"/>
+      <c r="AD39"/>
+      <c r="AF39"/>
+    </row>
+    <row r="40" spans="1:32">
       <c r="A40">
         <v>41</v>
       </c>
       <c r="B40" t="s">
+        <v>117</v>
+      </c>
+      <c r="C40" t="s">
         <v>118</v>
       </c>
-      <c r="C40" t="s">
-        <v>119</v>
-      </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" t="s">
+        <v>118</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>40</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>54</v>
       </c>
-      <c r="I40" t="s">
+      <c r="J40" t="s">
         <v>37</v>
       </c>
-      <c r="J40"/>
-      <c r="K40" s="2">
+      <c r="K40"/>
+      <c r="L40" s="2">
         <v>4</v>
       </c>
-      <c r="L40" s="3">
-        <v>3</v>
-      </c>
-      <c r="M40">
-        <v>1</v>
+      <c r="M40" s="3">
+        <v>3</v>
       </c>
       <c r="N40">
         <v>1</v>
       </c>
-      <c r="O40"/>
-      <c r="P40" s="2">
+      <c r="O40">
+        <v>1</v>
+      </c>
+      <c r="P40"/>
+      <c r="Q40" s="2">
         <v>7</v>
       </c>
-      <c r="Q40">
+      <c r="R40">
         <v>4</v>
       </c>
-      <c r="R40" s="3">
+      <c r="S40" s="3">
         <v>5</v>
       </c>
-      <c r="S40" s="2">
+      <c r="T40" s="2">
         <v>38</v>
       </c>
-      <c r="T40">
+      <c r="U40">
         <v>4</v>
       </c>
-      <c r="U40" s="3">
+      <c r="V40" s="3">
         <v>5</v>
       </c>
-      <c r="X40"/>
-      <c r="AA40"/>
-      <c r="AC40"/>
-      <c r="AE40"/>
-    </row>
-    <row r="41" spans="1:31">
+      <c r="Y40"/>
+      <c r="AB40"/>
+      <c r="AD40"/>
+      <c r="AF40"/>
+    </row>
+    <row r="41" spans="1:32">
       <c r="A41">
         <v>42</v>
       </c>
       <c r="B41" t="s">
+        <v>119</v>
+      </c>
+      <c r="C41" t="s">
         <v>120</v>
       </c>
-      <c r="C41" t="s">
-        <v>121</v>
-      </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" t="s">
+        <v>120</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>40</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>35</v>
       </c>
-      <c r="I41" t="s">
+      <c r="J41" t="s">
         <v>37</v>
       </c>
-      <c r="J41"/>
-      <c r="K41" s="2">
-        <v>2</v>
-      </c>
-      <c r="L41" s="3">
-        <v>2</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
+      <c r="K41"/>
+      <c r="L41" s="2">
+        <v>2</v>
+      </c>
+      <c r="M41" s="3">
+        <v>2</v>
       </c>
       <c r="N41">
         <v>0</v>
       </c>
-      <c r="O41"/>
-      <c r="P41" s="2">
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41"/>
+      <c r="Q41" s="2">
         <v>6</v>
       </c>
-      <c r="Q41">
-        <v>3</v>
-      </c>
-      <c r="R41" s="3">
-        <v>3</v>
-      </c>
-      <c r="S41" s="2">
+      <c r="R41">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3">
+        <v>3</v>
+      </c>
+      <c r="T41" s="2">
         <v>39</v>
       </c>
-      <c r="T41">
-        <v>2</v>
-      </c>
-      <c r="U41" s="3">
-        <v>3</v>
-      </c>
-      <c r="X41"/>
-      <c r="AA41"/>
-      <c r="AC41"/>
-      <c r="AE41"/>
-    </row>
-    <row r="42" spans="1:31">
+      <c r="U41">
+        <v>2</v>
+      </c>
+      <c r="V41" s="3">
+        <v>3</v>
+      </c>
+      <c r="Y41"/>
+      <c r="AB41"/>
+      <c r="AD41"/>
+      <c r="AF41"/>
+    </row>
+    <row r="42" spans="1:32">
       <c r="A42">
         <v>43</v>
       </c>
       <c r="B42" t="s">
+        <v>121</v>
+      </c>
+      <c r="C42" t="s">
         <v>122</v>
       </c>
-      <c r="C42" t="s">
-        <v>123</v>
-      </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" t="s">
+        <v>122</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>40</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>54</v>
       </c>
-      <c r="I42" t="s">
+      <c r="J42" t="s">
         <v>37</v>
       </c>
-      <c r="J42"/>
-      <c r="K42" s="2">
+      <c r="K42"/>
+      <c r="L42" s="2">
         <v>4</v>
       </c>
-      <c r="L42" s="3">
-        <v>3</v>
-      </c>
-      <c r="M42">
-        <v>1</v>
+      <c r="M42" s="3">
+        <v>3</v>
       </c>
       <c r="N42">
         <v>1</v>
       </c>
-      <c r="O42"/>
-      <c r="P42" s="2">
+      <c r="O42">
+        <v>1</v>
+      </c>
+      <c r="P42"/>
+      <c r="Q42" s="2">
         <v>7</v>
       </c>
-      <c r="Q42">
-        <v>1</v>
-      </c>
-      <c r="R42" s="3">
-        <v>3</v>
-      </c>
-      <c r="S42" s="2">
+      <c r="R42">
+        <v>1</v>
+      </c>
+      <c r="S42" s="3">
+        <v>3</v>
+      </c>
+      <c r="T42" s="2">
         <v>41</v>
       </c>
-      <c r="T42">
-        <v>1</v>
-      </c>
-      <c r="U42" s="3">
-        <v>1</v>
-      </c>
-      <c r="X42"/>
-      <c r="AA42"/>
-      <c r="AC42"/>
-      <c r="AE42"/>
-    </row>
-    <row r="43" spans="1:31">
+      <c r="U42">
+        <v>1</v>
+      </c>
+      <c r="V42" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y42"/>
+      <c r="AB42"/>
+      <c r="AD42"/>
+      <c r="AF42"/>
+    </row>
+    <row r="43" spans="1:32">
       <c r="A43">
         <v>44</v>
       </c>
       <c r="B43" t="s">
+        <v>123</v>
+      </c>
+      <c r="C43" t="s">
         <v>124</v>
       </c>
-      <c r="C43" t="s">
-        <v>125</v>
-      </c>
-      <c r="D43" s="2" t="s">
+      <c r="D43" t="s">
+        <v>124</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="E43" t="s">
-        <v>35</v>
       </c>
       <c r="F43" t="s">
         <v>35</v>
       </c>
-      <c r="I43" t="s">
+      <c r="G43" t="s">
+        <v>35</v>
+      </c>
+      <c r="J43" t="s">
         <v>37</v>
       </c>
-      <c r="J43"/>
-      <c r="K43" s="2">
+      <c r="K43"/>
+      <c r="L43" s="2">
         <v>7</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4</v>
       </c>
-      <c r="M43">
-        <v>0</v>
-      </c>
       <c r="N43">
-        <v>1</v>
-      </c>
-      <c r="O43"/>
-      <c r="P43" s="2">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>1</v>
+      </c>
+      <c r="P43"/>
+      <c r="Q43" s="2">
         <v>6</v>
       </c>
-      <c r="Q43">
+      <c r="R43">
         <v>5</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5</v>
       </c>
-      <c r="S43" s="2">
+      <c r="T43" s="2">
         <v>14</v>
       </c>
-      <c r="T43">
-        <v>1</v>
-      </c>
-      <c r="U43" s="3">
-        <v>1</v>
-      </c>
-      <c r="V43" s="2">
+      <c r="U43">
+        <v>1</v>
+      </c>
+      <c r="V43" s="3">
+        <v>1</v>
+      </c>
+      <c r="W43" s="2">
         <v>18</v>
       </c>
-      <c r="W43">
+      <c r="X43">
         <v>0.9</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1.2</v>
       </c>
-      <c r="AA43"/>
-      <c r="AC43"/>
-      <c r="AE43"/>
-    </row>
-    <row r="44" spans="1:31">
+      <c r="AB43"/>
+      <c r="AD43"/>
+      <c r="AF43"/>
+    </row>
+    <row r="44" spans="1:32">
       <c r="A44">
         <v>45</v>
       </c>
       <c r="B44" t="s">
+        <v>125</v>
+      </c>
+      <c r="C44" t="s">
         <v>126</v>
       </c>
-      <c r="C44" t="s">
-        <v>127</v>
-      </c>
-      <c r="D44" s="2" t="s">
+      <c r="D44" t="s">
+        <v>126</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>35</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>43</v>
       </c>
-      <c r="I44" t="s">
+      <c r="J44" t="s">
         <v>37</v>
       </c>
-      <c r="K44">
+      <c r="L44">
         <v>6</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4</v>
       </c>
-      <c r="M44">
-        <v>1</v>
-      </c>
       <c r="N44">
         <v>1</v>
       </c>
-      <c r="P44" s="2">
+      <c r="O44">
+        <v>1</v>
+      </c>
+      <c r="Q44" s="2">
         <v>15</v>
       </c>
-      <c r="Q44">
-        <v>2</v>
-      </c>
-      <c r="R44" s="3">
-        <v>2</v>
-      </c>
-      <c r="S44" s="2">
+      <c r="R44">
+        <v>2</v>
+      </c>
+      <c r="S44" s="3">
+        <v>2</v>
+      </c>
+      <c r="T44" s="2">
         <v>42</v>
       </c>
-      <c r="T44">
+      <c r="U44">
         <v>8</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:31">
+    <row r="45" spans="1:32">
       <c r="A45">
         <v>46</v>
       </c>
       <c r="B45" t="s">
+        <v>127</v>
+      </c>
+      <c r="C45" t="s">
         <v>128</v>
       </c>
-      <c r="C45" t="s">
-        <v>129</v>
-      </c>
-      <c r="D45" s="2" t="s">
+      <c r="D45" t="s">
+        <v>128</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>40</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>54</v>
       </c>
-      <c r="I45" t="s">
+      <c r="J45" t="s">
         <v>37</v>
       </c>
-      <c r="J45"/>
-      <c r="K45" s="2">
+      <c r="K45"/>
+      <c r="L45" s="2">
         <v>5</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4</v>
       </c>
-      <c r="M45">
-        <v>0</v>
-      </c>
       <c r="N45">
-        <v>1</v>
-      </c>
-      <c r="O45"/>
-      <c r="P45" s="2">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>1</v>
+      </c>
+      <c r="P45"/>
+      <c r="Q45" s="2">
         <v>7</v>
       </c>
-      <c r="Q45">
+      <c r="R45">
         <v>7</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>9</v>
       </c>
-      <c r="S45" s="2">
+      <c r="T45" s="2">
         <v>26</v>
       </c>
-      <c r="T45">
-        <v>2</v>
-      </c>
-      <c r="U45" s="3">
-        <v>2</v>
-      </c>
-      <c r="V45" s="2">
-        <v>2</v>
-      </c>
-      <c r="W45">
+      <c r="U45">
+        <v>2</v>
+      </c>
+      <c r="V45" s="3">
+        <v>2</v>
+      </c>
+      <c r="W45" s="2">
+        <v>2</v>
+      </c>
+      <c r="X45">
         <v>7</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>8</v>
       </c>
-      <c r="AA45"/>
-      <c r="AC45"/>
-      <c r="AE45"/>
-    </row>
-    <row r="46" spans="1:31">
+      <c r="AB45"/>
+      <c r="AD45"/>
+      <c r="AF45"/>
+    </row>
+    <row r="46" spans="1:32">
       <c r="A46">
         <v>47</v>
       </c>
       <c r="B46" t="s">
+        <v>129</v>
+      </c>
+      <c r="C46" t="s">
         <v>130</v>
       </c>
-      <c r="C46" t="s">
-        <v>131</v>
-      </c>
-      <c r="D46" s="2" t="s">
+      <c r="D46" t="s">
+        <v>130</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>40</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>36</v>
       </c>
-      <c r="I46" t="s">
+      <c r="J46" t="s">
         <v>37</v>
       </c>
-      <c r="J46"/>
-      <c r="K46" s="2">
+      <c r="K46"/>
+      <c r="L46" s="2">
         <v>10</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6</v>
       </c>
-      <c r="M46">
-        <v>1</v>
-      </c>
       <c r="N46">
         <v>1</v>
       </c>
-      <c r="O46"/>
-      <c r="P46" s="2">
+      <c r="O46">
+        <v>1</v>
+      </c>
+      <c r="P46"/>
+      <c r="Q46" s="2">
         <v>32</v>
       </c>
-      <c r="Q46">
+      <c r="R46">
         <v>40</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>40</v>
       </c>
-      <c r="S46" s="2">
+      <c r="T46" s="2">
         <v>33</v>
       </c>
-      <c r="T46">
+      <c r="U46">
         <v>30</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>30</v>
       </c>
-      <c r="V46" s="2">
+      <c r="W46" s="2">
         <v>19</v>
       </c>
-      <c r="W46">
-        <v>1</v>
-      </c>
-      <c r="X46" s="3">
-        <v>1</v>
-      </c>
-      <c r="AA46"/>
-      <c r="AC46"/>
-      <c r="AE46"/>
-    </row>
-    <row r="47" spans="1:31">
+      <c r="X46">
+        <v>1</v>
+      </c>
+      <c r="Y46" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB46"/>
+      <c r="AD46"/>
+      <c r="AF46"/>
+    </row>
+    <row r="47" spans="1:32">
       <c r="A47">
         <v>48</v>
       </c>
       <c r="B47" t="s">
+        <v>131</v>
+      </c>
+      <c r="C47" t="s">
         <v>132</v>
       </c>
-      <c r="C47" t="s">
-        <v>133</v>
-      </c>
-      <c r="D47" s="2" t="s">
+      <c r="D47" t="s">
+        <v>132</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>35</v>
       </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>54</v>
       </c>
-      <c r="I47" t="s">
+      <c r="J47" t="s">
         <v>37</v>
       </c>
-      <c r="J47"/>
-      <c r="K47" s="2">
-        <v>2</v>
-      </c>
-      <c r="L47" s="3">
-        <v>1</v>
-      </c>
-      <c r="M47">
-        <v>0</v>
+      <c r="K47"/>
+      <c r="L47" s="2">
+        <v>2</v>
+      </c>
+      <c r="M47" s="3">
+        <v>1</v>
       </c>
       <c r="N47">
         <v>0</v>
       </c>
-      <c r="O47"/>
-      <c r="P47" s="2">
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47"/>
+      <c r="Q47" s="2">
         <v>11</v>
       </c>
-      <c r="Q47">
+      <c r="R47">
         <v>10</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>14</v>
       </c>
-      <c r="U47"/>
-      <c r="X47"/>
-      <c r="AA47"/>
-      <c r="AC47"/>
-      <c r="AE47"/>
-    </row>
-    <row r="48" spans="1:31">
+      <c r="V47"/>
+      <c r="Y47"/>
+      <c r="AB47"/>
+      <c r="AD47"/>
+      <c r="AF47"/>
+    </row>
+    <row r="48" spans="1:32">
       <c r="A48">
         <v>49</v>
       </c>
@@ -4104,730 +4294,772 @@
         <v>123</v>
       </c>
       <c r="C48" t="s">
-        <v>134</v>
-      </c>
-      <c r="D48" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D48" t="s">
+        <v>133</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="E48" t="s">
-        <v>35</v>
       </c>
       <c r="F48" t="s">
         <v>35</v>
       </c>
-      <c r="I48" t="s">
+      <c r="G48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J48" t="s">
         <v>37</v>
       </c>
-      <c r="J48"/>
-      <c r="K48" s="2">
+      <c r="K48"/>
+      <c r="L48" s="2">
         <v>4</v>
       </c>
-      <c r="L48" s="3">
-        <v>3</v>
-      </c>
-      <c r="M48">
-        <v>0</v>
+      <c r="M48" s="3">
+        <v>3</v>
       </c>
       <c r="N48">
         <v>0</v>
       </c>
-      <c r="O48"/>
-      <c r="P48" s="2">
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48"/>
+      <c r="Q48" s="2">
         <v>11</v>
       </c>
-      <c r="Q48">
+      <c r="R48">
         <v>8</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11</v>
       </c>
-      <c r="S48" s="2">
+      <c r="T48" s="2">
         <v>6</v>
       </c>
-      <c r="T48">
-        <v>3</v>
-      </c>
-      <c r="U48" s="3">
-        <v>3</v>
-      </c>
-      <c r="X48"/>
-      <c r="AA48"/>
-      <c r="AC48"/>
-      <c r="AE48"/>
-    </row>
-    <row r="49" spans="1:31">
+      <c r="U48">
+        <v>3</v>
+      </c>
+      <c r="V48" s="3">
+        <v>3</v>
+      </c>
+      <c r="Y48"/>
+      <c r="AB48"/>
+      <c r="AD48"/>
+      <c r="AF48"/>
+    </row>
+    <row r="49" spans="1:32">
       <c r="A49">
         <v>50</v>
       </c>
       <c r="B49" t="s">
+        <v>134</v>
+      </c>
+      <c r="C49" t="s">
         <v>135</v>
       </c>
-      <c r="C49" t="s">
-        <v>136</v>
-      </c>
-      <c r="D49" s="2" t="s">
+      <c r="D49" t="s">
+        <v>135</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>35</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>43</v>
       </c>
-      <c r="I49" t="s">
+      <c r="J49" t="s">
         <v>37</v>
       </c>
-      <c r="K49">
+      <c r="L49">
         <v>4</v>
       </c>
-      <c r="L49" s="3">
-        <v>3</v>
-      </c>
-      <c r="M49">
-        <v>0</v>
+      <c r="M49" s="3">
+        <v>3</v>
       </c>
       <c r="N49">
         <v>0</v>
       </c>
-      <c r="P49" s="2">
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="2">
         <v>11</v>
       </c>
-      <c r="Q49">
+      <c r="R49">
         <v>7</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>11</v>
       </c>
-      <c r="S49" s="2">
+      <c r="T49" s="2">
         <v>45</v>
       </c>
-      <c r="T49">
-        <v>2</v>
-      </c>
-      <c r="U49" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:31">
+      <c r="U49">
+        <v>2</v>
+      </c>
+      <c r="V49" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:32">
       <c r="A50">
         <v>51</v>
       </c>
       <c r="B50" t="s">
+        <v>136</v>
+      </c>
+      <c r="C50" t="s">
         <v>137</v>
       </c>
-      <c r="C50" t="s">
-        <v>138</v>
-      </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" t="s">
+        <v>137</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="E50" t="s">
-        <v>35</v>
       </c>
       <c r="F50" t="s">
         <v>35</v>
       </c>
-      <c r="I50" t="s">
+      <c r="G50" t="s">
+        <v>35</v>
+      </c>
+      <c r="J50" t="s">
         <v>37</v>
       </c>
-      <c r="J50"/>
-      <c r="K50" s="2">
+      <c r="K50"/>
+      <c r="L50" s="2">
         <v>5</v>
       </c>
-      <c r="L50" s="3">
+      <c r="M50" s="3">
         <v>4</v>
       </c>
-      <c r="M50">
-        <v>1</v>
-      </c>
       <c r="N50">
         <v>1</v>
       </c>
-      <c r="O50"/>
-      <c r="P50" s="2">
+      <c r="O50">
+        <v>1</v>
+      </c>
+      <c r="P50"/>
+      <c r="Q50" s="2">
         <v>6</v>
       </c>
-      <c r="Q50">
+      <c r="R50">
         <v>5</v>
       </c>
-      <c r="R50" s="3">
+      <c r="S50" s="3">
         <v>7</v>
       </c>
-      <c r="S50" s="2">
+      <c r="T50" s="2">
         <v>18</v>
       </c>
-      <c r="T50">
+      <c r="U50">
         <v>1.1000000000000001</v>
       </c>
-      <c r="U50" s="3">
+      <c r="V50" s="3">
         <v>1.7</v>
       </c>
-      <c r="X50"/>
-      <c r="AA50"/>
-      <c r="AC50"/>
-      <c r="AE50"/>
-    </row>
-    <row r="51" spans="1:31">
+      <c r="Y50"/>
+      <c r="AB50"/>
+      <c r="AD50"/>
+      <c r="AF50"/>
+    </row>
+    <row r="51" spans="1:32">
       <c r="A51">
         <v>52</v>
       </c>
       <c r="B51" t="s">
+        <v>138</v>
+      </c>
+      <c r="C51" t="s">
         <v>139</v>
       </c>
-      <c r="C51" t="s">
-        <v>140</v>
-      </c>
-      <c r="D51" s="2" t="s">
+      <c r="D51" t="s">
+        <v>139</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>40</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>35</v>
       </c>
-      <c r="I51" t="s">
+      <c r="J51" t="s">
         <v>37</v>
       </c>
-      <c r="J51"/>
-      <c r="K51" s="2">
+      <c r="K51"/>
+      <c r="L51" s="2">
         <v>9</v>
       </c>
-      <c r="L51" s="3">
+      <c r="M51" s="3">
         <v>6</v>
       </c>
-      <c r="M51">
-        <v>1</v>
-      </c>
       <c r="N51">
         <v>1</v>
       </c>
-      <c r="O51"/>
-      <c r="P51" s="2">
+      <c r="O51">
+        <v>1</v>
+      </c>
+      <c r="P51"/>
+      <c r="Q51" s="2">
         <v>6</v>
       </c>
-      <c r="Q51">
-        <v>1</v>
-      </c>
-      <c r="R51" s="3">
-        <v>3</v>
-      </c>
-      <c r="S51" s="2">
+      <c r="R51">
+        <v>1</v>
+      </c>
+      <c r="S51" s="3">
+        <v>3</v>
+      </c>
+      <c r="T51" s="2">
         <v>49</v>
       </c>
-      <c r="T51">
-        <v>1</v>
-      </c>
-      <c r="U51" s="3">
-        <v>1</v>
-      </c>
-      <c r="X51"/>
-      <c r="AA51"/>
-      <c r="AC51"/>
-      <c r="AE51"/>
-    </row>
-    <row r="52" spans="1:31">
+      <c r="U51">
+        <v>1</v>
+      </c>
+      <c r="V51" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y51"/>
+      <c r="AB51"/>
+      <c r="AD51"/>
+      <c r="AF51"/>
+    </row>
+    <row r="52" spans="1:32">
       <c r="A52">
         <v>53</v>
       </c>
       <c r="B52" t="s">
+        <v>140</v>
+      </c>
+      <c r="C52" t="s">
         <v>141</v>
       </c>
-      <c r="C52" t="s">
-        <v>142</v>
-      </c>
-      <c r="D52" s="2" t="s">
+      <c r="D52" t="s">
+        <v>141</v>
+      </c>
+      <c r="E52" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>40</v>
       </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
         <v>36</v>
       </c>
-      <c r="I52" t="s">
+      <c r="J52" t="s">
         <v>37</v>
       </c>
-      <c r="J52"/>
-      <c r="K52" s="2">
-        <v>1</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
-      <c r="M52">
-        <v>1</v>
+      <c r="K52"/>
+      <c r="L52" s="2">
+        <v>1</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
       </c>
       <c r="N52">
         <v>1</v>
       </c>
-      <c r="O52"/>
-      <c r="P52" s="2">
+      <c r="O52">
+        <v>1</v>
+      </c>
+      <c r="P52"/>
+      <c r="Q52" s="2">
         <v>9</v>
       </c>
-      <c r="Q52">
-        <v>2</v>
-      </c>
-      <c r="R52" s="3">
-        <v>2</v>
-      </c>
-      <c r="S52" s="2">
+      <c r="R52">
+        <v>2</v>
+      </c>
+      <c r="S52" s="3">
+        <v>2</v>
+      </c>
+      <c r="T52" s="2">
         <v>21</v>
       </c>
-      <c r="T52">
-        <v>2</v>
-      </c>
-      <c r="U52" s="3">
-        <v>2</v>
-      </c>
-      <c r="X52"/>
-      <c r="AA52"/>
-      <c r="AC52"/>
-      <c r="AE52"/>
-    </row>
-    <row r="53" spans="1:31">
+      <c r="U52">
+        <v>2</v>
+      </c>
+      <c r="V52" s="3">
+        <v>2</v>
+      </c>
+      <c r="Y52"/>
+      <c r="AB52"/>
+      <c r="AD52"/>
+      <c r="AF52"/>
+    </row>
+    <row r="53" spans="1:32">
       <c r="A53">
         <v>54</v>
       </c>
       <c r="B53" t="s">
+        <v>142</v>
+      </c>
+      <c r="C53" t="s">
         <v>143</v>
       </c>
-      <c r="C53" t="s">
-        <v>144</v>
-      </c>
-      <c r="D53" s="2" t="s">
+      <c r="D53" t="s">
+        <v>143</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
         <v>35</v>
       </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
         <v>43</v>
       </c>
-      <c r="I53" t="s">
+      <c r="J53" t="s">
         <v>37</v>
       </c>
-      <c r="K53">
+      <c r="L53">
         <v>5</v>
       </c>
-      <c r="L53" s="3">
+      <c r="M53" s="3">
         <v>5</v>
       </c>
-      <c r="M53">
-        <v>0</v>
-      </c>
       <c r="N53">
-        <v>1</v>
-      </c>
-      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>1</v>
+      </c>
+      <c r="P53" s="3">
         <v>6</v>
       </c>
-      <c r="P53">
+      <c r="Q53">
         <v>50</v>
       </c>
-      <c r="Q53">
-        <v>3</v>
-      </c>
-      <c r="R53" s="3">
+      <c r="R53">
+        <v>3</v>
+      </c>
+      <c r="S53" s="3">
         <v>4</v>
       </c>
-      <c r="S53">
+      <c r="T53">
         <v>51</v>
       </c>
-      <c r="T53">
+      <c r="U53">
         <v>-0.5</v>
       </c>
-      <c r="U53" s="3">
+      <c r="V53" s="3">
         <v>-0.5</v>
       </c>
     </row>
-    <row r="54" spans="1:31">
+    <row r="54" spans="1:32">
       <c r="A54">
         <v>55</v>
       </c>
       <c r="B54" t="s">
+        <v>144</v>
+      </c>
+      <c r="C54" t="s">
         <v>145</v>
       </c>
-      <c r="C54" t="s">
-        <v>146</v>
-      </c>
-      <c r="D54" s="2" t="s">
+      <c r="D54" t="s">
+        <v>145</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>40</v>
       </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
         <v>43</v>
       </c>
-      <c r="I54" t="s">
+      <c r="J54" t="s">
         <v>49</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14</v>
       </c>
-      <c r="K54">
-        <v>2</v>
-      </c>
-      <c r="L54" s="3">
-        <v>1</v>
-      </c>
-      <c r="M54">
-        <v>0</v>
+      <c r="L54">
+        <v>2</v>
+      </c>
+      <c r="M54" s="3">
+        <v>1</v>
       </c>
       <c r="N54">
-        <v>1</v>
-      </c>
-      <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>1</v>
+      </c>
+      <c r="Q54">
         <v>15</v>
       </c>
-      <c r="Q54">
-        <v>3</v>
-      </c>
-      <c r="R54" s="3">
+      <c r="R54">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3">
         <v>4</v>
       </c>
-      <c r="S54">
+      <c r="T54">
         <v>14</v>
       </c>
-      <c r="T54">
-        <v>1</v>
-      </c>
-      <c r="U54" s="3">
-        <v>1</v>
-      </c>
-      <c r="V54">
+      <c r="U54">
+        <v>1</v>
+      </c>
+      <c r="V54" s="3">
+        <v>1</v>
+      </c>
+      <c r="W54">
         <v>52</v>
       </c>
-      <c r="W54">
-        <v>3</v>
-      </c>
-      <c r="X54" s="3">
+      <c r="X54">
+        <v>3</v>
+      </c>
+      <c r="Y54" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:31">
+    <row r="55" spans="1:32">
       <c r="A55">
         <v>56</v>
       </c>
       <c r="B55" t="s">
+        <v>146</v>
+      </c>
+      <c r="C55" t="s">
         <v>147</v>
       </c>
-      <c r="C55" t="s">
-        <v>148</v>
-      </c>
-      <c r="D55" s="2" t="s">
+      <c r="D55" t="s">
+        <v>147</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>40</v>
       </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>43</v>
       </c>
-      <c r="I55" t="s">
+      <c r="J55" t="s">
         <v>37</v>
       </c>
-      <c r="K55">
+      <c r="L55">
         <v>4</v>
       </c>
-      <c r="L55" s="3">
-        <v>3</v>
-      </c>
-      <c r="M55">
-        <v>1</v>
+      <c r="M55" s="3">
+        <v>3</v>
       </c>
       <c r="N55">
         <v>1</v>
       </c>
-      <c r="P55">
+      <c r="O55">
+        <v>1</v>
+      </c>
+      <c r="Q55">
         <v>15</v>
       </c>
-      <c r="Q55">
-        <v>1</v>
-      </c>
-      <c r="R55" s="3">
-        <v>3</v>
-      </c>
-      <c r="S55">
+      <c r="R55">
+        <v>1</v>
+      </c>
+      <c r="S55" s="3">
+        <v>3</v>
+      </c>
+      <c r="T55">
         <v>60</v>
       </c>
-      <c r="T55">
-        <v>1</v>
-      </c>
-      <c r="U55" s="3">
-        <v>1</v>
-      </c>
-      <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="1:31">
+      <c r="U55">
+        <v>1</v>
+      </c>
+      <c r="V55" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="1:32">
       <c r="A56">
         <v>57</v>
       </c>
       <c r="B56" t="s">
+        <v>148</v>
+      </c>
+      <c r="C56" t="s">
         <v>149</v>
       </c>
-      <c r="C56" t="s">
-        <v>150</v>
-      </c>
-      <c r="D56" s="2" t="s">
+      <c r="D56" t="s">
+        <v>149</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>35</v>
       </c>
-      <c r="F56" t="s">
+      <c r="G56" t="s">
         <v>43</v>
       </c>
-      <c r="I56" t="s">
+      <c r="J56" t="s">
         <v>49</v>
       </c>
-      <c r="J56" s="3">
-        <v>3</v>
-      </c>
-      <c r="K56">
-        <v>2</v>
-      </c>
-      <c r="L56" s="3">
-        <v>1</v>
-      </c>
-      <c r="M56">
-        <v>0</v>
+      <c r="K56" s="3">
+        <v>3</v>
+      </c>
+      <c r="L56">
+        <v>2</v>
+      </c>
+      <c r="M56" s="3">
+        <v>1</v>
       </c>
       <c r="N56">
-        <v>1</v>
-      </c>
-      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>1</v>
+      </c>
+      <c r="Q56">
         <v>45</v>
       </c>
-      <c r="Q56">
-        <v>3</v>
-      </c>
-      <c r="R56" s="3">
+      <c r="R56">
+        <v>3</v>
+      </c>
+      <c r="S56" s="3">
         <v>4</v>
       </c>
-      <c r="S56">
+      <c r="T56">
         <v>11</v>
       </c>
-      <c r="T56">
+      <c r="U56">
         <v>12</v>
       </c>
-      <c r="U56" s="3">
+      <c r="V56" s="3">
         <v>18</v>
       </c>
-      <c r="V56">
+      <c r="W56">
         <v>14</v>
       </c>
-      <c r="W56">
-        <v>1</v>
-      </c>
-      <c r="X56" s="3">
-        <v>1</v>
-      </c>
-      <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="1:31">
+      <c r="X56">
+        <v>1</v>
+      </c>
+      <c r="Y56" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="1:32">
       <c r="A57">
         <v>58</v>
       </c>
       <c r="B57" t="s">
+        <v>150</v>
+      </c>
+      <c r="C57" t="s">
         <v>151</v>
       </c>
-      <c r="C57" t="s">
-        <v>152</v>
-      </c>
-      <c r="D57" s="2" t="s">
+      <c r="D57" t="s">
+        <v>151</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>35</v>
       </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>43</v>
       </c>
-      <c r="I57" t="s">
+      <c r="J57" t="s">
         <v>49</v>
       </c>
-      <c r="J57" s="3">
-        <v>3</v>
-      </c>
-      <c r="K57">
-        <v>2</v>
-      </c>
-      <c r="L57" s="3">
-        <v>1</v>
-      </c>
-      <c r="M57">
+      <c r="K57" s="3">
+        <v>3</v>
+      </c>
+      <c r="L57">
+        <v>2</v>
+      </c>
+      <c r="M57" s="3">
         <v>1</v>
       </c>
       <c r="N57">
         <v>1</v>
       </c>
-      <c r="P57">
-        <v>2</v>
+      <c r="O57">
+        <v>1</v>
       </c>
       <c r="Q57">
+        <v>2</v>
+      </c>
+      <c r="R57">
         <v>5</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6</v>
       </c>
-      <c r="S57">
-        <v>2</v>
-      </c>
       <c r="T57">
+        <v>2</v>
+      </c>
+      <c r="U57">
         <v>5</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:31">
+    <row r="58" spans="1:32">
       <c r="A58">
         <v>59</v>
       </c>
       <c r="B58" t="s">
+        <v>152</v>
+      </c>
+      <c r="C58" t="s">
         <v>153</v>
       </c>
-      <c r="C58" t="s">
-        <v>154</v>
-      </c>
-      <c r="D58" s="2" t="s">
+      <c r="D58" t="s">
+        <v>153</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>35</v>
       </c>
-      <c r="F58" t="s">
+      <c r="G58" t="s">
         <v>43</v>
       </c>
-      <c r="I58" t="s">
+      <c r="J58" t="s">
         <v>37</v>
       </c>
-      <c r="K58">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3">
-        <v>2</v>
-      </c>
-      <c r="M58">
-        <v>1</v>
+      <c r="L58">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3">
+        <v>2</v>
       </c>
       <c r="N58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:32">
       <c r="A59">
         <v>60</v>
       </c>
       <c r="B59" t="s">
+        <v>154</v>
+      </c>
+      <c r="C59" t="s">
         <v>155</v>
       </c>
-      <c r="C59" t="s">
-        <v>156</v>
-      </c>
-      <c r="D59" s="2" t="s">
+      <c r="D59" t="s">
+        <v>155</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
         <v>35</v>
       </c>
-      <c r="F59" t="s">
+      <c r="G59" t="s">
         <v>43</v>
       </c>
-      <c r="I59" t="s">
+      <c r="J59" t="s">
         <v>37</v>
       </c>
-      <c r="K59">
+      <c r="L59">
         <v>4</v>
       </c>
-      <c r="L59" s="3">
-        <v>3</v>
-      </c>
-      <c r="M59">
-        <v>1</v>
+      <c r="M59" s="3">
+        <v>3</v>
       </c>
       <c r="N59">
-        <v>0</v>
-      </c>
-      <c r="P59">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
       </c>
       <c r="Q59">
+        <v>2</v>
+      </c>
+      <c r="R59">
         <v>7</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:31">
+    <row r="60" spans="1:32">
       <c r="A60">
         <v>61</v>
       </c>
       <c r="B60" t="s">
+        <v>156</v>
+      </c>
+      <c r="C60" t="s">
         <v>157</v>
       </c>
-      <c r="C60" t="s">
-        <v>158</v>
-      </c>
-      <c r="D60" s="2" t="s">
+      <c r="D60" t="s">
+        <v>157</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
         <v>35</v>
       </c>
-      <c r="F60" t="s">
+      <c r="G60" t="s">
         <v>43</v>
       </c>
-      <c r="I60" t="s">
+      <c r="J60" t="s">
         <v>37</v>
       </c>
-      <c r="K60">
-        <v>2</v>
-      </c>
-      <c r="L60" s="3">
-        <v>2</v>
-      </c>
-      <c r="M60">
-        <v>1</v>
+      <c r="L60">
+        <v>2</v>
+      </c>
+      <c r="M60" s="3">
+        <v>2</v>
       </c>
       <c r="N60">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:31">
+      <c r="O60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:32">
       <c r="A61">
         <v>62</v>
       </c>
       <c r="B61" t="s">
+        <v>158</v>
+      </c>
+      <c r="C61" t="s">
         <v>159</v>
       </c>
-      <c r="C61" t="s">
-        <v>160</v>
-      </c>
-      <c r="D61" s="2" t="s">
+      <c r="D61" t="s">
+        <v>159</v>
+      </c>
+      <c r="E61" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>35</v>
       </c>
-      <c r="I61" t="s">
+      <c r="J61" t="s">
         <v>49</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>14</v>
       </c>
-      <c r="K61">
-        <v>3</v>
-      </c>
-      <c r="L61" s="3">
-        <v>2</v>
-      </c>
-      <c r="M61">
-        <v>0</v>
+      <c r="L61">
+        <v>3</v>
+      </c>
+      <c r="M61" s="3">
+        <v>2</v>
       </c>
       <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
         <v>1</v>
       </c>
     </row>
@@ -4867,19 +5099,19 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" t="s">
         <v>162</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>163</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>164</v>
-      </c>
-      <c r="I1" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -4887,13 +5119,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D2" t="s">
         <v>166</v>
-      </c>
-      <c r="C2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D2" t="s">
-        <v>167</v>
       </c>
       <c r="I2">
         <v>-1</v>
@@ -4904,19 +5136,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C3" t="s">
         <v>168</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>169</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>170</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>171</v>
-      </c>
-      <c r="F3" t="s">
-        <v>172</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -4927,16 +5159,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C4" t="s">
         <v>173</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E4" t="s">
         <v>174</v>
-      </c>
-      <c r="D4" t="s">
-        <v>170</v>
-      </c>
-      <c r="E4" t="s">
-        <v>175</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -4947,16 +5179,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C5" t="s">
         <v>176</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E5" t="s">
         <v>177</v>
-      </c>
-      <c r="D5" t="s">
-        <v>170</v>
-      </c>
-      <c r="E5" t="s">
-        <v>178</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -4967,13 +5199,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C6" t="s">
         <v>179</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>180</v>
-      </c>
-      <c r="D6" t="s">
-        <v>181</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -4984,16 +5216,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C7" t="s">
+        <v>181</v>
+      </c>
+      <c r="D7" t="s">
         <v>182</v>
       </c>
-      <c r="C7" t="s">
-        <v>182</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>183</v>
-      </c>
-      <c r="E7" t="s">
-        <v>184</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -5004,13 +5236,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D8" t="s">
         <v>185</v>
-      </c>
-      <c r="C8" t="s">
-        <v>185</v>
-      </c>
-      <c r="D8" t="s">
-        <v>186</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -5024,13 +5256,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -5044,13 +5276,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -5064,13 +5296,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>188</v>
+      </c>
+      <c r="C11" t="s">
+        <v>188</v>
+      </c>
+      <c r="D11" t="s">
         <v>189</v>
-      </c>
-      <c r="C11" t="s">
-        <v>189</v>
-      </c>
-      <c r="D11" t="s">
-        <v>190</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -5081,16 +5313,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
+        <v>190</v>
+      </c>
+      <c r="C12" t="s">
+        <v>190</v>
+      </c>
+      <c r="D12" t="s">
         <v>191</v>
       </c>
-      <c r="C12" t="s">
-        <v>191</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>192</v>
-      </c>
-      <c r="E12" t="s">
-        <v>193</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -5101,16 +5333,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
+        <v>193</v>
+      </c>
+      <c r="C13" t="s">
         <v>194</v>
       </c>
-      <c r="C13" t="s">
-        <v>195</v>
-      </c>
       <c r="D13" t="s">
+        <v>169</v>
+      </c>
+      <c r="E13" t="s">
         <v>170</v>
-      </c>
-      <c r="E13" t="s">
-        <v>171</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -5121,19 +5353,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
+        <v>195</v>
+      </c>
+      <c r="C14" t="s">
         <v>196</v>
       </c>
-      <c r="C14" t="s">
-        <v>197</v>
-      </c>
       <c r="D14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -5144,16 +5376,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
+        <v>197</v>
+      </c>
+      <c r="C15" t="s">
+        <v>197</v>
+      </c>
+      <c r="D15" t="s">
         <v>198</v>
       </c>
-      <c r="C15" t="s">
-        <v>198</v>
-      </c>
-      <c r="D15" t="s">
-        <v>199</v>
-      </c>
       <c r="E15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -5164,16 +5396,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
+        <v>199</v>
+      </c>
+      <c r="C16" t="s">
+        <v>199</v>
+      </c>
+      <c r="D16" t="s">
+        <v>169</v>
+      </c>
+      <c r="E16" t="s">
         <v>200</v>
-      </c>
-      <c r="C16" t="s">
-        <v>200</v>
-      </c>
-      <c r="D16" t="s">
-        <v>170</v>
-      </c>
-      <c r="E16" t="s">
-        <v>201</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -5184,13 +5416,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C17" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -5204,16 +5436,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
+        <v>202</v>
+      </c>
+      <c r="C18" t="s">
+        <v>202</v>
+      </c>
+      <c r="D18" t="s">
         <v>203</v>
       </c>
-      <c r="C18" t="s">
-        <v>203</v>
-      </c>
-      <c r="D18" t="s">
-        <v>204</v>
-      </c>
       <c r="E18" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -5224,13 +5456,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C19" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D19" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -5244,13 +5476,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
+        <v>205</v>
+      </c>
+      <c r="C20" t="s">
+        <v>205</v>
+      </c>
+      <c r="D20" t="s">
         <v>206</v>
-      </c>
-      <c r="C20" t="s">
-        <v>206</v>
-      </c>
-      <c r="D20" t="s">
-        <v>207</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5264,16 +5496,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
+        <v>207</v>
+      </c>
+      <c r="C21" t="s">
+        <v>207</v>
+      </c>
+      <c r="D21" t="s">
+        <v>169</v>
+      </c>
+      <c r="E21" t="s">
         <v>208</v>
-      </c>
-      <c r="C21" t="s">
-        <v>208</v>
-      </c>
-      <c r="D21" t="s">
-        <v>170</v>
-      </c>
-      <c r="E21" t="s">
-        <v>209</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -5284,16 +5516,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
+        <v>209</v>
+      </c>
+      <c r="C22" t="s">
+        <v>209</v>
+      </c>
+      <c r="D22" t="s">
+        <v>182</v>
+      </c>
+      <c r="E22" t="s">
         <v>210</v>
-      </c>
-      <c r="C22" t="s">
-        <v>210</v>
-      </c>
-      <c r="D22" t="s">
-        <v>183</v>
-      </c>
-      <c r="E22" t="s">
-        <v>211</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -5304,13 +5536,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C23" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D23" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -5324,19 +5556,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C24" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D24" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -5347,13 +5579,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C25" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -5367,16 +5599,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D26" t="s">
+        <v>169</v>
+      </c>
+      <c r="E26" t="s">
         <v>170</v>
-      </c>
-      <c r="E26" t="s">
-        <v>171</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -5390,16 +5622,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C27" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D27" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E27" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -5410,13 +5642,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C28" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D28" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -5430,19 +5662,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
+        <v>217</v>
+      </c>
+      <c r="C29" t="s">
+        <v>217</v>
+      </c>
+      <c r="D29" t="s">
+        <v>185</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29" t="s">
         <v>218</v>
-      </c>
-      <c r="C29" t="s">
-        <v>218</v>
-      </c>
-      <c r="D29" t="s">
-        <v>186</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29" t="s">
-        <v>219</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -5456,13 +5688,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
+        <v>219</v>
+      </c>
+      <c r="C30" t="s">
         <v>220</v>
       </c>
-      <c r="C30" t="s">
-        <v>221</v>
-      </c>
       <c r="D30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -5476,19 +5708,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
+        <v>221</v>
+      </c>
+      <c r="C31" t="s">
+        <v>221</v>
+      </c>
+      <c r="D31" t="s">
+        <v>169</v>
+      </c>
+      <c r="E31" t="s">
+        <v>170</v>
+      </c>
+      <c r="F31" t="s">
         <v>222</v>
-      </c>
-      <c r="C31" t="s">
-        <v>222</v>
-      </c>
-      <c r="D31" t="s">
-        <v>170</v>
-      </c>
-      <c r="E31" t="s">
-        <v>171</v>
-      </c>
-      <c r="F31" t="s">
-        <v>223</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -5499,19 +5731,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C32" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D32" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -5522,19 +5754,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C33" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D33" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E33">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -5545,16 +5777,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
+        <v>225</v>
+      </c>
+      <c r="C34" t="s">
+        <v>225</v>
+      </c>
+      <c r="D34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E34" t="s">
         <v>226</v>
-      </c>
-      <c r="C34" t="s">
-        <v>226</v>
-      </c>
-      <c r="D34" t="s">
-        <v>170</v>
-      </c>
-      <c r="E34" t="s">
-        <v>227</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -5565,16 +5797,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
+        <v>227</v>
+      </c>
+      <c r="C35" t="s">
+        <v>227</v>
+      </c>
+      <c r="D35" t="s">
+        <v>169</v>
+      </c>
+      <c r="E35" t="s">
         <v>228</v>
-      </c>
-      <c r="C35" t="s">
-        <v>228</v>
-      </c>
-      <c r="D35" t="s">
-        <v>170</v>
-      </c>
-      <c r="E35" t="s">
-        <v>229</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -5585,19 +5817,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C36" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D36" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F36" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -5611,13 +5843,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
+        <v>230</v>
+      </c>
+      <c r="C37" t="s">
         <v>231</v>
       </c>
-      <c r="C37" t="s">
-        <v>232</v>
-      </c>
       <c r="D37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E37">
         <v>11</v>
@@ -5631,16 +5863,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C38" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D38" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E38" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -5651,13 +5883,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C39" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D39" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -5674,16 +5906,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
+        <v>234</v>
+      </c>
+      <c r="C40" t="s">
+        <v>234</v>
+      </c>
+      <c r="D40" t="s">
+        <v>169</v>
+      </c>
+      <c r="E40" t="s">
         <v>235</v>
-      </c>
-      <c r="C40" t="s">
-        <v>235</v>
-      </c>
-      <c r="D40" t="s">
-        <v>170</v>
-      </c>
-      <c r="E40" t="s">
-        <v>236</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -5694,13 +5926,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C41" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D41" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -5717,19 +5949,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D42" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -5743,13 +5975,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C43" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D43" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E43">
         <v>12</v>
@@ -5763,13 +5995,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C44" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D44" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E44">
         <v>13</v>
@@ -5783,19 +6015,19 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C45" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D45" t="s">
+        <v>169</v>
+      </c>
+      <c r="E45" t="s">
         <v>170</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>171</v>
-      </c>
-      <c r="F45" t="s">
-        <v>172</v>
       </c>
       <c r="I45">
         <v>-1</v>
@@ -5806,16 +6038,16 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C46" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D46" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E46" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -5826,13 +6058,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C47" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D47" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E47">
         <v>14</v>
@@ -5846,19 +6078,19 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
+        <v>243</v>
+      </c>
+      <c r="C48" t="s">
+        <v>243</v>
+      </c>
+      <c r="D48" t="s">
         <v>244</v>
       </c>
-      <c r="C48" t="s">
-        <v>244</v>
-      </c>
-      <c r="D48" t="s">
-        <v>245</v>
-      </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I48">
         <v>-1</v>
@@ -5869,13 +6101,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C49" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D49" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E49">
         <v>15</v>
@@ -5889,19 +6121,19 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C50" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D50" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I50">
         <v>-1</v>
@@ -5912,13 +6144,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C51" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D51" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E51">
         <v>16</v>
@@ -5932,13 +6164,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C52" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D52" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -5952,13 +6184,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C53" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D53" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -5972,13 +6204,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C54" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D54" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E54">
         <v>3</v>
@@ -5995,16 +6227,16 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C55" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D55" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E55" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G55">
         <v>6</v>
@@ -6018,16 +6250,16 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C56" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D56" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E56" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G56">
         <v>7</v>
@@ -6041,16 +6273,16 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
+        <v>253</v>
+      </c>
+      <c r="C57" t="s">
         <v>254</v>
       </c>
-      <c r="C57" t="s">
-        <v>255</v>
-      </c>
       <c r="D57" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E57" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G57">
         <v>8</v>
@@ -6064,16 +6296,16 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
+        <v>255</v>
+      </c>
+      <c r="C58" t="s">
         <v>256</v>
       </c>
-      <c r="C58" t="s">
-        <v>257</v>
-      </c>
       <c r="D58" t="s">
+        <v>169</v>
+      </c>
+      <c r="E58" t="s">
         <v>170</v>
-      </c>
-      <c r="E58" t="s">
-        <v>171</v>
       </c>
       <c r="G58">
         <v>6</v>
@@ -6087,16 +6319,16 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C59" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D59" t="s">
+        <v>169</v>
+      </c>
+      <c r="E59" t="s">
         <v>170</v>
-      </c>
-      <c r="E59" t="s">
-        <v>171</v>
       </c>
       <c r="G59">
         <v>7</v>
@@ -6110,16 +6342,16 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C60" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D60" t="s">
+        <v>169</v>
+      </c>
+      <c r="E60" t="s">
         <v>170</v>
-      </c>
-      <c r="E60" t="s">
-        <v>171</v>
       </c>
       <c r="G60">
         <v>8</v>
@@ -6133,19 +6365,19 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C61" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E61">
         <v>3</v>
       </c>
       <c r="F61" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I61">
         <v>-1</v>
@@ -6156,13 +6388,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C62" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D62" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E62">
         <v>20</v>
@@ -6202,13 +6434,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D1" t="s">
         <v>262</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="1" t="s">
         <v>263</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>264</v>
       </c>
       <c r="F1" t="s">
         <v>15</v>
@@ -6235,10 +6467,10 @@
         <v>25</v>
       </c>
       <c r="N1" t="s">
+        <v>264</v>
+      </c>
+      <c r="O1" t="s">
         <v>265</v>
-      </c>
-      <c r="O1" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -6246,10 +6478,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C2" t="s">
         <v>267</v>
-      </c>
-      <c r="C2" t="s">
-        <v>268</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -6275,10 +6507,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -6298,10 +6530,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -6315,10 +6547,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C5" t="s">
         <v>271</v>
-      </c>
-      <c r="C5" t="s">
-        <v>272</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -6350,10 +6582,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -6373,10 +6605,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -6396,10 +6628,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -6419,10 +6651,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -6442,10 +6674,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -6465,10 +6697,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -6494,10 +6726,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -6523,10 +6755,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -6546,10 +6778,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C14" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -6569,10 +6801,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C15" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -6592,10 +6824,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C16" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -6615,10 +6847,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C17" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -6638,10 +6870,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C18" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -6661,10 +6893,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C19" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -6678,10 +6910,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C20" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -6695,10 +6927,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C21" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -6712,10 +6944,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C22" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -6761,16 +6993,16 @@
         <v>4</v>
       </c>
       <c r="D1" t="s">
+        <v>282</v>
+      </c>
+      <c r="E1" t="s">
         <v>283</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>284</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>285</v>
-      </c>
-      <c r="G1" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -6778,13 +7010,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C2" t="s">
         <v>287</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>288</v>
-      </c>
-      <c r="D2" t="s">
-        <v>289</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -6798,13 +7030,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C3" t="s">
         <v>290</v>
       </c>
-      <c r="C3" t="s">
-        <v>291</v>
-      </c>
       <c r="D3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F3" t="s">
         <v>40</v>
@@ -6815,13 +7047,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F4" t="s">
         <v>35</v>
@@ -6832,13 +7064,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C5" t="s">
+        <v>287</v>
+      </c>
+      <c r="D5" t="s">
         <v>288</v>
-      </c>
-      <c r="D5" t="s">
-        <v>289</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -6852,13 +7084,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C6" t="s">
+        <v>287</v>
+      </c>
+      <c r="D6" t="s">
         <v>288</v>
-      </c>
-      <c r="D6" t="s">
-        <v>289</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -6872,13 +7104,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C7" t="s">
+        <v>287</v>
+      </c>
+      <c r="D7" t="s">
         <v>288</v>
-      </c>
-      <c r="D7" t="s">
-        <v>289</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -6892,13 +7124,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C8" t="s">
+        <v>287</v>
+      </c>
+      <c r="D8" t="s">
         <v>288</v>
-      </c>
-      <c r="D8" t="s">
-        <v>289</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -6912,13 +7144,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C9" t="s">
+        <v>287</v>
+      </c>
+      <c r="D9" t="s">
         <v>288</v>
-      </c>
-      <c r="D9" t="s">
-        <v>289</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -6932,13 +7164,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C10" t="s">
+        <v>287</v>
+      </c>
+      <c r="D10" t="s">
         <v>288</v>
-      </c>
-      <c r="D10" t="s">
-        <v>289</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -6952,13 +7184,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>298</v>
+      </c>
+      <c r="C11" t="s">
         <v>299</v>
       </c>
-      <c r="C11" t="s">
-        <v>300</v>
-      </c>
       <c r="D11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E11" t="s">
         <v>40</v>

--- a/Assets/StreamingAssets/Configurations/dev/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/dev/Cards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFAA2696-E98F-42D5-8367-B5DB15D52C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB9F7ED-0D7D-4CC2-A1E4-09522CD89ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -939,9 +939,6 @@
     <t>VCardTypeUsedCountCondition</t>
   </si>
   <si>
-    <t>参数+X1</t>
-  </si>
-  <si>
     <t>DescriptionInGame</t>
   </si>
   <si>
@@ -988,6 +985,9 @@
   </si>
   <si>
     <t>亲和力+X1</t>
+  </si>
+  <si>
+    <t>参数+X1$1212</t>
   </si>
 </sst>
 </file>
@@ -1397,7 +1397,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>3</v>
@@ -1498,7 +1498,7 @@
         <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>34</v>
@@ -1553,7 +1553,7 @@
         <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>34</v>
@@ -1608,7 +1608,7 @@
         <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>34</v>
@@ -1665,7 +1665,7 @@
         <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>34</v>
@@ -1728,7 +1728,7 @@
         <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>48</v>
@@ -1791,7 +1791,7 @@
         <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>48</v>
@@ -1857,7 +1857,7 @@
         <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>48</v>
@@ -1930,7 +1930,7 @@
         <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>34</v>
@@ -1993,7 +1993,7 @@
         <v>58</v>
       </c>
       <c r="D10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>34</v>
@@ -2056,7 +2056,7 @@
         <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>34</v>
@@ -2113,7 +2113,7 @@
         <v>62</v>
       </c>
       <c r="D12" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>34</v>
@@ -2179,7 +2179,7 @@
         <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>66</v>
@@ -2242,7 +2242,7 @@
         <v>68</v>
       </c>
       <c r="D14" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>34</v>
@@ -2297,7 +2297,7 @@
         <v>70</v>
       </c>
       <c r="D15" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>66</v>
@@ -2352,7 +2352,7 @@
         <v>72</v>
       </c>
       <c r="D16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>66</v>
@@ -2412,10 +2412,10 @@
         <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D17" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>66</v>

--- a/Assets/StreamingAssets/Configurations/dev/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/dev/Cards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB9F7ED-0D7D-4CC2-A1E4-09522CD89ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A35982-8265-441E-963A-ED652C2938CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -994,12 +994,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1053,7 +1060,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1065,6 +1072,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1616,7 +1624,7 @@
       <c r="F4" t="s">
         <v>35</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="7" t="s">
         <v>43</v>
       </c>
       <c r="J4" t="s">

--- a/Assets/StreamingAssets/Configurations/dev/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/dev/Cards.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\dev\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A35982-8265-441E-963A-ED652C2938CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C73CFC0A-AF50-4F60-A563-A94655455336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Conditions" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$A$1:$AH$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$A$1:$AI$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="339">
   <si>
     <t>ID</t>
   </si>
@@ -48,6 +48,9 @@
     <t>Description</t>
   </si>
   <si>
+    <t>DescriptionInGame</t>
+  </si>
+  <si>
     <t>Rarity</t>
   </si>
   <si>
@@ -141,6 +144,9 @@
     <t>参数+7</t>
   </si>
   <si>
+    <t>参数+X1</t>
+  </si>
+  <si>
     <t>Common</t>
   </si>
   <si>
@@ -159,6 +165,9 @@
     <t>神采+4</t>
   </si>
   <si>
+    <t>神采+X1</t>
+  </si>
+  <si>
     <t>M</t>
   </si>
   <si>
@@ -168,21 +177,33 @@
     <t>参数+15，红温大于10层时，参数+9</t>
   </si>
   <si>
+    <t>参数+X1，红温大于10层时，参数+X2</t>
+  </si>
+  <si>
     <t>C</t>
   </si>
   <si>
+    <t>angry</t>
+  </si>
+  <si>
     <t>战术喝水</t>
   </si>
   <si>
     <t>参数+5，神采+4</t>
   </si>
   <si>
+    <t>参数+X1，神采+X2</t>
+  </si>
+  <si>
     <t>kale</t>
   </si>
   <si>
     <t>下一张使用的牌会使用两次，抽一张卡,神采+2</t>
   </si>
   <si>
+    <t>下一张使用的牌会使用两次，抽X3张卡,神采+X2</t>
+  </si>
+  <si>
     <t>Epic</t>
   </si>
   <si>
@@ -195,12 +216,18 @@
     <t>重抽其他手牌，卡牌使用次数+1，体力消耗减少50%+2回合</t>
   </si>
   <si>
+    <t>重抽其他手牌，卡牌使用次数+X3，体力消耗减少50%+X2回合</t>
+  </si>
+  <si>
     <t>才八点</t>
   </si>
   <si>
     <t>获得一个额外回合，神采+7，出牌次数+1</t>
   </si>
   <si>
+    <t>获得一个额外回合，神采+X1，出牌次数+X2</t>
+  </si>
+  <si>
     <t>I</t>
   </si>
   <si>
@@ -210,24 +237,36 @@
     <t>亲和力+3，神采+2</t>
   </si>
   <si>
+    <t>亲和力+X1，神采+X2</t>
+  </si>
+  <si>
     <t>集中</t>
   </si>
   <si>
     <t>专注+2，神采+2</t>
   </si>
   <si>
+    <t>专注+X1，神采+X2</t>
+  </si>
+  <si>
     <t>生气</t>
   </si>
   <si>
     <t>红温+2，神采+2</t>
   </si>
   <si>
+    <t>红温+X1，神采+X2</t>
+  </si>
+  <si>
     <t>二次推流</t>
   </si>
   <si>
     <t>参数+9/2次</t>
   </si>
   <si>
+    <t>参数+X1/2次</t>
+  </si>
+  <si>
     <t>加分动画显示需改进</t>
   </si>
   <si>
@@ -246,27 +285,48 @@
     <t>亲和力+6</t>
   </si>
   <si>
+    <t>亲和力+X1</t>
+  </si>
+  <si>
     <t>饭撒</t>
   </si>
   <si>
     <t>获得亲和力140%的参数</t>
   </si>
   <si>
+    <t>获得亲和力X1的参数</t>
+  </si>
+  <si>
     <t>desuwa</t>
   </si>
   <si>
     <t>亲和力+4，获得亲和力层数80%的参数</t>
   </si>
   <si>
+    <t>亲和力+X1，获得亲和力层数X2的参数</t>
+  </si>
+  <si>
     <t>欢迎上舰</t>
   </si>
   <si>
+    <t>舰长+1，神采+4，体力消耗减少+2回合</t>
+  </si>
+  <si>
+    <t>舰长+X1，神采+X2，体力消耗减少+X3回合</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
     <t>攻击弹幕</t>
   </si>
   <si>
     <t>红温+5</t>
   </si>
   <si>
+    <t>红温+X1$红温变为1.5倍</t>
+  </si>
+  <si>
     <t>神降临</t>
   </si>
   <si>
@@ -327,6 +387,9 @@
     <t>神采+6</t>
   </si>
   <si>
+    <t>fun</t>
+  </si>
+  <si>
     <t>SC</t>
   </si>
   <si>
@@ -741,6 +804,9 @@
     <t>有红温时，专注+X</t>
   </si>
   <si>
+    <t>体力+X</t>
+  </si>
+  <si>
     <t>体力回复X点</t>
   </si>
   <si>
@@ -822,6 +888,21 @@
     <t>每当使用A卡，红温+1</t>
   </si>
   <si>
+    <t>回合开始时，抽X张卡牌</t>
+  </si>
+  <si>
+    <t>回合开始时，抽1张卡牌</t>
+  </si>
+  <si>
+    <t>红温变成X倍</t>
+  </si>
+  <si>
+    <t>回合结束时，幽默+X</t>
+  </si>
+  <si>
+    <t>回合结束时，幽默+1</t>
+  </si>
+  <si>
     <t>BuffType</t>
   </si>
   <si>
@@ -885,6 +966,39 @@
     <t>每当使用A卡时，红温+1</t>
   </si>
   <si>
+    <t>回合开始时，抽一张卡</t>
+  </si>
+  <si>
+    <t>舰长BUFF1</t>
+  </si>
+  <si>
+    <t>舰长BUFF2</t>
+  </si>
+  <si>
+    <t>舰长BUFF3</t>
+  </si>
+  <si>
+    <t>舰长BUFF4</t>
+  </si>
+  <si>
+    <t>舰长BUFF5</t>
+  </si>
+  <si>
+    <t>舰长BUFF6</t>
+  </si>
+  <si>
+    <t>舰长BUFF7</t>
+  </si>
+  <si>
+    <t>舰长BUFF8</t>
+  </si>
+  <si>
+    <t>舰长BUFF9</t>
+  </si>
+  <si>
+    <t>舰长BUFF10</t>
+  </si>
+  <si>
     <t>OperatorType</t>
   </si>
   <si>
@@ -939,55 +1053,7 @@
     <t>VCardTypeUsedCountCondition</t>
   </si>
   <si>
-    <t>DescriptionInGame</t>
-  </si>
-  <si>
-    <t>神采+X1</t>
-  </si>
-  <si>
-    <t>参数+X1，红温大于10层时，参数+X2</t>
-  </si>
-  <si>
-    <t>参数+X1，神采+X2</t>
-  </si>
-  <si>
-    <t>重抽其他手牌，卡牌使用次数+X3，体力消耗减少50%+X2回合</t>
-  </si>
-  <si>
-    <t>获得一个额外回合，神采+X1，出牌次数+X2</t>
-  </si>
-  <si>
-    <t>亲和力+X1，神采+X2</t>
-  </si>
-  <si>
-    <t>专注+X1，神采+X2</t>
-  </si>
-  <si>
-    <t>红温+X1，神采+X2</t>
-  </si>
-  <si>
-    <t>参数+X1/2次</t>
-  </si>
-  <si>
-    <t>获得亲和力X1的参数</t>
-  </si>
-  <si>
-    <t>亲和力+X1，获得亲和力层数X2的参数</t>
-  </si>
-  <si>
-    <t>舰长+X1，神采+X2，体力消耗减少+X3回合</t>
-  </si>
-  <si>
-    <t>舰长+1，神采+4，体力消耗减少+2回合+UC17:V17</t>
-  </si>
-  <si>
-    <t>下一张使用的牌会使用两次，抽X3张卡,神采+X2</t>
-  </si>
-  <si>
-    <t>亲和力+X1</t>
-  </si>
-  <si>
-    <t>参数+X1$1212</t>
+    <t>Priority</t>
   </si>
 </sst>
 </file>
@@ -1072,7 +1138,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1358,7 +1424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH61"/>
+  <dimension ref="A1:AI61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
@@ -1375,26 +1441,26 @@
     <col min="12" max="12" width="7.140625" customWidth="1"/>
     <col min="13" max="13" width="14" style="3" customWidth="1"/>
     <col min="14" max="14" width="10.28515625" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="18" width="12.140625" customWidth="1"/>
-    <col min="19" max="19" width="17.7109375" style="3" customWidth="1"/>
-    <col min="20" max="20" width="11" customWidth="1"/>
-    <col min="21" max="21" width="12.28515625" customWidth="1"/>
-    <col min="22" max="22" width="17.140625" style="3" customWidth="1"/>
-    <col min="25" max="25" width="17.7109375" style="3" customWidth="1"/>
-    <col min="26" max="26" width="10.7109375" customWidth="1"/>
-    <col min="27" max="27" width="11" customWidth="1"/>
-    <col min="28" max="28" width="17.7109375" style="3" customWidth="1"/>
-    <col min="29" max="29" width="12.42578125" customWidth="1"/>
-    <col min="30" max="30" width="12.42578125" style="3" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" customWidth="1"/>
-    <col min="32" max="32" width="9" style="3"/>
-    <col min="33" max="33" width="4.28515625" customWidth="1"/>
+    <col min="15" max="16" width="13.7109375" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="3" customWidth="1"/>
+    <col min="18" max="18" width="9.7109375" customWidth="1"/>
+    <col min="19" max="19" width="12.140625" customWidth="1"/>
+    <col min="20" max="20" width="17.7109375" style="3" customWidth="1"/>
+    <col min="21" max="21" width="11" customWidth="1"/>
+    <col min="22" max="22" width="12.28515625" customWidth="1"/>
+    <col min="23" max="23" width="17.140625" style="3" customWidth="1"/>
+    <col min="26" max="26" width="17.7109375" style="3" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" customWidth="1"/>
+    <col min="28" max="28" width="11" customWidth="1"/>
+    <col min="29" max="29" width="17.7109375" style="3" customWidth="1"/>
+    <col min="30" max="30" width="12.42578125" customWidth="1"/>
+    <col min="31" max="31" width="12.42578125" style="3" customWidth="1"/>
+    <col min="32" max="32" width="12.28515625" customWidth="1"/>
+    <col min="33" max="33" width="9" style="3"/>
+    <col min="34" max="34" width="4.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1405,120 +1471,123 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>300</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="P1" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AB1" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AE1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AG1" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:34">
+      <c r="AH1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:35">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K2"/>
       <c r="L2" s="2">
@@ -1533,47 +1602,50 @@
       <c r="O2">
         <v>0</v>
       </c>
-      <c r="P2"/>
-      <c r="Q2" s="2">
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2"/>
+      <c r="R2" s="2">
         <v>11</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <v>7</v>
       </c>
-      <c r="S2" s="3">
+      <c r="T2" s="3">
         <v>7</v>
       </c>
-      <c r="V2"/>
-      <c r="Y2"/>
-      <c r="AB2"/>
-      <c r="AD2"/>
-      <c r="AF2"/>
-      <c r="AG2" s="5"/>
-    </row>
-    <row r="3" spans="1:34">
+      <c r="W2"/>
+      <c r="Z2"/>
+      <c r="AC2"/>
+      <c r="AE2"/>
+      <c r="AG2"/>
+      <c r="AH2" s="5"/>
+    </row>
+    <row r="3" spans="1:35">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" t="s">
         <v>38</v>
       </c>
-      <c r="C3" t="s">
+      <c r="J3" t="s">
         <v>39</v>
-      </c>
-      <c r="D3" t="s">
-        <v>301</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" t="s">
-        <v>37</v>
       </c>
       <c r="K3"/>
       <c r="L3" s="2">
@@ -1588,47 +1660,53 @@
       <c r="O3">
         <v>0</v>
       </c>
-      <c r="P3"/>
-      <c r="Q3" s="2">
-        <v>2</v>
-      </c>
-      <c r="R3">
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3"/>
+      <c r="R3" s="2">
+        <v>2</v>
+      </c>
+      <c r="S3">
         <v>4</v>
       </c>
-      <c r="S3" s="3">
+      <c r="T3" s="3">
         <v>4</v>
       </c>
-      <c r="V3"/>
-      <c r="Y3"/>
-      <c r="AB3"/>
-      <c r="AD3"/>
-      <c r="AF3"/>
-      <c r="AG3" s="5"/>
-    </row>
-    <row r="4" spans="1:34">
+      <c r="W3"/>
+      <c r="Z3"/>
+      <c r="AC3"/>
+      <c r="AE3"/>
+      <c r="AG3"/>
+      <c r="AH3" s="5"/>
+    </row>
+    <row r="4" spans="1:35">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>302</v>
+        <v>46</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>43</v>
+        <v>37</v>
+      </c>
+      <c r="G4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" t="s">
+        <v>48</v>
       </c>
       <c r="J4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L4">
         <v>5</v>
@@ -1642,50 +1720,53 @@
       <c r="O4">
         <v>0</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="R4" s="2">
         <v>11</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <v>15</v>
       </c>
-      <c r="S4" s="3">
+      <c r="T4" s="3">
         <v>18</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <v>56</v>
       </c>
-      <c r="U4">
+      <c r="V4">
         <v>9</v>
       </c>
-      <c r="V4" s="3">
+      <c r="W4" s="3">
         <v>12</v>
       </c>
-      <c r="AG4" s="5"/>
-    </row>
-    <row r="5" spans="1:34">
+      <c r="AH4" s="5"/>
+    </row>
+    <row r="5" spans="1:35">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>303</v>
+        <v>51</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K5"/>
       <c r="L5" s="2">
@@ -1700,55 +1781,58 @@
       <c r="O5">
         <v>0</v>
       </c>
-      <c r="P5"/>
-      <c r="Q5" s="2">
+      <c r="Q5"/>
+      <c r="R5" s="2">
         <v>11</v>
       </c>
-      <c r="R5">
+      <c r="S5">
         <v>5</v>
       </c>
-      <c r="S5" s="3">
+      <c r="T5" s="3">
         <v>5</v>
       </c>
-      <c r="T5" s="2">
-        <v>2</v>
-      </c>
-      <c r="U5">
-        <v>2</v>
-      </c>
-      <c r="V5" s="3">
-        <v>2</v>
-      </c>
-      <c r="Y5"/>
-      <c r="AB5"/>
-      <c r="AD5"/>
-      <c r="AF5"/>
-      <c r="AG5" s="5"/>
-    </row>
-    <row r="6" spans="1:34">
+      <c r="U5" s="2">
+        <v>2</v>
+      </c>
+      <c r="V5">
+        <v>2</v>
+      </c>
+      <c r="W5" s="3">
+        <v>2</v>
+      </c>
+      <c r="Z5"/>
+      <c r="AC5"/>
+      <c r="AE5"/>
+      <c r="AG5"/>
+      <c r="AH5" s="5"/>
+    </row>
+    <row r="6" spans="1:35">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" t="s">
         <v>47</v>
       </c>
-      <c r="D6" t="s">
-        <v>314</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="H6" t="s">
         <v>48</v>
       </c>
-      <c r="F6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" t="s">
-        <v>43</v>
-      </c>
       <c r="J6" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="K6" s="3">
         <v>3</v>
@@ -1765,53 +1849,53 @@
       <c r="O6">
         <v>1</v>
       </c>
-      <c r="Q6" s="2">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>2</v>
+      <c r="R6" s="2">
+        <v>0</v>
       </c>
       <c r="U6">
         <v>2</v>
       </c>
-      <c r="V6" s="3">
+      <c r="V6">
+        <v>2</v>
+      </c>
+      <c r="W6" s="3">
         <v>7</v>
       </c>
-      <c r="W6">
+      <c r="X6">
         <v>9</v>
       </c>
-      <c r="X6">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG6" s="5"/>
-    </row>
-    <row r="7" spans="1:34">
+      <c r="Y6">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="5"/>
+    </row>
+    <row r="7" spans="1:35">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>304</v>
+        <v>59</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K7"/>
       <c r="L7" s="2">
@@ -1826,58 +1910,58 @@
       <c r="O7">
         <v>1</v>
       </c>
-      <c r="P7"/>
-      <c r="Q7" s="2">
+      <c r="Q7"/>
+      <c r="R7" s="2">
         <v>4</v>
       </c>
-      <c r="S7"/>
-      <c r="T7" s="2">
+      <c r="T7"/>
+      <c r="U7" s="2">
         <v>21</v>
       </c>
-      <c r="U7">
-        <v>2</v>
-      </c>
-      <c r="V7" s="3">
-        <v>2</v>
-      </c>
-      <c r="W7" s="2">
+      <c r="V7">
+        <v>2</v>
+      </c>
+      <c r="W7" s="3">
+        <v>2</v>
+      </c>
+      <c r="X7" s="2">
         <v>14</v>
       </c>
-      <c r="X7">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="3">
-        <v>1</v>
-      </c>
-      <c r="AB7"/>
-      <c r="AD7"/>
-      <c r="AF7"/>
-      <c r="AG7" s="5"/>
-    </row>
-    <row r="8" spans="1:34">
+      <c r="Y7">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC7"/>
+      <c r="AE7"/>
+      <c r="AG7"/>
+      <c r="AH7" s="5"/>
+    </row>
+    <row r="8" spans="1:35">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>305</v>
+        <v>62</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G8" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="J8" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -1894,63 +1978,63 @@
       <c r="O8">
         <v>1</v>
       </c>
-      <c r="P8"/>
-      <c r="Q8" s="2">
-        <v>2</v>
-      </c>
-      <c r="R8">
+      <c r="Q8"/>
+      <c r="R8" s="2">
+        <v>2</v>
+      </c>
+      <c r="S8">
         <v>7</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7</v>
       </c>
-      <c r="T8" s="2">
-        <v>3</v>
-      </c>
-      <c r="U8">
-        <v>1</v>
-      </c>
-      <c r="V8" s="3">
-        <v>1</v>
-      </c>
-      <c r="W8" s="2">
+      <c r="U8" s="2">
+        <v>3</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="W8" s="3">
+        <v>1</v>
+      </c>
+      <c r="X8" s="2">
         <v>14</v>
       </c>
-      <c r="X8">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>1</v>
-      </c>
-      <c r="AB8"/>
-      <c r="AD8"/>
-      <c r="AF8"/>
-      <c r="AG8" s="5"/>
-    </row>
-    <row r="9" spans="1:34">
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC8"/>
+      <c r="AE8"/>
+      <c r="AG8"/>
+      <c r="AH8" s="5"/>
+    </row>
+    <row r="9" spans="1:35">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>306</v>
+        <v>66</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K9"/>
       <c r="L9" s="2">
@@ -1965,55 +2049,55 @@
       <c r="O9">
         <v>0</v>
       </c>
-      <c r="P9"/>
-      <c r="Q9" s="2">
+      <c r="Q9"/>
+      <c r="R9" s="2">
         <v>6</v>
       </c>
-      <c r="R9">
-        <v>3</v>
-      </c>
-      <c r="S9" s="3">
+      <c r="S9">
+        <v>3</v>
+      </c>
+      <c r="T9" s="3">
         <v>4</v>
       </c>
-      <c r="T9" s="2">
-        <v>2</v>
-      </c>
-      <c r="U9">
-        <v>3</v>
-      </c>
-      <c r="V9" s="3">
+      <c r="U9" s="2">
+        <v>2</v>
+      </c>
+      <c r="V9">
+        <v>3</v>
+      </c>
+      <c r="W9" s="3">
         <v>4</v>
       </c>
-      <c r="Y9"/>
-      <c r="AB9"/>
-      <c r="AD9"/>
-      <c r="AF9"/>
-      <c r="AG9" s="5"/>
-    </row>
-    <row r="10" spans="1:34">
+      <c r="Z9"/>
+      <c r="AC9"/>
+      <c r="AE9"/>
+      <c r="AG9"/>
+      <c r="AH9" s="5"/>
+    </row>
+    <row r="10" spans="1:35">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>307</v>
+        <v>69</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F10" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G10" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="J10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K10"/>
       <c r="L10" s="2">
@@ -2028,55 +2112,58 @@
       <c r="O10">
         <v>0</v>
       </c>
-      <c r="P10"/>
-      <c r="Q10" s="2">
+      <c r="Q10"/>
+      <c r="R10" s="2">
         <v>7</v>
       </c>
-      <c r="R10">
-        <v>2</v>
-      </c>
-      <c r="S10" s="3">
-        <v>3</v>
-      </c>
-      <c r="T10" s="2">
-        <v>2</v>
-      </c>
-      <c r="U10">
-        <v>2</v>
-      </c>
-      <c r="V10" s="3">
-        <v>3</v>
-      </c>
-      <c r="Y10"/>
-      <c r="AB10"/>
-      <c r="AD10"/>
-      <c r="AF10"/>
-      <c r="AG10" s="5"/>
-    </row>
-    <row r="11" spans="1:34">
+      <c r="S10">
+        <v>2</v>
+      </c>
+      <c r="T10" s="3">
+        <v>3</v>
+      </c>
+      <c r="U10" s="2">
+        <v>2</v>
+      </c>
+      <c r="V10">
+        <v>2</v>
+      </c>
+      <c r="W10" s="3">
+        <v>3</v>
+      </c>
+      <c r="Z10"/>
+      <c r="AC10"/>
+      <c r="AE10"/>
+      <c r="AG10"/>
+      <c r="AH10" s="5"/>
+    </row>
+    <row r="11" spans="1:35">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>308</v>
+        <v>72</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G11" t="s">
-        <v>43</v>
+        <v>47</v>
+      </c>
+      <c r="H11" t="s">
+        <v>48</v>
       </c>
       <c r="J11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L11">
         <v>2</v>
@@ -2090,50 +2177,50 @@
       <c r="O11">
         <v>0</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="R11" s="2">
         <v>15</v>
       </c>
-      <c r="R11">
-        <v>2</v>
-      </c>
-      <c r="S11" s="3">
-        <v>3</v>
-      </c>
-      <c r="T11" s="2">
-        <v>2</v>
-      </c>
-      <c r="U11">
-        <v>2</v>
-      </c>
-      <c r="V11" s="3">
-        <v>3</v>
-      </c>
-      <c r="AG11" s="5"/>
-    </row>
-    <row r="12" spans="1:34">
+      <c r="S11">
+        <v>2</v>
+      </c>
+      <c r="T11" s="3">
+        <v>3</v>
+      </c>
+      <c r="U11" s="2">
+        <v>2</v>
+      </c>
+      <c r="V11">
+        <v>2</v>
+      </c>
+      <c r="W11" s="3">
+        <v>3</v>
+      </c>
+      <c r="AH11" s="5"/>
+    </row>
+    <row r="12" spans="1:35">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>309</v>
+        <v>75</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G12" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="J12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K12"/>
       <c r="L12" s="2">
@@ -2148,58 +2235,58 @@
       <c r="O12">
         <v>0</v>
       </c>
-      <c r="P12"/>
-      <c r="Q12" s="2">
+      <c r="Q12"/>
+      <c r="R12" s="2">
         <v>11</v>
       </c>
-      <c r="R12">
+      <c r="S12">
         <v>9</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>13</v>
       </c>
-      <c r="T12" s="2">
+      <c r="U12" s="2">
         <v>11</v>
       </c>
-      <c r="U12">
+      <c r="V12">
         <v>9</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>13</v>
       </c>
-      <c r="Y12"/>
-      <c r="AB12"/>
-      <c r="AD12"/>
-      <c r="AF12"/>
-      <c r="AG12" s="5"/>
-      <c r="AH12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:34">
+      <c r="Z12"/>
+      <c r="AC12"/>
+      <c r="AE12"/>
+      <c r="AG12"/>
+      <c r="AH12" s="5"/>
+      <c r="AI12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="D13" t="s">
-        <v>303</v>
+        <v>51</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K13"/>
       <c r="L13" s="2">
@@ -2214,55 +2301,55 @@
       <c r="O13">
         <v>0</v>
       </c>
-      <c r="P13"/>
-      <c r="Q13" s="2">
+      <c r="Q13"/>
+      <c r="R13" s="2">
         <v>11</v>
       </c>
-      <c r="R13">
+      <c r="S13">
         <v>11</v>
       </c>
-      <c r="S13" s="3">
+      <c r="T13" s="3">
         <v>15</v>
       </c>
-      <c r="T13" s="2">
-        <v>2</v>
-      </c>
-      <c r="U13">
+      <c r="U13" s="2">
+        <v>2</v>
+      </c>
+      <c r="V13">
         <v>7</v>
       </c>
-      <c r="V13" s="3">
+      <c r="W13" s="3">
         <v>9</v>
       </c>
-      <c r="Y13"/>
-      <c r="AB13"/>
-      <c r="AD13"/>
-      <c r="AF13"/>
-      <c r="AG13" s="5"/>
-    </row>
-    <row r="14" spans="1:34">
+      <c r="Z13"/>
+      <c r="AC13"/>
+      <c r="AE13"/>
+      <c r="AG13"/>
+      <c r="AH13" s="5"/>
+    </row>
+    <row r="14" spans="1:35">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>315</v>
+        <v>82</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F14" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K14"/>
       <c r="L14" s="2">
@@ -2277,47 +2364,47 @@
       <c r="O14">
         <v>0</v>
       </c>
-      <c r="P14"/>
-      <c r="Q14" s="2">
+      <c r="Q14"/>
+      <c r="R14" s="2">
         <v>6</v>
       </c>
-      <c r="R14">
+      <c r="S14">
         <v>6</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>8</v>
       </c>
-      <c r="V14"/>
-      <c r="Y14"/>
-      <c r="AB14"/>
-      <c r="AD14"/>
-      <c r="AF14"/>
-      <c r="AG14" s="5"/>
-    </row>
-    <row r="15" spans="1:34">
+      <c r="W14"/>
+      <c r="Z14"/>
+      <c r="AC14"/>
+      <c r="AE14"/>
+      <c r="AG14"/>
+      <c r="AH14" s="5"/>
+    </row>
+    <row r="15" spans="1:35">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="D15" t="s">
-        <v>310</v>
+        <v>85</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F15" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G15" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K15"/>
       <c r="L15" s="2">
@@ -2332,47 +2419,47 @@
       <c r="O15">
         <v>0</v>
       </c>
-      <c r="P15"/>
-      <c r="Q15" s="2">
+      <c r="Q15"/>
+      <c r="R15" s="2">
         <v>18</v>
       </c>
-      <c r="R15">
+      <c r="S15">
         <v>1.4</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1.8</v>
       </c>
-      <c r="V15"/>
-      <c r="Y15"/>
-      <c r="AB15"/>
-      <c r="AD15"/>
-      <c r="AF15"/>
-      <c r="AG15" s="5"/>
-    </row>
-    <row r="16" spans="1:34">
+      <c r="W15"/>
+      <c r="Z15"/>
+      <c r="AC15"/>
+      <c r="AE15"/>
+      <c r="AG15"/>
+      <c r="AH15" s="5"/>
+    </row>
+    <row r="16" spans="1:35">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
-        <v>311</v>
+        <v>88</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F16" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G16" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K16"/>
       <c r="L16" s="2">
@@ -2387,55 +2474,58 @@
       <c r="O16">
         <v>0</v>
       </c>
-      <c r="P16"/>
-      <c r="Q16" s="2">
+      <c r="Q16"/>
+      <c r="R16" s="2">
         <v>6</v>
       </c>
-      <c r="R16">
+      <c r="S16">
         <v>4</v>
       </c>
-      <c r="S16" s="3">
+      <c r="T16" s="3">
         <v>5</v>
       </c>
-      <c r="T16" s="2">
+      <c r="U16" s="2">
         <v>18</v>
       </c>
-      <c r="U16">
+      <c r="V16">
         <v>0.8</v>
       </c>
-      <c r="V16" s="3">
+      <c r="W16" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Y16"/>
-      <c r="AB16"/>
-      <c r="AD16"/>
-      <c r="AF16"/>
-      <c r="AG16" s="5"/>
-    </row>
-    <row r="17" spans="1:33">
+      <c r="Z16"/>
+      <c r="AC16"/>
+      <c r="AE16"/>
+      <c r="AG16"/>
+      <c r="AH16" s="5"/>
+    </row>
+    <row r="17" spans="1:34">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>313</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
-        <v>312</v>
+        <v>91</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F17" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G17" t="s">
-        <v>36</v>
+        <v>38</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="J17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K17"/>
       <c r="L17" s="2">
@@ -2450,63 +2540,66 @@
       <c r="O17">
         <v>1</v>
       </c>
-      <c r="P17"/>
-      <c r="Q17" s="2">
+      <c r="Q17"/>
+      <c r="R17" s="2">
         <v>19</v>
       </c>
-      <c r="R17">
-        <v>1</v>
-      </c>
-      <c r="S17" s="3">
-        <v>1</v>
-      </c>
-      <c r="T17" s="2">
-        <v>2</v>
-      </c>
-      <c r="U17">
+      <c r="S17">
+        <v>1</v>
+      </c>
+      <c r="T17" s="3">
+        <v>1</v>
+      </c>
+      <c r="U17" s="2">
+        <v>2</v>
+      </c>
+      <c r="V17">
         <v>4</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6</v>
       </c>
-      <c r="W17" s="2">
+      <c r="X17" s="2">
         <v>21</v>
       </c>
-      <c r="X17">
-        <v>2</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>3</v>
-      </c>
-      <c r="AB17"/>
-      <c r="AD17"/>
-      <c r="AF17"/>
-      <c r="AG17" s="6"/>
-    </row>
-    <row r="18" spans="1:33">
+      <c r="Y17">
+        <v>2</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>3</v>
+      </c>
+      <c r="AC17"/>
+      <c r="AE17"/>
+      <c r="AG17"/>
+      <c r="AH17" s="6"/>
+    </row>
+    <row r="18" spans="1:34">
       <c r="A18">
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F18" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G18" t="s">
-        <v>43</v>
+        <v>47</v>
+      </c>
+      <c r="H18" t="s">
+        <v>48</v>
       </c>
       <c r="J18" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L18">
         <v>4</v>
@@ -2520,47 +2613,47 @@
       <c r="O18">
         <v>0</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="R18" s="2">
         <v>15</v>
       </c>
-      <c r="R18">
+      <c r="S18">
         <v>5</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>7</v>
       </c>
-      <c r="AC18">
-        <v>61</v>
-      </c>
-      <c r="AD18" s="3">
+      <c r="AD18">
+        <v>63</v>
+      </c>
+      <c r="AE18" s="3">
         <v>1.5</v>
       </c>
-      <c r="AG18" s="5"/>
-    </row>
-    <row r="19" spans="1:33">
+      <c r="AH18" s="5"/>
+    </row>
+    <row r="19" spans="1:34">
       <c r="A19">
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="C19" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="D19" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F19" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G19" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="J19" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K19"/>
       <c r="L19" s="2">
@@ -2575,55 +2668,58 @@
       <c r="O19">
         <v>1</v>
       </c>
-      <c r="P19"/>
-      <c r="Q19" s="2">
+      <c r="Q19"/>
+      <c r="R19" s="2">
         <v>23</v>
       </c>
-      <c r="R19">
-        <v>1</v>
-      </c>
-      <c r="S19" s="3">
-        <v>1</v>
-      </c>
-      <c r="T19" s="2">
+      <c r="S19">
+        <v>1</v>
+      </c>
+      <c r="T19" s="3">
+        <v>1</v>
+      </c>
+      <c r="U19" s="2">
         <v>7</v>
       </c>
-      <c r="U19">
-        <v>1</v>
-      </c>
-      <c r="V19" s="3">
-        <v>2</v>
-      </c>
-      <c r="Y19"/>
-      <c r="AB19"/>
-      <c r="AD19"/>
-      <c r="AF19"/>
-      <c r="AG19" s="5"/>
-    </row>
-    <row r="20" spans="1:33">
+      <c r="V19">
+        <v>1</v>
+      </c>
+      <c r="W19" s="3">
+        <v>2</v>
+      </c>
+      <c r="Z19"/>
+      <c r="AC19"/>
+      <c r="AE19"/>
+      <c r="AG19"/>
+      <c r="AH19" s="5"/>
+    </row>
+    <row r="20" spans="1:34">
       <c r="A20">
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="D20" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F20" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G20" t="s">
-        <v>43</v>
+        <v>47</v>
+      </c>
+      <c r="H20" t="s">
+        <v>48</v>
       </c>
       <c r="J20" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L20">
         <v>6</v>
@@ -2637,50 +2733,53 @@
       <c r="O20">
         <v>0</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="2">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="2">
         <v>11</v>
       </c>
-      <c r="R20">
+      <c r="S20">
         <v>24</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>30</v>
       </c>
-      <c r="AC20">
+      <c r="AD20">
         <v>62</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>7</v>
       </c>
-      <c r="AG20" s="6"/>
-    </row>
-    <row r="21" spans="1:33">
+      <c r="AH20" s="6"/>
+    </row>
+    <row r="21" spans="1:34">
       <c r="A21">
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C21" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G21" t="s">
-        <v>43</v>
+        <v>47</v>
+      </c>
+      <c r="H21" t="s">
+        <v>48</v>
       </c>
       <c r="J21" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L21">
         <v>5</v>
@@ -2694,59 +2793,59 @@
       <c r="O21">
         <v>1</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="R21" s="2">
         <v>26</v>
       </c>
-      <c r="R21">
-        <v>2</v>
-      </c>
-      <c r="S21" s="3">
-        <v>2</v>
-      </c>
-      <c r="T21" s="2">
+      <c r="S21">
+        <v>2</v>
+      </c>
+      <c r="T21" s="3">
+        <v>2</v>
+      </c>
+      <c r="U21" s="2">
         <v>11</v>
       </c>
-      <c r="U21">
+      <c r="V21">
         <v>30</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>42</v>
       </c>
-      <c r="W21">
-        <v>2</v>
-      </c>
       <c r="X21">
+        <v>2</v>
+      </c>
+      <c r="Y21">
         <v>5</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>7</v>
       </c>
-      <c r="AG21" s="5"/>
-    </row>
-    <row r="22" spans="1:33">
+      <c r="AH21" s="5"/>
+    </row>
+    <row r="22" spans="1:34">
       <c r="A22">
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="C22" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F22" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G22" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J22" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K22"/>
       <c r="L22" s="2">
@@ -2761,55 +2860,55 @@
       <c r="O22">
         <v>1</v>
       </c>
-      <c r="P22"/>
-      <c r="Q22" s="2">
+      <c r="Q22"/>
+      <c r="R22" s="2">
         <v>6</v>
       </c>
-      <c r="R22">
-        <v>2</v>
-      </c>
-      <c r="S22" s="3">
+      <c r="S22">
+        <v>2</v>
+      </c>
+      <c r="T22" s="3">
         <v>4</v>
       </c>
-      <c r="T22" s="2">
+      <c r="U22" s="2">
         <v>28</v>
       </c>
-      <c r="U22">
-        <v>1</v>
-      </c>
-      <c r="V22" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y22"/>
-      <c r="AB22"/>
-      <c r="AD22"/>
-      <c r="AF22"/>
-      <c r="AG22" s="5"/>
-    </row>
-    <row r="23" spans="1:33">
+      <c r="V22">
+        <v>1</v>
+      </c>
+      <c r="W22" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z22"/>
+      <c r="AC22"/>
+      <c r="AE22"/>
+      <c r="AG22"/>
+      <c r="AH22" s="5"/>
+    </row>
+    <row r="23" spans="1:34">
       <c r="A23">
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="C23" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F23" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J23" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K23"/>
       <c r="L23" s="2">
@@ -2824,55 +2923,58 @@
       <c r="O23">
         <v>0</v>
       </c>
-      <c r="P23"/>
-      <c r="Q23" s="2">
+      <c r="Q23"/>
+      <c r="R23" s="2">
         <v>6</v>
       </c>
-      <c r="R23">
+      <c r="S23">
         <v>5</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7</v>
       </c>
-      <c r="T23" s="2">
-        <v>2</v>
-      </c>
-      <c r="U23">
-        <v>1</v>
-      </c>
-      <c r="V23" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y23"/>
-      <c r="AB23"/>
-      <c r="AD23"/>
-      <c r="AF23"/>
-      <c r="AG23" s="5"/>
-    </row>
-    <row r="24" spans="1:33">
+      <c r="U23" s="2">
+        <v>2</v>
+      </c>
+      <c r="V23">
+        <v>1</v>
+      </c>
+      <c r="W23" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z23"/>
+      <c r="AC23"/>
+      <c r="AE23"/>
+      <c r="AG23"/>
+      <c r="AH23" s="5"/>
+    </row>
+    <row r="24" spans="1:34">
       <c r="A24">
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="C24" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F24" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G24" t="s">
-        <v>43</v>
+        <v>47</v>
+      </c>
+      <c r="H24" t="s">
+        <v>48</v>
       </c>
       <c r="J24" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L24">
         <v>4</v>
@@ -2886,56 +2988,56 @@
       <c r="O24">
         <v>0</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="R24" s="2">
         <v>15</v>
       </c>
-      <c r="R24">
-        <v>3</v>
-      </c>
-      <c r="S24" s="3">
+      <c r="S24">
+        <v>3</v>
+      </c>
+      <c r="T24" s="3">
         <v>4</v>
       </c>
-      <c r="T24" s="2">
+      <c r="U24" s="2">
         <v>11</v>
       </c>
-      <c r="U24">
+      <c r="V24">
         <v>8</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>11</v>
       </c>
-      <c r="AC24">
+      <c r="AD24">
         <v>63</v>
       </c>
-      <c r="AD24" s="3">
-        <v>3</v>
-      </c>
-      <c r="AG24" s="5"/>
-    </row>
-    <row r="25" spans="1:33">
+      <c r="AE24" s="3">
+        <v>3</v>
+      </c>
+      <c r="AH24" s="5"/>
+    </row>
+    <row r="25" spans="1:34">
       <c r="A25">
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="C25" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="D25" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F25" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G25" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="J25" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K25"/>
       <c r="L25" s="2">
@@ -2950,47 +3052,47 @@
       <c r="O25">
         <v>0</v>
       </c>
-      <c r="P25"/>
-      <c r="Q25" s="2">
+      <c r="Q25"/>
+      <c r="R25" s="2">
         <v>7</v>
       </c>
-      <c r="R25">
-        <v>3</v>
-      </c>
-      <c r="S25" s="3">
+      <c r="S25">
+        <v>3</v>
+      </c>
+      <c r="T25" s="3">
         <v>5</v>
       </c>
-      <c r="V25"/>
-      <c r="Y25"/>
-      <c r="AB25"/>
-      <c r="AD25"/>
-      <c r="AF25"/>
-      <c r="AG25" s="5"/>
-    </row>
-    <row r="26" spans="1:33">
+      <c r="W25"/>
+      <c r="Z25"/>
+      <c r="AC25"/>
+      <c r="AE25"/>
+      <c r="AG25"/>
+      <c r="AH25" s="5"/>
+    </row>
+    <row r="26" spans="1:34">
       <c r="A26">
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="C26" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="D26" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F26" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G26" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="J26" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K26"/>
       <c r="L26" s="2">
@@ -3005,55 +3107,58 @@
       <c r="O26">
         <v>0</v>
       </c>
-      <c r="P26"/>
-      <c r="Q26" s="2">
+      <c r="Q26"/>
+      <c r="R26" s="2">
         <v>7</v>
       </c>
-      <c r="R26">
-        <v>3</v>
-      </c>
-      <c r="S26" s="3">
+      <c r="S26">
+        <v>3</v>
+      </c>
+      <c r="T26" s="3">
         <v>4</v>
       </c>
-      <c r="T26" s="2">
-        <v>2</v>
-      </c>
-      <c r="U26">
+      <c r="U26" s="2">
+        <v>2</v>
+      </c>
+      <c r="V26">
         <v>4</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>6</v>
       </c>
-      <c r="Y26"/>
-      <c r="AB26"/>
-      <c r="AD26"/>
-      <c r="AF26"/>
-      <c r="AG26" s="5"/>
-    </row>
-    <row r="27" spans="1:33">
+      <c r="Z26"/>
+      <c r="AC26"/>
+      <c r="AE26"/>
+      <c r="AG26"/>
+      <c r="AH26" s="5"/>
+    </row>
+    <row r="27" spans="1:34">
       <c r="A27">
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="C27" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="D27" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="E27" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F27" t="s">
+        <v>37</v>
+      </c>
+      <c r="G27" t="s">
+        <v>47</v>
+      </c>
+      <c r="H27" t="s">
         <v>48</v>
       </c>
-      <c r="F27" t="s">
-        <v>35</v>
-      </c>
-      <c r="G27" t="s">
-        <v>43</v>
-      </c>
       <c r="J27" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L27">
         <v>8</v>
@@ -3067,62 +3172,65 @@
       <c r="O27">
         <v>1</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="2">
+      <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2">
         <v>11</v>
       </c>
-      <c r="R27">
+      <c r="S27">
         <v>12</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>18</v>
       </c>
-      <c r="T27" s="2">
+      <c r="U27" s="2">
         <v>56</v>
       </c>
-      <c r="U27">
+      <c r="V27">
         <v>24</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>30</v>
       </c>
-      <c r="W27">
+      <c r="X27">
         <v>57</v>
       </c>
-      <c r="X27">
+      <c r="Y27">
         <v>36</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>44</v>
       </c>
-      <c r="AG27" s="6"/>
-    </row>
-    <row r="28" spans="1:33">
+      <c r="AH27" s="6"/>
+    </row>
+    <row r="28" spans="1:34">
       <c r="A28">
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="C28" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="D28" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F28" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G28" t="s">
-        <v>43</v>
+        <v>47</v>
+      </c>
+      <c r="H28" t="s">
+        <v>116</v>
       </c>
       <c r="J28" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L28">
         <v>1</v>
@@ -3136,47 +3244,47 @@
       <c r="O28">
         <v>0</v>
       </c>
-      <c r="Q28" s="2">
-        <v>2</v>
-      </c>
-      <c r="R28">
+      <c r="R28" s="2">
+        <v>2</v>
+      </c>
+      <c r="S28">
         <v>6</v>
       </c>
-      <c r="S28" s="3">
+      <c r="T28" s="3">
         <v>8</v>
       </c>
-      <c r="AC28">
+      <c r="AD28">
         <v>21</v>
       </c>
-      <c r="AD28" s="3">
+      <c r="AE28" s="3">
         <v>12</v>
       </c>
-      <c r="AG28" s="5"/>
-    </row>
-    <row r="29" spans="1:33">
+      <c r="AH28" s="5"/>
+    </row>
+    <row r="29" spans="1:34">
       <c r="A29">
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="C29" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="D29" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F29" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G29" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J29" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K29"/>
       <c r="L29" s="2">
@@ -3191,63 +3299,63 @@
       <c r="O29">
         <v>1</v>
       </c>
-      <c r="P29"/>
-      <c r="Q29" s="2">
+      <c r="Q29"/>
+      <c r="R29" s="2">
         <v>32</v>
       </c>
-      <c r="R29">
+      <c r="S29">
         <v>30</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>30</v>
       </c>
-      <c r="T29" s="2">
-        <v>2</v>
-      </c>
-      <c r="U29">
-        <v>3</v>
-      </c>
-      <c r="V29" s="3">
+      <c r="U29" s="2">
+        <v>2</v>
+      </c>
+      <c r="V29">
+        <v>3</v>
+      </c>
+      <c r="W29" s="3">
         <v>5</v>
       </c>
-      <c r="W29" s="2">
+      <c r="X29" s="2">
         <v>21</v>
       </c>
-      <c r="X29">
-        <v>2</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>3</v>
-      </c>
-      <c r="AB29"/>
-      <c r="AD29"/>
-      <c r="AF29"/>
-      <c r="AG29" s="5"/>
-    </row>
-    <row r="30" spans="1:33">
+      <c r="Y29">
+        <v>2</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>3</v>
+      </c>
+      <c r="AC29"/>
+      <c r="AE29"/>
+      <c r="AG29"/>
+      <c r="AH29" s="5"/>
+    </row>
+    <row r="30" spans="1:34">
       <c r="A30">
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="C30" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="D30" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F30" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J30" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K30"/>
       <c r="L30" s="2">
@@ -3262,55 +3370,55 @@
       <c r="O30">
         <v>1</v>
       </c>
-      <c r="P30"/>
-      <c r="Q30" s="2">
+      <c r="Q30"/>
+      <c r="R30" s="2">
         <v>33</v>
       </c>
-      <c r="R30">
+      <c r="S30">
         <v>50</v>
       </c>
-      <c r="S30" s="3">
+      <c r="T30" s="3">
         <v>70</v>
       </c>
-      <c r="T30" s="2">
-        <v>2</v>
-      </c>
-      <c r="U30">
-        <v>2</v>
-      </c>
-      <c r="V30" s="3">
+      <c r="U30" s="2">
+        <v>2</v>
+      </c>
+      <c r="V30">
+        <v>2</v>
+      </c>
+      <c r="W30" s="3">
         <v>4</v>
       </c>
-      <c r="Y30"/>
-      <c r="AB30"/>
-      <c r="AD30"/>
-      <c r="AF30"/>
-      <c r="AG30" s="6"/>
-    </row>
-    <row r="31" spans="1:33">
+      <c r="Z30"/>
+      <c r="AC30"/>
+      <c r="AE30"/>
+      <c r="AG30"/>
+      <c r="AH30" s="6"/>
+    </row>
+    <row r="31" spans="1:34">
       <c r="A31">
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="C31" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="D31" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F31" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G31" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J31" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K31"/>
       <c r="L31" s="2">
@@ -3325,55 +3433,55 @@
       <c r="O31">
         <v>1</v>
       </c>
-      <c r="P31"/>
-      <c r="Q31" s="2">
+      <c r="Q31"/>
+      <c r="R31" s="2">
         <v>33</v>
       </c>
-      <c r="R31">
+      <c r="S31">
         <v>20</v>
       </c>
-      <c r="S31" s="3">
+      <c r="T31" s="3">
         <v>30</v>
       </c>
-      <c r="T31" s="2">
+      <c r="U31" s="2">
         <v>35</v>
       </c>
-      <c r="U31">
-        <v>1</v>
-      </c>
-      <c r="V31" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y31"/>
-      <c r="AB31"/>
-      <c r="AD31"/>
-      <c r="AF31"/>
-      <c r="AG31" s="6"/>
-    </row>
-    <row r="32" spans="1:33">
+      <c r="V31">
+        <v>1</v>
+      </c>
+      <c r="W31" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z31"/>
+      <c r="AC31"/>
+      <c r="AE31"/>
+      <c r="AG31"/>
+      <c r="AH31" s="6"/>
+    </row>
+    <row r="32" spans="1:34">
       <c r="A32">
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="C32" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="D32" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F32" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G32" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J32" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K32"/>
       <c r="L32" s="2">
@@ -3388,38 +3496,41 @@
       <c r="O32">
         <v>1</v>
       </c>
-      <c r="P32"/>
-      <c r="S32"/>
-      <c r="V32"/>
-      <c r="Y32"/>
-      <c r="AB32"/>
-      <c r="AD32"/>
-      <c r="AF32"/>
-    </row>
-    <row r="33" spans="1:32">
+      <c r="Q32"/>
+      <c r="T32"/>
+      <c r="W32"/>
+      <c r="Z32"/>
+      <c r="AC32"/>
+      <c r="AE32"/>
+      <c r="AG32"/>
+    </row>
+    <row r="33" spans="1:33">
       <c r="A33">
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="C33" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="D33" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="E33" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F33" t="s">
+        <v>37</v>
+      </c>
+      <c r="G33" t="s">
+        <v>47</v>
+      </c>
+      <c r="H33" t="s">
         <v>48</v>
       </c>
-      <c r="F33" t="s">
-        <v>35</v>
-      </c>
-      <c r="G33" t="s">
-        <v>43</v>
-      </c>
       <c r="J33" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L33">
         <v>8</v>
@@ -3433,46 +3544,49 @@
       <c r="O33">
         <v>1</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="R33" s="2">
         <v>11</v>
       </c>
-      <c r="R33">
+      <c r="S33">
         <v>38</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>52</v>
       </c>
-      <c r="AC33">
+      <c r="AD33">
         <v>64</v>
       </c>
-      <c r="AD33" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:32">
+      <c r="AE33" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33">
       <c r="A34">
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="C34" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="D34" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F34" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G34" t="s">
-        <v>43</v>
+        <v>47</v>
+      </c>
+      <c r="H34" t="s">
+        <v>48</v>
       </c>
       <c r="J34" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L34">
         <v>3</v>
@@ -3486,43 +3600,46 @@
       <c r="O34">
         <v>0</v>
       </c>
-      <c r="P34" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="2">
         <v>15</v>
       </c>
-      <c r="R34">
-        <v>3</v>
-      </c>
-      <c r="S34" s="3">
+      <c r="S34">
+        <v>3</v>
+      </c>
+      <c r="T34" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:32">
+    <row r="35" spans="1:33">
       <c r="A35">
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="C35" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="D35" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F35" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G35" t="s">
-        <v>43</v>
+        <v>47</v>
+      </c>
+      <c r="H35" t="s">
+        <v>116</v>
       </c>
       <c r="J35" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L35">
         <v>3</v>
@@ -3536,17 +3653,17 @@
       <c r="O35">
         <v>0</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="R35" s="2">
         <v>11</v>
       </c>
-      <c r="R35">
+      <c r="S35">
         <v>18</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:32">
+    <row r="36" spans="1:33">
       <c r="A36">
         <v>37</v>
       </c>
@@ -3554,22 +3671,25 @@
         <v>144</v>
       </c>
       <c r="C36" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="D36" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F36" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G36" t="s">
-        <v>43</v>
+        <v>47</v>
+      </c>
+      <c r="H36" t="s">
+        <v>48</v>
       </c>
       <c r="J36" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L36">
         <v>3</v>
@@ -3583,49 +3703,49 @@
       <c r="O36">
         <v>0</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="R36" s="2">
         <v>15</v>
       </c>
-      <c r="R36">
-        <v>3</v>
-      </c>
-      <c r="S36" s="3">
+      <c r="S36">
+        <v>3</v>
+      </c>
+      <c r="T36" s="3">
         <v>4</v>
       </c>
-      <c r="T36" s="2">
-        <v>2</v>
-      </c>
-      <c r="U36">
+      <c r="U36" s="2">
+        <v>2</v>
+      </c>
+      <c r="V36">
         <v>6</v>
       </c>
-      <c r="V36" s="3">
+      <c r="W36" s="3">
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:32">
+    <row r="37" spans="1:33">
       <c r="A37">
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="C37" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="D37" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F37" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G37" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="J37" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K37"/>
       <c r="L37" s="2">
@@ -3640,54 +3760,54 @@
       <c r="O37">
         <v>0</v>
       </c>
-      <c r="P37"/>
-      <c r="Q37" s="2">
+      <c r="Q37"/>
+      <c r="R37" s="2">
         <v>7</v>
       </c>
-      <c r="R37">
-        <v>3</v>
-      </c>
-      <c r="S37" s="3">
+      <c r="S37">
+        <v>3</v>
+      </c>
+      <c r="T37" s="3">
         <v>4</v>
       </c>
-      <c r="T37" s="2">
-        <v>2</v>
-      </c>
-      <c r="U37">
+      <c r="U37" s="2">
+        <v>2</v>
+      </c>
+      <c r="V37">
         <v>6</v>
       </c>
-      <c r="V37" s="3">
+      <c r="W37" s="3">
         <v>8</v>
       </c>
-      <c r="Y37"/>
-      <c r="AB37"/>
-      <c r="AD37"/>
-      <c r="AF37"/>
-    </row>
-    <row r="38" spans="1:32">
+      <c r="Z37"/>
+      <c r="AC37"/>
+      <c r="AE37"/>
+      <c r="AG37"/>
+    </row>
+    <row r="38" spans="1:33">
       <c r="A38">
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="C38" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="D38" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F38" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G38" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J38" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K38"/>
       <c r="L38" s="2">
@@ -3702,54 +3822,54 @@
       <c r="O38">
         <v>1</v>
       </c>
-      <c r="P38"/>
-      <c r="Q38" s="2">
+      <c r="Q38"/>
+      <c r="R38" s="2">
         <v>21</v>
       </c>
-      <c r="R38">
+      <c r="S38">
         <v>4</v>
       </c>
-      <c r="S38" s="3">
+      <c r="T38" s="3">
         <v>5</v>
       </c>
-      <c r="T38" s="2">
-        <v>2</v>
-      </c>
-      <c r="U38">
-        <v>3</v>
-      </c>
-      <c r="V38" s="3">
+      <c r="U38" s="2">
+        <v>2</v>
+      </c>
+      <c r="V38">
+        <v>3</v>
+      </c>
+      <c r="W38" s="3">
         <v>5</v>
       </c>
-      <c r="Y38"/>
-      <c r="AB38"/>
-      <c r="AD38"/>
-      <c r="AF38"/>
-    </row>
-    <row r="39" spans="1:32">
+      <c r="Z38"/>
+      <c r="AC38"/>
+      <c r="AE38"/>
+      <c r="AG38"/>
+    </row>
+    <row r="39" spans="1:33">
       <c r="A39">
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="C39" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="D39" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F39" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G39" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J39" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K39"/>
       <c r="L39" s="2">
@@ -3764,54 +3884,54 @@
       <c r="O39">
         <v>1</v>
       </c>
-      <c r="P39"/>
-      <c r="Q39" s="2">
+      <c r="Q39"/>
+      <c r="R39" s="2">
         <v>5</v>
       </c>
-      <c r="R39">
-        <v>1</v>
-      </c>
-      <c r="S39" s="3">
-        <v>2</v>
-      </c>
-      <c r="T39" s="2">
-        <v>2</v>
-      </c>
-      <c r="U39">
+      <c r="S39">
+        <v>1</v>
+      </c>
+      <c r="T39" s="3">
+        <v>2</v>
+      </c>
+      <c r="U39" s="2">
+        <v>2</v>
+      </c>
+      <c r="V39">
         <v>6</v>
       </c>
-      <c r="V39" s="3">
+      <c r="W39" s="3">
         <v>7</v>
       </c>
-      <c r="Y39"/>
-      <c r="AB39"/>
-      <c r="AD39"/>
-      <c r="AF39"/>
-    </row>
-    <row r="40" spans="1:32">
+      <c r="Z39"/>
+      <c r="AC39"/>
+      <c r="AE39"/>
+      <c r="AG39"/>
+    </row>
+    <row r="40" spans="1:33">
       <c r="A40">
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="C40" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="D40" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F40" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G40" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="J40" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K40"/>
       <c r="L40" s="2">
@@ -3826,54 +3946,54 @@
       <c r="O40">
         <v>1</v>
       </c>
-      <c r="P40"/>
-      <c r="Q40" s="2">
+      <c r="Q40"/>
+      <c r="R40" s="2">
         <v>7</v>
       </c>
-      <c r="R40">
+      <c r="S40">
         <v>4</v>
       </c>
-      <c r="S40" s="3">
+      <c r="T40" s="3">
         <v>5</v>
       </c>
-      <c r="T40" s="2">
+      <c r="U40" s="2">
         <v>38</v>
       </c>
-      <c r="U40">
+      <c r="V40">
         <v>4</v>
       </c>
-      <c r="V40" s="3">
+      <c r="W40" s="3">
         <v>5</v>
       </c>
-      <c r="Y40"/>
-      <c r="AB40"/>
-      <c r="AD40"/>
-      <c r="AF40"/>
-    </row>
-    <row r="41" spans="1:32">
+      <c r="Z40"/>
+      <c r="AC40"/>
+      <c r="AE40"/>
+      <c r="AG40"/>
+    </row>
+    <row r="41" spans="1:33">
       <c r="A41">
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="C41" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="D41" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F41" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G41" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J41" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K41"/>
       <c r="L41" s="2">
@@ -3888,54 +4008,54 @@
       <c r="O41">
         <v>0</v>
       </c>
-      <c r="P41"/>
-      <c r="Q41" s="2">
+      <c r="Q41"/>
+      <c r="R41" s="2">
         <v>6</v>
       </c>
-      <c r="R41">
-        <v>3</v>
-      </c>
-      <c r="S41" s="3">
-        <v>3</v>
-      </c>
-      <c r="T41" s="2">
+      <c r="S41">
+        <v>3</v>
+      </c>
+      <c r="T41" s="3">
+        <v>3</v>
+      </c>
+      <c r="U41" s="2">
         <v>39</v>
       </c>
-      <c r="U41">
-        <v>2</v>
-      </c>
-      <c r="V41" s="3">
-        <v>3</v>
-      </c>
-      <c r="Y41"/>
-      <c r="AB41"/>
-      <c r="AD41"/>
-      <c r="AF41"/>
-    </row>
-    <row r="42" spans="1:32">
+      <c r="V41">
+        <v>2</v>
+      </c>
+      <c r="W41" s="3">
+        <v>3</v>
+      </c>
+      <c r="Z41"/>
+      <c r="AC41"/>
+      <c r="AE41"/>
+      <c r="AG41"/>
+    </row>
+    <row r="42" spans="1:33">
       <c r="A42">
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="C42" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="D42" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F42" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G42" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="J42" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K42"/>
       <c r="L42" s="2">
@@ -3950,54 +4070,54 @@
       <c r="O42">
         <v>1</v>
       </c>
-      <c r="P42"/>
-      <c r="Q42" s="2">
+      <c r="Q42"/>
+      <c r="R42" s="2">
         <v>7</v>
       </c>
-      <c r="R42">
-        <v>1</v>
-      </c>
-      <c r="S42" s="3">
-        <v>3</v>
-      </c>
-      <c r="T42" s="2">
+      <c r="S42">
+        <v>1</v>
+      </c>
+      <c r="T42" s="3">
+        <v>3</v>
+      </c>
+      <c r="U42" s="2">
         <v>41</v>
       </c>
-      <c r="U42">
-        <v>1</v>
-      </c>
-      <c r="V42" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y42"/>
-      <c r="AB42"/>
-      <c r="AD42"/>
-      <c r="AF42"/>
-    </row>
-    <row r="43" spans="1:32">
+      <c r="V42">
+        <v>1</v>
+      </c>
+      <c r="W42" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z42"/>
+      <c r="AC42"/>
+      <c r="AE42"/>
+      <c r="AG42"/>
+    </row>
+    <row r="43" spans="1:33">
       <c r="A43">
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="C43" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="D43" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F43" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G43" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J43" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K43"/>
       <c r="L43" s="2">
@@ -4012,62 +4132,65 @@
       <c r="O43">
         <v>1</v>
       </c>
-      <c r="P43"/>
-      <c r="Q43" s="2">
+      <c r="Q43"/>
+      <c r="R43" s="2">
         <v>6</v>
       </c>
-      <c r="R43">
+      <c r="S43">
         <v>5</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5</v>
       </c>
-      <c r="T43" s="2">
+      <c r="U43" s="2">
         <v>14</v>
       </c>
-      <c r="U43">
-        <v>1</v>
-      </c>
-      <c r="V43" s="3">
-        <v>1</v>
-      </c>
-      <c r="W43" s="2">
+      <c r="V43">
+        <v>1</v>
+      </c>
+      <c r="W43" s="3">
+        <v>1</v>
+      </c>
+      <c r="X43" s="2">
         <v>18</v>
       </c>
-      <c r="X43">
+      <c r="Y43">
         <v>0.9</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1.2</v>
       </c>
-      <c r="AB43"/>
-      <c r="AD43"/>
-      <c r="AF43"/>
-    </row>
-    <row r="44" spans="1:32">
+      <c r="AC43"/>
+      <c r="AE43"/>
+      <c r="AG43"/>
+    </row>
+    <row r="44" spans="1:33">
       <c r="A44">
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="C44" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="D44" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F44" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G44" t="s">
-        <v>43</v>
+        <v>47</v>
+      </c>
+      <c r="H44" t="s">
+        <v>48</v>
       </c>
       <c r="J44" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L44">
         <v>6</v>
@@ -4081,49 +4204,49 @@
       <c r="O44">
         <v>1</v>
       </c>
-      <c r="Q44" s="2">
+      <c r="R44" s="2">
         <v>15</v>
       </c>
-      <c r="R44">
-        <v>2</v>
-      </c>
-      <c r="S44" s="3">
-        <v>2</v>
-      </c>
-      <c r="T44" s="2">
+      <c r="S44">
+        <v>2</v>
+      </c>
+      <c r="T44" s="3">
+        <v>2</v>
+      </c>
+      <c r="U44" s="2">
         <v>42</v>
       </c>
-      <c r="U44">
+      <c r="V44">
         <v>8</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:32">
+    <row r="45" spans="1:33">
       <c r="A45">
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="C45" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="D45" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F45" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G45" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="J45" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K45"/>
       <c r="L45" s="2">
@@ -4138,62 +4261,62 @@
       <c r="O45">
         <v>1</v>
       </c>
-      <c r="P45"/>
-      <c r="Q45" s="2">
+      <c r="Q45"/>
+      <c r="R45" s="2">
         <v>7</v>
       </c>
-      <c r="R45">
+      <c r="S45">
         <v>7</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>9</v>
       </c>
-      <c r="T45" s="2">
+      <c r="U45" s="2">
         <v>26</v>
       </c>
-      <c r="U45">
-        <v>2</v>
-      </c>
-      <c r="V45" s="3">
-        <v>2</v>
-      </c>
-      <c r="W45" s="2">
-        <v>2</v>
-      </c>
-      <c r="X45">
+      <c r="V45">
+        <v>2</v>
+      </c>
+      <c r="W45" s="3">
+        <v>2</v>
+      </c>
+      <c r="X45" s="2">
+        <v>2</v>
+      </c>
+      <c r="Y45">
         <v>7</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>8</v>
       </c>
-      <c r="AB45"/>
-      <c r="AD45"/>
-      <c r="AF45"/>
-    </row>
-    <row r="46" spans="1:32">
+      <c r="AC45"/>
+      <c r="AE45"/>
+      <c r="AG45"/>
+    </row>
+    <row r="46" spans="1:33">
       <c r="A46">
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="C46" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="D46" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F46" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G46" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J46" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K46"/>
       <c r="L46" s="2">
@@ -4208,62 +4331,62 @@
       <c r="O46">
         <v>1</v>
       </c>
-      <c r="P46"/>
-      <c r="Q46" s="2">
+      <c r="Q46"/>
+      <c r="R46" s="2">
         <v>32</v>
       </c>
-      <c r="R46">
+      <c r="S46">
         <v>40</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>40</v>
       </c>
-      <c r="T46" s="2">
+      <c r="U46" s="2">
         <v>33</v>
       </c>
-      <c r="U46">
+      <c r="V46">
         <v>30</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>30</v>
       </c>
-      <c r="W46" s="2">
+      <c r="X46" s="2">
         <v>19</v>
       </c>
-      <c r="X46">
-        <v>1</v>
-      </c>
-      <c r="Y46" s="3">
-        <v>1</v>
-      </c>
-      <c r="AB46"/>
-      <c r="AD46"/>
-      <c r="AF46"/>
-    </row>
-    <row r="47" spans="1:32">
+      <c r="Y46">
+        <v>1</v>
+      </c>
+      <c r="Z46" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC46"/>
+      <c r="AE46"/>
+      <c r="AG46"/>
+    </row>
+    <row r="47" spans="1:33">
       <c r="A47">
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="C47" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="D47" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F47" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G47" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="J47" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K47"/>
       <c r="L47" s="2">
@@ -4278,23 +4401,23 @@
       <c r="O47">
         <v>0</v>
       </c>
-      <c r="P47"/>
-      <c r="Q47" s="2">
+      <c r="Q47"/>
+      <c r="R47" s="2">
         <v>11</v>
       </c>
-      <c r="R47">
+      <c r="S47">
         <v>10</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>14</v>
       </c>
-      <c r="V47"/>
-      <c r="Y47"/>
-      <c r="AB47"/>
-      <c r="AD47"/>
-      <c r="AF47"/>
-    </row>
-    <row r="48" spans="1:32">
+      <c r="W47"/>
+      <c r="Z47"/>
+      <c r="AC47"/>
+      <c r="AE47"/>
+      <c r="AG47"/>
+    </row>
+    <row r="48" spans="1:33">
       <c r="A48">
         <v>49</v>
       </c>
@@ -4302,22 +4425,22 @@
         <v>123</v>
       </c>
       <c r="C48" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="D48" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F48" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G48" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J48" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K48"/>
       <c r="L48" s="2">
@@ -4332,54 +4455,57 @@
       <c r="O48">
         <v>0</v>
       </c>
-      <c r="P48"/>
-      <c r="Q48" s="2">
+      <c r="Q48"/>
+      <c r="R48" s="2">
         <v>11</v>
       </c>
-      <c r="R48">
+      <c r="S48">
         <v>8</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11</v>
       </c>
-      <c r="T48" s="2">
+      <c r="U48" s="2">
         <v>6</v>
       </c>
-      <c r="U48">
-        <v>3</v>
-      </c>
-      <c r="V48" s="3">
-        <v>3</v>
-      </c>
-      <c r="Y48"/>
-      <c r="AB48"/>
-      <c r="AD48"/>
-      <c r="AF48"/>
-    </row>
-    <row r="49" spans="1:32">
+      <c r="V48">
+        <v>3</v>
+      </c>
+      <c r="W48" s="3">
+        <v>3</v>
+      </c>
+      <c r="Z48"/>
+      <c r="AC48"/>
+      <c r="AE48"/>
+      <c r="AG48"/>
+    </row>
+    <row r="49" spans="1:33">
       <c r="A49">
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="C49" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="D49" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F49" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G49" t="s">
-        <v>43</v>
+        <v>47</v>
+      </c>
+      <c r="H49" t="s">
+        <v>116</v>
       </c>
       <c r="J49" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L49">
         <v>4</v>
@@ -4393,49 +4519,49 @@
       <c r="O49">
         <v>0</v>
       </c>
-      <c r="Q49" s="2">
+      <c r="R49" s="2">
         <v>11</v>
       </c>
-      <c r="R49">
+      <c r="S49">
         <v>7</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>11</v>
       </c>
-      <c r="T49" s="2">
+      <c r="U49" s="2">
         <v>45</v>
       </c>
-      <c r="U49">
-        <v>2</v>
-      </c>
-      <c r="V49" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:32">
+      <c r="V49">
+        <v>2</v>
+      </c>
+      <c r="W49" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:33">
       <c r="A50">
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="C50" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="D50" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F50" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G50" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J50" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K50"/>
       <c r="L50" s="2">
@@ -4450,54 +4576,54 @@
       <c r="O50">
         <v>1</v>
       </c>
-      <c r="P50"/>
-      <c r="Q50" s="2">
+      <c r="Q50"/>
+      <c r="R50" s="2">
         <v>6</v>
       </c>
-      <c r="R50">
+      <c r="S50">
         <v>5</v>
       </c>
-      <c r="S50" s="3">
+      <c r="T50" s="3">
         <v>7</v>
       </c>
-      <c r="T50" s="2">
+      <c r="U50" s="2">
         <v>18</v>
       </c>
-      <c r="U50">
+      <c r="V50">
         <v>1.1000000000000001</v>
       </c>
-      <c r="V50" s="3">
+      <c r="W50" s="3">
         <v>1.7</v>
       </c>
-      <c r="Y50"/>
-      <c r="AB50"/>
-      <c r="AD50"/>
-      <c r="AF50"/>
-    </row>
-    <row r="51" spans="1:32">
+      <c r="Z50"/>
+      <c r="AC50"/>
+      <c r="AE50"/>
+      <c r="AG50"/>
+    </row>
+    <row r="51" spans="1:33">
       <c r="A51">
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="C51" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="D51" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F51" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G51" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J51" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K51"/>
       <c r="L51" s="2">
@@ -4512,54 +4638,54 @@
       <c r="O51">
         <v>1</v>
       </c>
-      <c r="P51"/>
-      <c r="Q51" s="2">
+      <c r="Q51"/>
+      <c r="R51" s="2">
         <v>6</v>
       </c>
-      <c r="R51">
-        <v>1</v>
-      </c>
-      <c r="S51" s="3">
-        <v>3</v>
-      </c>
-      <c r="T51" s="2">
+      <c r="S51">
+        <v>1</v>
+      </c>
+      <c r="T51" s="3">
+        <v>3</v>
+      </c>
+      <c r="U51" s="2">
         <v>49</v>
       </c>
-      <c r="U51">
-        <v>1</v>
-      </c>
-      <c r="V51" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y51"/>
-      <c r="AB51"/>
-      <c r="AD51"/>
-      <c r="AF51"/>
-    </row>
-    <row r="52" spans="1:32">
+      <c r="V51">
+        <v>1</v>
+      </c>
+      <c r="W51" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z51"/>
+      <c r="AC51"/>
+      <c r="AE51"/>
+      <c r="AG51"/>
+    </row>
+    <row r="52" spans="1:33">
       <c r="A52">
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="C52" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="D52" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F52" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G52" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J52" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K52"/>
       <c r="L52" s="2">
@@ -4574,54 +4700,57 @@
       <c r="O52">
         <v>1</v>
       </c>
-      <c r="P52"/>
-      <c r="Q52" s="2">
+      <c r="Q52"/>
+      <c r="R52" s="2">
         <v>9</v>
       </c>
-      <c r="R52">
-        <v>2</v>
-      </c>
-      <c r="S52" s="3">
-        <v>2</v>
-      </c>
-      <c r="T52" s="2">
+      <c r="S52">
+        <v>2</v>
+      </c>
+      <c r="T52" s="3">
+        <v>2</v>
+      </c>
+      <c r="U52" s="2">
         <v>21</v>
       </c>
-      <c r="U52">
-        <v>2</v>
-      </c>
-      <c r="V52" s="3">
-        <v>2</v>
-      </c>
-      <c r="Y52"/>
-      <c r="AB52"/>
-      <c r="AD52"/>
-      <c r="AF52"/>
-    </row>
-    <row r="53" spans="1:32">
+      <c r="V52">
+        <v>2</v>
+      </c>
+      <c r="W52" s="3">
+        <v>2</v>
+      </c>
+      <c r="Z52"/>
+      <c r="AC52"/>
+      <c r="AE52"/>
+      <c r="AG52"/>
+    </row>
+    <row r="53" spans="1:33">
       <c r="A53">
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="C53" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="D53" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="E53" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F53" t="s">
+        <v>37</v>
+      </c>
+      <c r="G53" t="s">
+        <v>47</v>
+      </c>
+      <c r="H53" t="s">
         <v>48</v>
       </c>
-      <c r="F53" t="s">
-        <v>35</v>
-      </c>
-      <c r="G53" t="s">
-        <v>43</v>
-      </c>
       <c r="J53" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L53">
         <v>5</v>
@@ -4635,52 +4764,55 @@
       <c r="O53">
         <v>1</v>
       </c>
-      <c r="P53" s="3">
+      <c r="Q53" s="3">
         <v>6</v>
       </c>
-      <c r="Q53">
+      <c r="R53">
         <v>50</v>
       </c>
-      <c r="R53">
-        <v>3</v>
-      </c>
-      <c r="S53" s="3">
+      <c r="S53">
+        <v>3</v>
+      </c>
+      <c r="T53" s="3">
         <v>4</v>
       </c>
-      <c r="T53">
+      <c r="U53">
         <v>51</v>
       </c>
-      <c r="U53">
+      <c r="V53">
         <v>-0.5</v>
       </c>
-      <c r="V53" s="3">
+      <c r="W53" s="3">
         <v>-0.5</v>
       </c>
     </row>
-    <row r="54" spans="1:32">
+    <row r="54" spans="1:33">
       <c r="A54">
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="C54" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="D54" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F54" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G54" t="s">
-        <v>43</v>
+        <v>47</v>
+      </c>
+      <c r="H54" t="s">
+        <v>48</v>
       </c>
       <c r="J54" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="K54" s="3">
         <v>14</v>
@@ -4697,58 +4829,61 @@
       <c r="O54">
         <v>1</v>
       </c>
-      <c r="Q54">
+      <c r="R54">
         <v>15</v>
       </c>
-      <c r="R54">
-        <v>3</v>
-      </c>
-      <c r="S54" s="3">
+      <c r="S54">
+        <v>3</v>
+      </c>
+      <c r="T54" s="3">
         <v>4</v>
       </c>
-      <c r="T54">
+      <c r="U54">
         <v>14</v>
       </c>
-      <c r="U54">
-        <v>1</v>
-      </c>
-      <c r="V54" s="3">
-        <v>1</v>
-      </c>
-      <c r="W54">
+      <c r="V54">
+        <v>1</v>
+      </c>
+      <c r="W54" s="3">
+        <v>1</v>
+      </c>
+      <c r="X54">
         <v>52</v>
       </c>
-      <c r="X54">
-        <v>3</v>
-      </c>
-      <c r="Y54" s="3">
+      <c r="Y54">
+        <v>3</v>
+      </c>
+      <c r="Z54" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:32">
+    <row r="55" spans="1:33">
       <c r="A55">
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="C55" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="D55" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F55" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G55" t="s">
-        <v>43</v>
+        <v>47</v>
+      </c>
+      <c r="H55" t="s">
+        <v>48</v>
       </c>
       <c r="J55" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L55">
         <v>4</v>
@@ -4762,50 +4897,53 @@
       <c r="O55">
         <v>1</v>
       </c>
-      <c r="Q55">
+      <c r="R55">
         <v>15</v>
       </c>
-      <c r="R55">
-        <v>1</v>
-      </c>
-      <c r="S55" s="3">
-        <v>3</v>
-      </c>
-      <c r="T55">
+      <c r="S55">
+        <v>1</v>
+      </c>
+      <c r="T55" s="3">
+        <v>3</v>
+      </c>
+      <c r="U55">
         <v>60</v>
       </c>
-      <c r="U55">
-        <v>1</v>
-      </c>
-      <c r="V55" s="3">
-        <v>1</v>
-      </c>
-      <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="1:32">
+      <c r="V55">
+        <v>1</v>
+      </c>
+      <c r="W55" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="1:33">
       <c r="A56">
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="C56" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="D56" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F56" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G56" t="s">
-        <v>43</v>
+        <v>47</v>
+      </c>
+      <c r="H56" t="s">
+        <v>116</v>
       </c>
       <c r="J56" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="K56" s="3">
         <v>3</v>
@@ -4822,59 +4960,62 @@
       <c r="O56">
         <v>1</v>
       </c>
-      <c r="Q56">
+      <c r="R56">
         <v>45</v>
       </c>
-      <c r="R56">
-        <v>3</v>
-      </c>
-      <c r="S56" s="3">
+      <c r="S56">
+        <v>3</v>
+      </c>
+      <c r="T56" s="3">
         <v>4</v>
       </c>
-      <c r="T56">
+      <c r="U56">
         <v>11</v>
       </c>
-      <c r="U56">
+      <c r="V56">
         <v>12</v>
       </c>
-      <c r="V56" s="3">
+      <c r="W56" s="3">
         <v>18</v>
       </c>
-      <c r="W56">
+      <c r="X56">
         <v>14</v>
       </c>
-      <c r="X56">
-        <v>1</v>
-      </c>
-      <c r="Y56" s="3">
-        <v>1</v>
-      </c>
-      <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="1:32">
+      <c r="Y56">
+        <v>1</v>
+      </c>
+      <c r="Z56" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="1:33">
       <c r="A57">
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="C57" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="D57" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F57" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G57" t="s">
-        <v>43</v>
+        <v>47</v>
+      </c>
+      <c r="H57" t="s">
+        <v>116</v>
       </c>
       <c r="J57" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="K57" s="3">
         <v>3</v>
@@ -4891,49 +5032,52 @@
       <c r="O57">
         <v>1</v>
       </c>
-      <c r="Q57">
-        <v>2</v>
-      </c>
       <c r="R57">
+        <v>2</v>
+      </c>
+      <c r="S57">
         <v>5</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6</v>
       </c>
-      <c r="T57">
-        <v>2</v>
-      </c>
       <c r="U57">
+        <v>2</v>
+      </c>
+      <c r="V57">
         <v>5</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:32">
+    <row r="58" spans="1:33">
       <c r="A58">
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="C58" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="D58" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F58" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G58" t="s">
-        <v>43</v>
+        <v>47</v>
+      </c>
+      <c r="H58" t="s">
+        <v>116</v>
       </c>
       <c r="J58" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L58">
         <v>3</v>
@@ -4948,30 +5092,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:32">
+    <row r="59" spans="1:33">
       <c r="A59">
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="C59" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="D59" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F59" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G59" t="s">
-        <v>43</v>
+        <v>47</v>
+      </c>
+      <c r="H59" t="s">
+        <v>116</v>
       </c>
       <c r="J59" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L59">
         <v>4</v>
@@ -4985,40 +5132,43 @@
       <c r="O59">
         <v>0</v>
       </c>
-      <c r="Q59">
-        <v>2</v>
-      </c>
       <c r="R59">
+        <v>2</v>
+      </c>
+      <c r="S59">
         <v>7</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:32">
+    <row r="60" spans="1:33">
       <c r="A60">
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="C60" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="D60" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F60" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G60" t="s">
-        <v>43</v>
+        <v>47</v>
+      </c>
+      <c r="H60" t="s">
+        <v>116</v>
       </c>
       <c r="J60" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L60">
         <v>2</v>
@@ -5033,27 +5183,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:32">
+    <row r="61" spans="1:33">
       <c r="A61">
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="C61" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="D61" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F61" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="G61" t="s">
+        <v>47</v>
+      </c>
+      <c r="H61" t="s">
+        <v>116</v>
       </c>
       <c r="J61" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="K61" s="3">
         <v>14</v>
@@ -5079,7 +5235,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
@@ -5104,22 +5260,22 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E1" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="G1" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="H1" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="I1" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5127,13 +5283,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="C2" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="D2" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="I2">
         <v>-1</v>
@@ -5144,19 +5300,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="C3" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="D3" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="E3" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="F3" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -5167,16 +5323,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="C4" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="D4" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="E4" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -5187,16 +5343,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="C5" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="D5" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="E5" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -5207,13 +5363,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="C6" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="D6" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -5224,16 +5380,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="C7" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="D7" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="E7" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -5244,13 +5400,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="C8" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="D8" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -5264,13 +5420,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="C9" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="D9" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -5284,13 +5440,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="C10" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="D10" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -5304,13 +5460,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="C11" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="D11" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -5321,16 +5477,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="C12" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="D12" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="E12" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -5341,16 +5497,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="C13" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="D13" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="E13" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -5361,19 +5517,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="C14" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="D14" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -5384,16 +5540,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="C15" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="D15" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="E15" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -5404,16 +5560,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="C16" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="D16" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="E16" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -5424,13 +5580,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="C17" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="D17" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -5444,16 +5600,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="C18" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="D18" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="E18" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -5464,13 +5620,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="C19" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="D19" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -5484,13 +5640,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="C20" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="D20" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5504,16 +5660,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="C21" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="D21" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="E21" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -5524,16 +5680,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="C22" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="D22" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="E22" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -5544,13 +5700,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="C23" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="D23" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -5564,19 +5720,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="C24" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="D24" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -5587,13 +5743,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="C25" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="D25" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -5607,16 +5763,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="C26" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="D26" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="E26" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -5630,16 +5786,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="C27" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="D27" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="E27" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -5650,13 +5806,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="C28" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="D28" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -5670,19 +5826,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="C29" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="D29" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -5696,13 +5852,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="C30" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="D30" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -5716,19 +5872,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="C31" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="D31" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="E31" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="F31" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -5739,19 +5895,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="C32" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="D32" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -5762,19 +5918,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="C33" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="D33" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="E33">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -5785,16 +5941,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="C34" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="D34" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="E34" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -5805,16 +5961,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="C35" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="D35" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="E35" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -5825,19 +5981,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="C36" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="D36" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="E36" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="F36" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -5851,13 +6007,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="C37" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="D37" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="E37">
         <v>11</v>
@@ -5871,16 +6027,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="C38" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="D38" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="E38" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -5891,13 +6047,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="C39" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="D39" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -5914,16 +6070,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="C40" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="D40" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="E40" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -5934,13 +6090,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="C41" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="D41" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -5957,19 +6113,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="C42" t="s">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="D42" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -5983,13 +6139,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="C43" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="D43" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="E43">
         <v>12</v>
@@ -6003,13 +6159,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="C44" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="D44" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="E44">
         <v>13</v>
@@ -6023,19 +6179,19 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="C45" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="D45" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="E45" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="F45" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="I45">
         <v>-1</v>
@@ -6046,16 +6202,16 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="C46" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="D46" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="E46" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -6066,13 +6222,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="C47" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="D47" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="E47">
         <v>14</v>
@@ -6086,19 +6242,19 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="C48" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="D48" t="s">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="I48">
         <v>-1</v>
@@ -6109,13 +6265,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="C49" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="D49" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="E49">
         <v>15</v>
@@ -6129,19 +6285,19 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="C50" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="D50" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="I50">
         <v>-1</v>
@@ -6152,13 +6308,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>247</v>
+        <v>269</v>
       </c>
       <c r="C51" t="s">
-        <v>247</v>
+        <v>269</v>
       </c>
       <c r="D51" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="E51">
         <v>16</v>
@@ -6172,13 +6328,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="C52" t="s">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="D52" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -6192,13 +6348,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>249</v>
+        <v>271</v>
       </c>
       <c r="C53" t="s">
-        <v>249</v>
+        <v>271</v>
       </c>
       <c r="D53" t="s">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -6212,13 +6368,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="C54" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="D54" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="E54">
         <v>3</v>
@@ -6235,16 +6391,16 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="C55" t="s">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="D55" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="E55" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="G55">
         <v>6</v>
@@ -6258,16 +6414,16 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="C56" t="s">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="D56" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="E56" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="G56">
         <v>7</v>
@@ -6281,16 +6437,16 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="C57" t="s">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="D57" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="E57" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="G57">
         <v>8</v>
@@ -6304,16 +6460,16 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="C58" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="D58" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="E58" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="G58">
         <v>6</v>
@@ -6327,16 +6483,16 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="C59" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="D59" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="E59" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="G59">
         <v>7</v>
@@ -6350,16 +6506,16 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="C60" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="D60" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="E60" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="G60">
         <v>8</v>
@@ -6373,19 +6529,19 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="C61" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="D61" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="E61">
         <v>3</v>
       </c>
       <c r="F61" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="I61">
         <v>-1</v>
@@ -6396,18 +6552,121 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="C62" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="D62" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="E62">
         <v>20</v>
       </c>
       <c r="I62">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63" t="s">
+        <v>283</v>
+      </c>
+      <c r="C63" t="s">
+        <v>283</v>
+      </c>
+      <c r="D63" t="s">
+        <v>210</v>
+      </c>
+      <c r="F63" t="s">
+        <v>243</v>
+      </c>
+      <c r="I63">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64">
+        <v>62</v>
+      </c>
+      <c r="B64" t="s">
+        <v>284</v>
+      </c>
+      <c r="C64" t="s">
+        <v>284</v>
+      </c>
+      <c r="D64" t="s">
+        <v>206</v>
+      </c>
+      <c r="E64">
+        <v>21</v>
+      </c>
+      <c r="I64">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65">
+        <v>63</v>
+      </c>
+      <c r="B65" t="s">
+        <v>285</v>
+      </c>
+      <c r="C65" t="s">
+        <v>285</v>
+      </c>
+      <c r="D65" t="s">
+        <v>266</v>
+      </c>
+      <c r="E65">
+        <v>3</v>
+      </c>
+      <c r="I65">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66">
+        <v>64</v>
+      </c>
+      <c r="B66" t="s">
+        <v>286</v>
+      </c>
+      <c r="C66" t="s">
+        <v>286</v>
+      </c>
+      <c r="D66" t="s">
+        <v>206</v>
+      </c>
+      <c r="E66">
+        <v>14</v>
+      </c>
+      <c r="F66" t="s">
+        <v>192</v>
+      </c>
+      <c r="I66">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67">
+        <v>65</v>
+      </c>
+      <c r="B67" t="s">
+        <v>287</v>
+      </c>
+      <c r="C67" t="s">
+        <v>287</v>
+      </c>
+      <c r="D67" t="s">
+        <v>206</v>
+      </c>
+      <c r="E67">
+        <v>22</v>
+      </c>
+      <c r="I67">
         <v>-1</v>
       </c>
     </row>
@@ -6419,7 +6678,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -6442,43 +6701,43 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>261</v>
+        <v>288</v>
       </c>
       <c r="D1" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="F1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N1" t="s">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="O1" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -6486,10 +6745,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="C2" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -6515,10 +6774,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="C3" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -6538,10 +6797,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>269</v>
+        <v>296</v>
       </c>
       <c r="C4" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -6555,10 +6814,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>270</v>
+        <v>297</v>
       </c>
       <c r="C5" t="s">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -6590,10 +6849,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>272</v>
+        <v>299</v>
       </c>
       <c r="C6" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -6613,10 +6872,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>273</v>
+        <v>300</v>
       </c>
       <c r="C7" t="s">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -6636,10 +6895,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>274</v>
+        <v>301</v>
       </c>
       <c r="C8" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -6659,10 +6918,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>275</v>
+        <v>302</v>
       </c>
       <c r="C9" t="s">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -6682,10 +6941,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="C10" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -6705,10 +6964,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="C11" t="s">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -6734,10 +6993,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="C12" t="s">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -6763,10 +7022,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="C13" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -6786,10 +7045,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="C14" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -6809,10 +7068,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>276</v>
+        <v>303</v>
       </c>
       <c r="C15" t="s">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -6832,10 +7091,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>277</v>
+        <v>304</v>
       </c>
       <c r="C16" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -6855,10 +7114,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="C17" t="s">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -6878,10 +7137,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>247</v>
+        <v>269</v>
       </c>
       <c r="C18" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -6901,10 +7160,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="C19" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -6918,10 +7177,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>279</v>
+        <v>306</v>
       </c>
       <c r="C20" t="s">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -6935,10 +7194,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>280</v>
+        <v>307</v>
       </c>
       <c r="C21" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -6952,10 +7211,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>281</v>
+        <v>308</v>
       </c>
       <c r="C22" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -6968,6 +7227,222 @@
       </c>
       <c r="G22">
         <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>309</v>
+      </c>
+      <c r="C23" t="s">
+        <v>298</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>61</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>287</v>
+      </c>
+      <c r="C24" t="s">
+        <v>294</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>64</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>310</v>
+      </c>
+      <c r="C25" t="s">
+        <v>294</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C26" t="s">
+        <v>294</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>312</v>
+      </c>
+      <c r="C27" t="s">
+        <v>294</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>313</v>
+      </c>
+      <c r="C28" t="s">
+        <v>294</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>314</v>
+      </c>
+      <c r="C29" t="s">
+        <v>294</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>315</v>
+      </c>
+      <c r="C30" t="s">
+        <v>294</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>316</v>
+      </c>
+      <c r="C31" t="s">
+        <v>294</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>317</v>
+      </c>
+      <c r="C32" t="s">
+        <v>294</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>318</v>
+      </c>
+      <c r="C33" t="s">
+        <v>294</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>319</v>
+      </c>
+      <c r="C34" t="s">
+        <v>294</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6998,19 +7473,19 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>282</v>
+        <v>320</v>
       </c>
       <c r="E1" t="s">
-        <v>283</v>
+        <v>321</v>
       </c>
       <c r="F1" t="s">
-        <v>284</v>
+        <v>322</v>
       </c>
       <c r="G1" t="s">
-        <v>285</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -7018,13 +7493,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>286</v>
+        <v>324</v>
       </c>
       <c r="C2" t="s">
-        <v>287</v>
+        <v>325</v>
       </c>
       <c r="D2" t="s">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -7038,16 +7513,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>289</v>
+        <v>327</v>
       </c>
       <c r="C3" t="s">
-        <v>290</v>
+        <v>328</v>
       </c>
       <c r="D3" t="s">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="12.95" customHeight="1">
@@ -7055,16 +7530,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>291</v>
+        <v>329</v>
       </c>
       <c r="C4" t="s">
-        <v>290</v>
+        <v>328</v>
       </c>
       <c r="D4" t="s">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="F4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -7072,13 +7547,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>292</v>
+        <v>330</v>
       </c>
       <c r="C5" t="s">
-        <v>287</v>
+        <v>325</v>
       </c>
       <c r="D5" t="s">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -7092,13 +7567,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>293</v>
+        <v>331</v>
       </c>
       <c r="C6" t="s">
-        <v>287</v>
+        <v>325</v>
       </c>
       <c r="D6" t="s">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -7112,13 +7587,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>294</v>
+        <v>332</v>
       </c>
       <c r="C7" t="s">
-        <v>287</v>
+        <v>325</v>
       </c>
       <c r="D7" t="s">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -7132,13 +7607,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>295</v>
+        <v>333</v>
       </c>
       <c r="C8" t="s">
-        <v>287</v>
+        <v>325</v>
       </c>
       <c r="D8" t="s">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -7152,13 +7627,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>296</v>
+        <v>334</v>
       </c>
       <c r="C9" t="s">
-        <v>287</v>
+        <v>325</v>
       </c>
       <c r="D9" t="s">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -7172,13 +7647,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>297</v>
+        <v>335</v>
       </c>
       <c r="C10" t="s">
-        <v>287</v>
+        <v>325</v>
       </c>
       <c r="D10" t="s">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -7192,16 +7667,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>298</v>
+        <v>336</v>
       </c>
       <c r="C11" t="s">
-        <v>299</v>
+        <v>337</v>
       </c>
       <c r="D11" t="s">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="E11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F11">
         <v>2</v>

--- a/Assets/StreamingAssets/Configurations/dev/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/dev/Cards.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25445DB6-07B5-4749-ACC2-57EB25569AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F7F6C2F-AB49-4852-AAEA-8DE1AED9A0E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>

--- a/Assets/StreamingAssets/Configurations/dev/Cards.xlsx
+++ b/Assets/StreamingAssets/Configurations/dev/Cards.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\dev\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F7F6C2F-AB49-4852-AAEA-8DE1AED9A0E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25445DB6-07B5-4749-ACC2-57EB25569AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
